--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -35094,7 +35094,7 @@
         <v>0</v>
       </c>
       <c r="G1496" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
@@ -35108,7 +35108,7 @@
         <v>53</v>
       </c>
       <c r="D1497" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E1497">
         <v>1</v>
@@ -35117,7 +35117,7 @@
         <v>1</v>
       </c>
       <c r="G1497" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1498" spans="1:7" x14ac:dyDescent="0.25">
@@ -35140,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="G1498" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1499" spans="1:7" x14ac:dyDescent="0.25">
@@ -35154,7 +35154,7 @@
         <v>53</v>
       </c>
       <c r="D1499" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E1499">
         <v>2</v>
@@ -35163,7 +35163,7 @@
         <v>1</v>
       </c>
       <c r="G1499" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1500" spans="1:7" x14ac:dyDescent="0.25">
@@ -35177,7 +35177,7 @@
         <v>53</v>
       </c>
       <c r="D1500" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E1500">
         <v>1</v>
@@ -35186,7 +35186,7 @@
         <v>2</v>
       </c>
       <c r="G1500" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1501" spans="1:7" x14ac:dyDescent="0.25">
@@ -35200,7 +35200,7 @@
         <v>53</v>
       </c>
       <c r="D1501" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E1501">
         <v>1</v>
@@ -35209,7 +35209,7 @@
         <v>1</v>
       </c>
       <c r="G1501" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
@@ -35232,7 +35232,7 @@
         <v>0</v>
       </c>
       <c r="G1502" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
@@ -35246,16 +35246,16 @@
         <v>60</v>
       </c>
       <c r="D1503" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1503">
+        <v>2</v>
+      </c>
+      <c r="F1503">
+        <v>0</v>
+      </c>
+      <c r="G1503" t="s">
         <v>64</v>
-      </c>
-      <c r="E1503">
-        <v>2</v>
-      </c>
-      <c r="F1503">
-        <v>0</v>
-      </c>
-      <c r="G1503" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
@@ -35278,7 +35278,7 @@
         <v>1</v>
       </c>
       <c r="G1504" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
@@ -35292,7 +35292,7 @@
         <v>60</v>
       </c>
       <c r="D1505" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E1505">
         <v>1</v>
@@ -35301,7 +35301,7 @@
         <v>2</v>
       </c>
       <c r="G1505" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
@@ -35315,7 +35315,7 @@
         <v>60</v>
       </c>
       <c r="D1506" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E1506">
         <v>0</v>
@@ -35338,7 +35338,7 @@
         <v>60</v>
       </c>
       <c r="D1507" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E1507">
         <v>1</v>
@@ -35347,7 +35347,7 @@
         <v>2</v>
       </c>
       <c r="G1507" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
@@ -35370,7 +35370,7 @@
         <v>0</v>
       </c>
       <c r="G1508" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1509" spans="1:7" x14ac:dyDescent="0.25">
@@ -35384,7 +35384,7 @@
         <v>65</v>
       </c>
       <c r="D1509" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E1509">
         <v>1</v>
@@ -35393,7 +35393,7 @@
         <v>1</v>
       </c>
       <c r="G1509" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1510" spans="1:7" x14ac:dyDescent="0.25">
@@ -35416,7 +35416,7 @@
         <v>1</v>
       </c>
       <c r="G1510" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1511" spans="1:7" x14ac:dyDescent="0.25">
@@ -35430,16 +35430,16 @@
         <v>65</v>
       </c>
       <c r="D1511" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1511">
+        <v>2</v>
+      </c>
+      <c r="F1511">
+        <v>0</v>
+      </c>
+      <c r="G1511" t="s">
         <v>67</v>
-      </c>
-      <c r="E1511">
-        <v>2</v>
-      </c>
-      <c r="F1511">
-        <v>0</v>
-      </c>
-      <c r="G1511" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="1512" spans="1:7" x14ac:dyDescent="0.25">
@@ -35453,16 +35453,16 @@
         <v>65</v>
       </c>
       <c r="D1512" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1512">
+        <v>1</v>
+      </c>
+      <c r="F1512">
+        <v>2</v>
+      </c>
+      <c r="G1512" t="s">
         <v>66</v>
-      </c>
-      <c r="E1512">
-        <v>1</v>
-      </c>
-      <c r="F1512">
-        <v>2</v>
-      </c>
-      <c r="G1512" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="1513" spans="1:7" x14ac:dyDescent="0.25">
@@ -35476,7 +35476,7 @@
         <v>65</v>
       </c>
       <c r="D1513" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E1513">
         <v>1</v>
@@ -35485,7 +35485,7 @@
         <v>1</v>
       </c>
       <c r="G1513" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1514" spans="1:7" x14ac:dyDescent="0.25">

--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -4121,7 +4121,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4197,7 +4197,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4273,7 +4273,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4311,7 +4311,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4349,7 +4349,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,7 +4387,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4425,7 +4425,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4615,7 +4615,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4653,7 +4653,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4691,7 +4691,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4729,7 +4729,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sudáfrica/Canadá</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Paises Bajos/Marruecos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4767,7 +4767,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>USA/Bosnia &amp; Herzegovina</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Belgica/Senegal</t>
+          <t>belgica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Brasil/Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Costa de Marfil/Noruega</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4843,7 +4843,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Argentina/Cabo Verde</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Australia/Egipto</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4881,7 +4881,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Suiza/Argelia</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Colombia/Ghana</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4919,7 +4919,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>México/Ecuador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Inglaterra/Congo</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Portugal/Croacia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>España Austria</t>
+          <t>España</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4995,7 +4995,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Alemania/Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Francia/Suecia</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5033,7 +5033,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5261,7 +5261,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5299,7 +5299,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Diego Martínez</t>
+          <t>Diego Martinez</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11126,7 +11126,11 @@
           <t>Canadá</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -11160,7 +11164,11 @@
           <t>Marruecos</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -11194,7 +11202,11 @@
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -11228,7 +11240,11 @@
           <t>Japón</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -11262,7 +11278,11 @@
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11296,7 +11316,11 @@
           <t>Argelia</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Suiza</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11330,7 +11354,11 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11364,7 +11392,11 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11398,7 +11430,11 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11432,7 +11468,11 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr"/>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11466,7 +11506,11 @@
           <t>Suecia</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr"/>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11500,7 +11544,11 @@
           <t>Croacia</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11534,7 +11582,11 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr"/>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11568,7 +11620,11 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr"/>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Belgica</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11602,7 +11658,11 @@
           <t>Congo</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11636,7 +11696,11 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr"/>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11670,7 +11734,11 @@
           <t>Países Bajos</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr"/>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11704,7 +11772,11 @@
           <t>Belgica</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11738,7 +11810,11 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11772,7 +11848,11 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11806,7 +11886,11 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11840,7 +11924,11 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11874,7 +11962,11 @@
           <t xml:space="preserve">España </t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11908,7 +12000,11 @@
           <t>Francia</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11942,7 +12038,11 @@
           <t>Países Bajos</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11976,7 +12076,11 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -12010,7 +12114,11 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -12044,7 +12152,11 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -12078,7 +12190,11 @@
           <t xml:space="preserve">España </t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -12112,7 +12228,11 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -12146,7 +12266,11 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -12180,7 +12304,11 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12214,7 +12342,11 @@
           <t>Canadá</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12248,7 +12380,11 @@
           <t>Marruecos</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12282,7 +12418,11 @@
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12309,14 +12449,18 @@
         <v>3</v>
       </c>
       <c r="F325" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12350,7 +12494,11 @@
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12418,7 +12566,11 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Egipto</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12445,7 +12597,7 @@
         <v>2</v>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -12486,7 +12638,11 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12520,7 +12676,11 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12554,7 +12714,11 @@
           <t>Suecia</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12622,7 +12786,11 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12649,14 +12817,18 @@
         <v>2</v>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Bélgica</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12690,7 +12862,11 @@
           <t>Congo</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12705,7 +12881,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Partido 1</t>
+          <t>Partido 16</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -12724,7 +12900,11 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12744,7 +12924,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Sudáfrica/Canadá</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -12755,10 +12935,14 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Paises Bajos/Marruecos</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr"/>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12778,18 +12962,18 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>USA/Bosnia &amp; Herzegovina</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E339" t="n">
         <v>2</v>
       </c>
       <c r="F339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Belgica/Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="H339" t="inlineStr"/>
@@ -12812,7 +12996,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Brasil/Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -12823,10 +13007,14 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Costa de Marfil/Noruega</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12846,7 +13034,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Argentina/Cabo Verde</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -12857,10 +13045,14 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Australia/Egipto</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
+          <t>Egipto</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12891,10 +13083,14 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Colombia/Ghana</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12925,10 +13121,14 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Inglaterra/Congo</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12959,10 +13159,14 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>España Austria</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr"/>
+          <t xml:space="preserve">España </t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12982,21 +13186,25 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Alemania/Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E345" t="n">
         <v>2</v>
       </c>
       <c r="F345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Francia/Suecia</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr"/>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -13016,21 +13224,25 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Ganador Partido 24</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E346" t="n">
         <v>2</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Ganador Partido 17</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr"/>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -13050,21 +13262,25 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Ganador Partido 23</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Ganador Partido 18</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr"/>
+          <t>Belgica</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -13084,21 +13300,25 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Ganador Partido 19</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E348" t="n">
         <v>2</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Ganador Partido 22</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -13118,18 +13338,18 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Ganador Partido 20</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ganador Partido 21</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H349" t="inlineStr"/>
@@ -13152,21 +13372,25 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Ganador Partido 25</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Ganador Partido 26</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr"/>
+          <t xml:space="preserve">España </t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -13186,21 +13410,25 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Ganador Partido 27</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Ganador Partido 28</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr"/>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13220,21 +13448,25 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Perdedor Partido 29</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Perdedor Partido 30</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr"/>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -13254,26 +13486,30 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Ganador Partido 29</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Ganador Partido 30</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr"/>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -13292,22 +13528,26 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
           <t>Canadá</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -13326,22 +13566,26 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
           <t>Marruecos</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Marruecos</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -13360,7 +13604,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F356" t="n">
         <v>1</v>
@@ -13370,12 +13614,16 @@
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -13394,7 +13642,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F357" t="n">
         <v>1</v>
@@ -13404,12 +13652,16 @@
           <t>Japón</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -13428,7 +13680,7 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -13438,12 +13690,16 @@
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -13465,19 +13721,23 @@
         <v>2</v>
       </c>
       <c r="F359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
           <t>Argelia</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Suiza</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -13506,12 +13766,16 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Egipto</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -13530,7 +13794,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F361" t="n">
         <v>2</v>
@@ -13540,12 +13804,16 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr"/>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -13574,12 +13842,16 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -13598,22 +13870,26 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -13642,12 +13918,16 @@
           <t>Suecia</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr"/>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -13676,12 +13956,16 @@
           <t>Croacia</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -13703,19 +13987,23 @@
         <v>3</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -13734,7 +14022,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F367" t="n">
         <v>1</v>
@@ -13744,12 +14032,16 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr"/>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Belgica</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -13768,7 +14060,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
@@ -13778,12 +14070,16 @@
           <t>Congo</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -13805,19 +14101,23 @@
         <v>2</v>
       </c>
       <c r="F369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -13832,7 +14132,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Sudáfrica/Canadá</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -13843,15 +14143,19 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Paises Bajos/Marruecos</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr"/>
+          <t>Marruecos</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Marruecos</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -13866,26 +14170,30 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>USA/Bosnia &amp; Herzegovina</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Belgica/Senegal</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr"/>
+          <t>Belgica</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Belgica</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -13900,7 +14208,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Brasil/Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -13911,15 +14219,19 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Costa de Marfil/Noruega</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr"/>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -13934,26 +14246,30 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Argentina/Cabo Verde</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Australia/Egipto</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr"/>
+          <t>Egipto</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -13968,26 +14284,30 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Suiza/Argelia</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F374" t="n">
         <v>2</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Colombia/Ghana</t>
-        </is>
-      </c>
-      <c r="H374" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14002,26 +14322,30 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>México/Ecuador</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F375" t="n">
         <v>2</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Inglaterra/Congo</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14036,26 +14360,30 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Portugal/Croacia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F376" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>España Austria</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr"/>
+          <t xml:space="preserve">España </t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -14070,26 +14398,30 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Alemania/Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F377" t="n">
         <v>3</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Francia/Suecia</t>
-        </is>
-      </c>
-      <c r="H377" t="inlineStr"/>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -14115,15 +14447,19 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
-        </is>
-      </c>
-      <c r="H378" t="inlineStr"/>
+          <t>Marruecos</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -14145,19 +14481,23 @@
         <v>2</v>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
           <t>Belgica</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -14176,22 +14516,26 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -14213,19 +14557,23 @@
         <v>1</v>
       </c>
       <c r="F381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr"/>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -14244,7 +14592,7 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F382" t="n">
         <v>1</v>
@@ -14254,12 +14602,16 @@
           <t xml:space="preserve">España </t>
         </is>
       </c>
-      <c r="H382" t="inlineStr"/>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -14274,26 +14626,30 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="E383" t="n">
         <v>1</v>
       </c>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="H383" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -14315,19 +14671,23 @@
         <v>1</v>
       </c>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="H384" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Julián Lozano</t>
+          <t>Mario Betancourt</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -14346,22 +14706,26 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -14380,10 +14744,10 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
@@ -14392,14 +14756,14 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Canadá</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -14418,10 +14782,10 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -14430,14 +14794,14 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -14459,7 +14823,7 @@
         <v>2</v>
       </c>
       <c r="F388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -14475,7 +14839,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -14513,7 +14877,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -14532,7 +14896,7 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F390" t="n">
         <v>0</v>
@@ -14551,7 +14915,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -14589,7 +14953,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -14611,23 +14975,19 @@
         <v>1</v>
       </c>
       <c r="F392" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>Egipto</t>
-        </is>
-      </c>
+      <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -14646,10 +15006,10 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
@@ -14658,14 +15018,14 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>México</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -14703,7 +15063,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -14722,7 +15082,7 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F395" t="n">
         <v>1</v>
@@ -14741,7 +15101,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -14763,7 +15123,7 @@
         <v>3</v>
       </c>
       <c r="F396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -14779,7 +15139,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -14801,7 +15161,7 @@
         <v>1</v>
       </c>
       <c r="F397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -14817,7 +15177,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -14839,7 +15199,7 @@
         <v>3</v>
       </c>
       <c r="F398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -14855,7 +15215,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -14877,7 +15237,7 @@
         <v>1</v>
       </c>
       <c r="F399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -14886,14 +15246,14 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Belgica</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -14931,7 +15291,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -14969,7 +15329,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -14995,19 +15355,19 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15033,19 +15393,15 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Belgica</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>Belgica</t>
-        </is>
-      </c>
+          <t>Bélgica</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15076,14 +15432,14 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Brasiñ</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15102,14 +15458,14 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Australia/Egipto</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -15121,7 +15477,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15159,7 +15515,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15174,30 +15530,26 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E407" t="n">
         <v>1</v>
       </c>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+      <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15216,14 +15568,14 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F408" t="n">
         <v>2</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
+          <t>España</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -15235,7 +15587,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15257,7 +15609,7 @@
         <v>1</v>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -15273,7 +15625,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15299,7 +15651,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -15311,7 +15663,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15337,19 +15689,15 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Belgica</t>
-        </is>
-      </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+          <t>Ganador Partido 18</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15368,26 +15716,22 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F412" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+          <t>Ganador Partido 22</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15409,23 +15753,19 @@
         <v>1</v>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
+      <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15451,7 +15791,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
+          <t>España</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -15463,7 +15803,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15478,30 +15818,26 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
+          <t>Ganador Partido 28</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15520,26 +15856,22 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+          <t>Perdedor Partido 30</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Mario Betancourt</t>
+          <t>Natalia Martinez</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15565,19 +15897,15 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+          <t>Ganador Partido 30</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15615,7 +15943,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15646,14 +15974,14 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t>Países Bajos</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15672,10 +16000,10 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -15691,7 +16019,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15710,7 +16038,7 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F421" t="n">
         <v>1</v>
@@ -15729,7 +16057,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15748,7 +16076,7 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F422" t="n">
         <v>0</v>
@@ -15767,7 +16095,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15805,7 +16133,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15824,22 +16152,26 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Egipto</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15861,7 +16193,7 @@
         <v>2</v>
       </c>
       <c r="F425" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -15877,7 +16209,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15899,7 +16231,7 @@
         <v>1</v>
       </c>
       <c r="F426" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
@@ -15915,7 +16247,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15934,10 +16266,10 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -15953,7 +16285,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -15975,7 +16307,7 @@
         <v>3</v>
       </c>
       <c r="F428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -15991,7 +16323,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16010,10 +16342,10 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F429" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -16029,7 +16361,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16067,7 +16399,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16086,10 +16418,10 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -16105,7 +16437,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16124,10 +16456,10 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -16143,7 +16475,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16181,7 +16513,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16203,23 +16535,23 @@
         <v>1</v>
       </c>
       <c r="F434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t>Países Bajos</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16241,19 +16573,23 @@
         <v>1</v>
       </c>
       <c r="F435" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
           <t>Bélgica</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Bélgica</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16284,14 +16620,14 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Brasiñ</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16313,11 +16649,11 @@
         <v>2</v>
       </c>
       <c r="F437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Australia/Egipto</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -16329,7 +16665,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16367,7 +16703,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16382,26 +16718,30 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Méxco</t>
         </is>
       </c>
       <c r="E439" t="n">
         <v>1</v>
       </c>
       <c r="F439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16423,7 +16763,7 @@
         <v>1</v>
       </c>
       <c r="F440" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -16439,7 +16779,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16458,7 +16798,7 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F441" t="n">
         <v>2</v>
@@ -16477,7 +16817,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16499,11 +16839,11 @@
         <v>2</v>
       </c>
       <c r="F442" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -16515,7 +16855,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16537,19 +16877,23 @@
         <v>2</v>
       </c>
       <c r="F443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Ganador Partido 18</t>
-        </is>
-      </c>
-      <c r="H443" t="inlineStr"/>
+          <t>Bélgica</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16568,22 +16912,26 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Ganador Partido 22</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16612,12 +16960,16 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16636,10 +16988,10 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -16648,14 +17000,14 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>España</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16670,7 +17022,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -16681,15 +17033,19 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Ganador Partido 28</t>
-        </is>
-      </c>
-      <c r="H447" t="inlineStr"/>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16704,26 +17060,30 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E448" t="n">
         <v>2</v>
       </c>
       <c r="F448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Perdedor Partido 30</t>
-        </is>
-      </c>
-      <c r="H448" t="inlineStr"/>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Natalia Martinez</t>
+          <t>Rigoberto Arango</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16738,7 +17098,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -16749,15 +17109,19 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Ganador Partido 30</t>
-        </is>
-      </c>
-      <c r="H449" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16795,7 +17159,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16814,7 +17178,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F451" t="n">
         <v>1</v>
@@ -16826,14 +17190,14 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16852,7 +17216,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F452" t="n">
         <v>1</v>
@@ -16871,7 +17235,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16890,7 +17254,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F453" t="n">
         <v>1</v>
@@ -16909,7 +17273,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16928,10 +17292,10 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -16947,7 +17311,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16966,7 +17330,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F455" t="n">
         <v>1</v>
@@ -16985,7 +17349,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -17007,7 +17371,7 @@
         <v>0</v>
       </c>
       <c r="F456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -17023,7 +17387,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -17045,7 +17409,7 @@
         <v>2</v>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -17061,7 +17425,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -17083,7 +17447,7 @@
         <v>1</v>
       </c>
       <c r="F458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -17099,7 +17463,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -17121,7 +17485,7 @@
         <v>2</v>
       </c>
       <c r="F459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -17137,7 +17501,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -17156,10 +17520,10 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -17175,7 +17539,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -17194,10 +17558,10 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -17206,14 +17570,14 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Croacia</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -17232,10 +17596,10 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -17251,7 +17615,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -17270,10 +17634,10 @@
         </is>
       </c>
       <c r="E463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
@@ -17282,14 +17646,14 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -17308,10 +17672,10 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F464" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -17327,7 +17691,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -17365,7 +17729,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -17387,23 +17751,23 @@
         <v>1</v>
       </c>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -17429,19 +17793,19 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -17479,7 +17843,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -17501,7 +17865,7 @@
         <v>2</v>
       </c>
       <c r="F469" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
@@ -17517,7 +17881,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -17536,7 +17900,7 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F470" t="n">
         <v>2</v>
@@ -17555,7 +17919,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -17570,7 +17934,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Méxco</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E471" t="n">
@@ -17593,7 +17957,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -17608,14 +17972,14 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="E472" t="n">
         <v>1</v>
       </c>
       <c r="F472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
@@ -17631,7 +17995,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -17650,7 +18014,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F473" t="n">
         <v>2</v>
@@ -17669,7 +18033,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -17691,11 +18055,11 @@
         <v>2</v>
       </c>
       <c r="F474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -17707,7 +18071,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -17726,14 +18090,14 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F475" t="n">
         <v>1</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -17745,7 +18109,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -17764,10 +18128,10 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
@@ -17776,14 +18140,14 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -17802,7 +18166,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F477" t="n">
         <v>1</v>
@@ -17821,12 +18185,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Semifinales</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -17840,10 +18204,10 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -17852,19 +18216,19 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Francia</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Semifinales</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -17874,7 +18238,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E479" t="n">
@@ -17885,19 +18249,19 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
           <t>Argentina</t>
-        </is>
-      </c>
-      <c r="H479" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -17912,7 +18276,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E480" t="n">
@@ -17923,19 +18287,19 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>España</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Rigoberto Arango</t>
+          <t>Sandra Salas</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -17950,7 +18314,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E481" t="n">
@@ -17961,19 +18325,19 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Francia</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -18011,7 +18375,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -18030,10 +18394,10 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -18042,14 +18406,14 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Paises Bajos (pen)</t>
+          <t>Paises Bajos</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -18087,7 +18451,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -18106,10 +18470,10 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -18118,14 +18482,14 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Japón</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -18147,7 +18511,7 @@
         <v>3</v>
       </c>
       <c r="F486" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -18163,7 +18527,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -18182,10 +18546,10 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F487" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -18194,14 +18558,14 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Suiza (pen)</t>
+          <t>Suiza</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -18220,7 +18584,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F488" t="n">
         <v>1</v>
@@ -18239,7 +18603,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -18258,10 +18622,10 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -18270,14 +18634,14 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Ecuador</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -18299,7 +18663,7 @@
         <v>1</v>
       </c>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -18315,7 +18679,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -18337,7 +18701,7 @@
         <v>2</v>
       </c>
       <c r="F491" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
@@ -18346,14 +18710,14 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -18372,7 +18736,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F492" t="n">
         <v>0</v>
@@ -18391,7 +18755,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -18429,7 +18793,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -18451,7 +18815,7 @@
         <v>2</v>
       </c>
       <c r="F494" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
@@ -18467,7 +18831,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -18489,7 +18853,7 @@
         <v>1</v>
       </c>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -18498,14 +18862,14 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -18543,7 +18907,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -18581,7 +18945,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -18619,7 +18983,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -18645,19 +19009,19 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -18672,14 +19036,14 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="E500" t="n">
         <v>2</v>
       </c>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
@@ -18688,14 +19052,14 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -18714,10 +19078,10 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F501" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -18733,7 +19097,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -18752,7 +19116,7 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F502" t="n">
         <v>2</v>
@@ -18771,7 +19135,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -18786,7 +19150,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E503" t="n">
@@ -18809,7 +19173,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -18847,7 +19211,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -18862,14 +19226,14 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E505" t="n">
         <v>1</v>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
@@ -18885,7 +19249,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -18904,7 +19268,7 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F506" t="n">
         <v>1</v>
@@ -18923,7 +19287,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -18942,26 +19306,26 @@
         </is>
       </c>
       <c r="E507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F507" t="n">
         <v>1</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>España (pen)</t>
+          <t>España</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -18976,14 +19340,14 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F508" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
@@ -18992,14 +19356,14 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -19021,7 +19385,7 @@
         <v>2</v>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
@@ -19037,12 +19401,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Semifinal</t>
+          <t>Semifinales</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -19075,12 +19439,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Semifinal</t>
+          <t>Semifinales</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -19090,18 +19454,18 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>1</v>
+      </c>
+      <c r="F511" t="n">
+        <v>3</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
           <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E511" t="n">
-        <v>2</v>
-      </c>
-      <c r="F511" t="n">
-        <v>1</v>
-      </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>Brasil</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -19113,7 +19477,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -19139,7 +19503,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -19151,7 +19515,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Sandra Salas</t>
+          <t>Sergio Pulgarin</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -19170,10 +19534,10 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
@@ -19189,7 +19553,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -19208,7 +19572,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F514" t="n">
         <v>2</v>
@@ -19227,7 +19591,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -19246,7 +19610,7 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F515" t="n">
         <v>2</v>
@@ -19265,7 +19629,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -19287,7 +19651,7 @@
         <v>2</v>
       </c>
       <c r="F516" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
@@ -19303,7 +19667,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -19322,10 +19686,10 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F517" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
@@ -19334,14 +19698,14 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -19360,7 +19724,7 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F518" t="n">
         <v>0</v>
@@ -19379,7 +19743,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -19401,7 +19765,7 @@
         <v>2</v>
       </c>
       <c r="F519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -19417,7 +19781,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -19455,7 +19819,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -19474,10 +19838,10 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
@@ -19493,7 +19857,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -19531,7 +19895,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -19553,7 +19917,7 @@
         <v>2</v>
       </c>
       <c r="F523" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
@@ -19562,14 +19926,14 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -19588,10 +19952,10 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F524" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -19607,7 +19971,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -19626,10 +19990,10 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F525" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
@@ -19638,14 +20002,14 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -19683,7 +20047,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -19705,7 +20069,7 @@
         <v>1</v>
       </c>
       <c r="F527" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
@@ -19714,14 +20078,14 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -19740,10 +20104,10 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
@@ -19759,7 +20123,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -19781,7 +20145,7 @@
         <v>2</v>
       </c>
       <c r="F529" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
@@ -19797,7 +20161,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -19816,10 +20180,10 @@
         </is>
       </c>
       <c r="E530" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G530" t="inlineStr">
         <is>
@@ -19835,7 +20199,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -19854,26 +20218,26 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -19888,14 +20252,14 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
@@ -19904,14 +20268,14 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -19949,7 +20313,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -19987,7 +20351,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -20009,7 +20373,7 @@
         <v>1</v>
       </c>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
@@ -20025,7 +20389,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -20040,30 +20404,30 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E536" t="n">
         <v>1</v>
       </c>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -20078,7 +20442,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E537" t="n">
@@ -20101,7 +20465,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -20120,7 +20484,7 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F538" t="n">
         <v>1</v>
@@ -20139,7 +20503,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -20154,30 +20518,30 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
       <c r="E539" t="n">
         <v>2</v>
       </c>
       <c r="F539" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -20192,14 +20556,14 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F540" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -20215,7 +20579,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -20237,7 +20601,7 @@
         <v>2</v>
       </c>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G541" t="inlineStr">
         <is>
@@ -20253,7 +20617,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -20279,7 +20643,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -20291,7 +20655,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -20313,7 +20677,7 @@
         <v>1</v>
       </c>
       <c r="F543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G543" t="inlineStr">
         <is>
@@ -20329,7 +20693,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -20344,14 +20708,14 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F544" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G544" t="inlineStr">
         <is>
@@ -20360,14 +20724,14 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Inglaterra</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Sergio Pulgarin</t>
+          <t>Tatiana Camargo</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -20405,7 +20769,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -20424,7 +20788,7 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F546" t="n">
         <v>2</v>
@@ -20443,7 +20807,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -20462,10 +20826,10 @@
         </is>
       </c>
       <c r="E547" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F547" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G547" t="inlineStr">
         <is>
@@ -20481,7 +20845,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -20519,7 +20883,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -20541,7 +20905,7 @@
         <v>2</v>
       </c>
       <c r="F549" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G549" t="inlineStr">
         <is>
@@ -20557,7 +20921,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -20576,7 +20940,7 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F550" t="n">
         <v>0</v>
@@ -20595,7 +20959,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -20614,10 +20978,10 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F551" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G551" t="inlineStr">
         <is>
@@ -20633,7 +20997,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -20652,7 +21016,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F552" t="n">
         <v>1</v>
@@ -20664,14 +21028,14 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -20690,7 +21054,7 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F553" t="n">
         <v>1</v>
@@ -20702,14 +21066,14 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>México</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -20728,10 +21092,10 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F554" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G554" t="inlineStr">
         <is>
@@ -20740,14 +21104,14 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Costa de Marfil</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -20785,7 +21149,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -20804,7 +21168,7 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F556" t="n">
         <v>1</v>
@@ -20823,7 +21187,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -20861,7 +21225,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -20880,10 +21244,10 @@
         </is>
       </c>
       <c r="E558" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F558" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G558" t="inlineStr">
         <is>
@@ -20899,7 +21263,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -20918,10 +21282,10 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F559" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G559" t="inlineStr">
         <is>
@@ -20930,14 +21294,14 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -20959,7 +21323,7 @@
         <v>3</v>
       </c>
       <c r="F560" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G560" t="inlineStr">
         <is>
@@ -20975,7 +21339,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -20997,7 +21361,7 @@
         <v>2</v>
       </c>
       <c r="F561" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G561" t="inlineStr">
         <is>
@@ -21013,7 +21377,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -21032,10 +21396,10 @@
         </is>
       </c>
       <c r="E562" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F562" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G562" t="inlineStr">
         <is>
@@ -21051,7 +21415,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -21077,7 +21441,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -21089,7 +21453,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -21111,11 +21475,11 @@
         <v>3</v>
       </c>
       <c r="F564" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Costa de Marfila</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -21127,7 +21491,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -21146,14 +21510,14 @@
         </is>
       </c>
       <c r="E565" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F565" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -21165,7 +21529,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -21203,7 +21567,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -21218,14 +21582,14 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E567" t="n">
         <v>1</v>
       </c>
       <c r="F567" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G567" t="inlineStr">
         <is>
@@ -21241,7 +21605,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -21263,23 +21627,23 @@
         <v>1</v>
       </c>
       <c r="F568" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
+          <t>España</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
+          <t>España</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -21298,10 +21662,10 @@
         </is>
       </c>
       <c r="E569" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G569" t="inlineStr">
         <is>
@@ -21310,14 +21674,14 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Alemania</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -21332,7 +21696,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E570" t="n">
@@ -21348,14 +21712,14 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Alemania</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -21370,7 +21734,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
+          <t>España</t>
         </is>
       </c>
       <c r="E571" t="n">
@@ -21386,14 +21750,14 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
+          <t>España</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -21424,14 +21788,14 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -21469,7 +21833,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -21484,30 +21848,22 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Francia</t>
-        </is>
-      </c>
-      <c r="E574" t="n">
-        <v>2</v>
-      </c>
-      <c r="F574" t="n">
-        <v>1</v>
-      </c>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr"/>
       <c r="G574" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
-        </is>
-      </c>
-      <c r="H574" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -21522,30 +21878,22 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="E575" t="n">
-        <v>1</v>
-      </c>
-      <c r="F575" t="n">
-        <v>2</v>
-      </c>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr"/>
+      <c r="F575" t="inlineStr"/>
       <c r="G575" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H575" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="H575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -21560,30 +21908,22 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
-        </is>
-      </c>
-      <c r="E576" t="n">
-        <v>1</v>
-      </c>
-      <c r="F576" t="n">
-        <v>2</v>
-      </c>
+          <t>Perdedor Partido 29</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr"/>
+      <c r="F576" t="inlineStr"/>
       <c r="G576" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="H576" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+          <t>Perdedor Partido 30</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Tatiana Camargo</t>
+          <t>Viviana Daza</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -21598,30 +21938,22 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Francia</t>
-        </is>
-      </c>
-      <c r="E577" t="n">
-        <v>3</v>
-      </c>
-      <c r="F577" t="n">
-        <v>2</v>
-      </c>
+          <t>Ganador Partido 29</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr"/>
+      <c r="F577" t="inlineStr"/>
       <c r="G577" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="H577" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+          <t>Ganador Partido 30</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -21640,10 +21972,10 @@
         </is>
       </c>
       <c r="E578" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F578" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G578" t="inlineStr">
         <is>
@@ -21652,14 +21984,14 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t xml:space="preserve">Canadá </t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -21678,7 +22010,7 @@
         </is>
       </c>
       <c r="E579" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F579" t="n">
         <v>1</v>
@@ -21690,14 +22022,14 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t xml:space="preserve">Países bajos </t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -21728,14 +22060,14 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Usa</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -21754,10 +22086,10 @@
         </is>
       </c>
       <c r="E581" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F581" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G581" t="inlineStr">
         <is>
@@ -21766,14 +22098,14 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t xml:space="preserve">Brasil </t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -21792,7 +22124,7 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F582" t="n">
         <v>0</v>
@@ -21804,14 +22136,14 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t xml:space="preserve">Argentina </t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -21833,7 +22165,7 @@
         <v>1</v>
       </c>
       <c r="F583" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G583" t="inlineStr">
         <is>
@@ -21842,14 +22174,14 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t xml:space="preserve">Suiza </t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -21868,10 +22200,10 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F584" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G584" t="inlineStr">
         <is>
@@ -21880,14 +22212,14 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t xml:space="preserve">Egipto </t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -21906,10 +22238,10 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F585" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G585" t="inlineStr">
         <is>
@@ -21918,14 +22250,14 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>México</t>
+          <t xml:space="preserve">Ecuador </t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -21944,10 +22276,10 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F586" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G586" t="inlineStr">
         <is>
@@ -21956,14 +22288,14 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Costa de Marfil</t>
+          <t xml:space="preserve">Noruega </t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -21982,7 +22314,7 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F587" t="n">
         <v>1</v>
@@ -21994,14 +22326,14 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t xml:space="preserve">Alemania </t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -22020,7 +22352,7 @@
         </is>
       </c>
       <c r="E588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F588" t="n">
         <v>1</v>
@@ -22032,14 +22364,14 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t xml:space="preserve">Francia </t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -22058,10 +22390,10 @@
         </is>
       </c>
       <c r="E589" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F589" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G589" t="inlineStr">
         <is>
@@ -22070,14 +22402,14 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t xml:space="preserve">Croacia </t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -22108,14 +22440,14 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -22146,14 +22478,14 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t xml:space="preserve">Bélgica </t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -22184,14 +22516,14 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t xml:space="preserve">Inglaterra </t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -22213,7 +22545,7 @@
         <v>2</v>
       </c>
       <c r="F593" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G593" t="inlineStr">
         <is>
@@ -22222,14 +22554,14 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t xml:space="preserve">Colombia </t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -22255,19 +22587,19 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t xml:space="preserve">Países bajos </t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t xml:space="preserve">Países bajos </t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -22286,26 +22618,26 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F595" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Belgica</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t xml:space="preserve">Bélgica </t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -22324,26 +22656,26 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F596" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Costa de Marfila</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t xml:space="preserve">Noruega </t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -22362,26 +22694,26 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F597" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t xml:space="preserve">Argentina </t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -22412,14 +22744,14 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t xml:space="preserve">Colombia </t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -22434,11 +22766,11 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F599" t="n">
         <v>2</v>
@@ -22450,14 +22782,14 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t xml:space="preserve">Inglaterra </t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -22472,30 +22804,30 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="E600" t="n">
         <v>1</v>
       </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -22514,10 +22846,10 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F601" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G601" t="inlineStr">
         <is>
@@ -22526,14 +22858,14 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t xml:space="preserve">Francia </t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -22548,7 +22880,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t xml:space="preserve">Francia </t>
         </is>
       </c>
       <c r="E602" t="n">
@@ -22559,19 +22891,19 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
+          <t xml:space="preserve">Países bajos </t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t xml:space="preserve">Alemania </t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -22593,23 +22925,23 @@
         <v>2</v>
       </c>
       <c r="F603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t xml:space="preserve">Bélgica </t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>España</t>
+          <t xml:space="preserve">España </t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -22624,30 +22956,30 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F604" t="n">
         <v>1</v>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t xml:space="preserve">Inglaterra </t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t xml:space="preserve">Inglaterra </t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -22662,14 +22994,14 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t xml:space="preserve">Argentina </t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F605" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G605" t="inlineStr">
         <is>
@@ -22678,14 +23010,14 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t xml:space="preserve">Colombia </t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -22700,22 +23032,30 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Alemania</t>
-        </is>
-      </c>
-      <c r="E606" t="inlineStr"/>
-      <c r="F606" t="inlineStr"/>
+          <t xml:space="preserve">Francia </t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>2</v>
+      </c>
+      <c r="F606" t="n">
+        <v>1</v>
+      </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="H606" t="inlineStr"/>
+          <t xml:space="preserve">España </t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francia </t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -22730,22 +23070,30 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr"/>
-      <c r="F607" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>1</v>
+      </c>
+      <c r="F607" t="n">
+        <v>1</v>
+      </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="H607" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colombia </t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -22760,22 +23108,30 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Perdedor Partido 29</t>
-        </is>
-      </c>
-      <c r="E608" t="inlineStr"/>
-      <c r="F608" t="inlineStr"/>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>1</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0</v>
+      </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Perdedor Partido 30</t>
-        </is>
-      </c>
-      <c r="H608" t="inlineStr"/>
+          <t xml:space="preserve">Inglaterra </t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">España </t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Viviana Daza</t>
+          <t>Walter Rojas</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -22790,17 +23146,25 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Ganador Partido 29</t>
-        </is>
-      </c>
-      <c r="E609" t="inlineStr"/>
-      <c r="F609" t="inlineStr"/>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>2</v>
+      </c>
+      <c r="F609" t="n">
+        <v>1</v>
+      </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Ganador Partido 30</t>
-        </is>
-      </c>
-      <c r="H609" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francia </t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -22834,7 +23198,11 @@
           <t>Canadá</t>
         </is>
       </c>
-      <c r="H610" t="inlineStr"/>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -22868,7 +23236,11 @@
           <t>Marruecos</t>
         </is>
       </c>
-      <c r="H611" t="inlineStr"/>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -22902,7 +23274,11 @@
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="H612" t="inlineStr"/>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -22936,7 +23312,11 @@
           <t>Japón</t>
         </is>
       </c>
-      <c r="H613" t="inlineStr"/>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -22970,7 +23350,11 @@
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="H614" t="inlineStr"/>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -23004,7 +23388,11 @@
           <t>Argelia</t>
         </is>
       </c>
-      <c r="H615" t="inlineStr"/>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Suiza</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -23038,7 +23426,11 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H616" t="inlineStr"/>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Egipto</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -23106,7 +23498,11 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="H618" t="inlineStr"/>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -23140,7 +23536,11 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr"/>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -23174,7 +23574,11 @@
           <t>Suecia</t>
         </is>
       </c>
-      <c r="H620" t="inlineStr"/>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -23208,7 +23612,11 @@
           <t>Croacia</t>
         </is>
       </c>
-      <c r="H621" t="inlineStr"/>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -23242,7 +23650,11 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="H622" t="inlineStr"/>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -23276,7 +23688,11 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="H623" t="inlineStr"/>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Bélgica</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -23310,7 +23726,11 @@
           <t>Congo</t>
         </is>
       </c>
-      <c r="H624" t="inlineStr"/>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -23344,7 +23764,11 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="H625" t="inlineStr"/>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -23364,7 +23788,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Sudáfrica/Canadá</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E626" t="n">
@@ -23375,10 +23799,14 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Paises Bajos/Marruecos</t>
-        </is>
-      </c>
-      <c r="H626" t="inlineStr"/>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -23398,7 +23826,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>USA/Bosnia &amp; Herzegovina</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E627" t="n">
@@ -23409,10 +23837,14 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Belgica/Senegal</t>
-        </is>
-      </c>
-      <c r="H627" t="inlineStr"/>
+          <t>Bélgica</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -23432,7 +23864,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Brasil/Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E628" t="n">
@@ -23443,10 +23875,14 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Costa de Marfil/Noruega</t>
-        </is>
-      </c>
-      <c r="H628" t="inlineStr"/>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -23466,7 +23902,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Argentina/Cabo Verde</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E629" t="n">
@@ -23477,10 +23913,14 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>Australia/Egipto</t>
-        </is>
-      </c>
-      <c r="H629" t="inlineStr"/>
+          <t>Egipto</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -23500,7 +23940,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Suiza/Argelia</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="E630" t="n">
@@ -23511,10 +23951,14 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Colombia/Ghana</t>
-        </is>
-      </c>
-      <c r="H630" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -23545,10 +23989,14 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Inglaterra/Congo</t>
-        </is>
-      </c>
-      <c r="H631" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -23568,7 +24016,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Portugal/Croacia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E632" t="n">
@@ -23579,10 +24027,14 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>España Austria</t>
-        </is>
-      </c>
-      <c r="H632" t="inlineStr"/>
+          <t xml:space="preserve">España </t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -23602,7 +24054,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Alemania/Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E633" t="n">
@@ -23613,10 +24065,14 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Francia/Suecia</t>
-        </is>
-      </c>
-      <c r="H633" t="inlineStr"/>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -23650,7 +24106,11 @@
           <t>Paises Bajos</t>
         </is>
       </c>
-      <c r="H634" t="inlineStr"/>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -23684,7 +24144,11 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr"/>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -23718,7 +24182,11 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr"/>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -23752,7 +24220,11 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr"/>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -23786,7 +24258,11 @@
           <t xml:space="preserve">España </t>
         </is>
       </c>
-      <c r="H638" t="inlineStr"/>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -23820,7 +24296,11 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H639" t="inlineStr"/>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -23854,7 +24334,11 @@
           <t>Brasil</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr"/>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -24516,7 +25000,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Sudáfrica/Canadá</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E658" t="n">
@@ -24527,10 +25011,14 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>Paises Bajos/Marruecos</t>
-        </is>
-      </c>
-      <c r="H658" t="inlineStr"/>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -24550,7 +25038,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>USA/Bosnia &amp; Herzegovina</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E659" t="n">
@@ -24561,10 +25049,14 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Belgica/Senegal</t>
-        </is>
-      </c>
-      <c r="H659" t="inlineStr"/>
+          <t>Belgica</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -24584,7 +25076,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Brasil/Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E660" t="n">
@@ -24595,10 +25087,14 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>Costa de Marfil/Noruega</t>
-        </is>
-      </c>
-      <c r="H660" t="inlineStr"/>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -24618,7 +25114,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Argentina/Cabo Verde</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E661" t="n">
@@ -24629,10 +25125,14 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Australia/Egipto</t>
-        </is>
-      </c>
-      <c r="H661" t="inlineStr"/>
+          <t>Egipto</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -24652,7 +25152,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Suiza/Argelia</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="E662" t="n">
@@ -24663,10 +25163,14 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Colombia/Ghana</t>
-        </is>
-      </c>
-      <c r="H662" t="inlineStr"/>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -24686,7 +25190,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>México/Ecuador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E663" t="n">
@@ -24697,10 +25201,14 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Inglaterra/Congo</t>
-        </is>
-      </c>
-      <c r="H663" t="inlineStr"/>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -24720,7 +25228,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Portugal/Croacia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E664" t="n">
@@ -24731,10 +25239,14 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>España Austria</t>
-        </is>
-      </c>
-      <c r="H664" t="inlineStr"/>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -24754,7 +25266,7 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Alemania/Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E665" t="n">
@@ -24765,10 +25277,14 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Francia/Suecia</t>
-        </is>
-      </c>
-      <c r="H665" t="inlineStr"/>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -24802,7 +25318,11 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="H666" t="inlineStr"/>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -24836,7 +25356,11 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr"/>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -24870,7 +25394,11 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr"/>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -24904,7 +25432,11 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H669" t="inlineStr"/>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -24938,7 +25470,11 @@
           <t>España</t>
         </is>
       </c>
-      <c r="H670" t="inlineStr"/>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -24972,7 +25508,11 @@
           <t xml:space="preserve">Colombia </t>
         </is>
       </c>
-      <c r="H671" t="inlineStr"/>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -25006,7 +25546,11 @@
           <t xml:space="preserve">Brasil </t>
         </is>
       </c>
-      <c r="H672" t="inlineStr"/>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -25040,7 +25584,11 @@
           <t xml:space="preserve">Colombia </t>
         </is>
       </c>
-      <c r="H673" t="inlineStr"/>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -7176,7 +7176,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Sudáfrica/Canadá</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Paises Bajos/Marruecos</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>USA/Bosnia &amp; Herzegovina</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Belgica/Senegal</t>
+          <t>Belgica</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Brasil/Japón</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Costa de Marfil/Noruega</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Argentina/Cabo Verde</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Australia/Egipto</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Suiza/Argelia</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Colombia/Ghana</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>México/Ecuador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Inglaterra/Congo</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Portugal/Croacia</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>España Austria</t>
+          <t>España</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Alemania/Paraguay</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Francia/Suecia</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ganador Partido 24</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ganador Partido 17</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Ganador Partido 23</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Ganador Partido 18</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Ganador Partido 19</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ganador Partido 22</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Ganador Partido 20</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Ganador Partido 21</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Ganador Partido 25</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ganador Partido 26</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Ganador Partido 27</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ganador Partido 28</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Perdedor Partido 29</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Perdedor Partido 30</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Ganador Partido 29</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ganador Partido 30</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12342,11 +12342,7 @@
           <t>Canadá</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>Canadá</t>
-        </is>
-      </c>
+      <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12380,11 +12376,7 @@
           <t>Marruecos</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>Paises Bajos</t>
-        </is>
-      </c>
+      <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12418,11 +12410,7 @@
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
+      <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12456,11 +12444,7 @@
           <t>Japón</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
+      <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12494,11 +12478,7 @@
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12532,7 +12512,11 @@
           <t>Argelia</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suiza </t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12566,11 +12550,7 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>Egipto</t>
-        </is>
-      </c>
+      <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12604,7 +12584,11 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecuador </t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12638,11 +12622,7 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>Noruega</t>
-        </is>
-      </c>
+      <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12676,11 +12656,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>Alemania</t>
-        </is>
-      </c>
+      <c r="H331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12714,11 +12690,7 @@
           <t>Suecia</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12752,7 +12724,11 @@
           <t>Croacia</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portugal </t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12786,11 +12762,7 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+      <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12824,11 +12796,7 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>Bélgica</t>
-        </is>
-      </c>
+      <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12862,11 +12830,7 @@
           <t>Congo</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+      <c r="H336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12900,11 +12864,7 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
+      <c r="H337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12924,7 +12884,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Sudáfrica/Canadá</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -12935,14 +12895,10 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>Paises Bajos</t>
-        </is>
-      </c>
+          <t>Paises Bajos/Marruecos</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12962,7 +12918,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA/Bosnia &amp; Herzegovina</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -12973,10 +12929,14 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Bélgica</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr"/>
+          <t>Belgica/Senegal</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bélgica </t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12996,7 +12956,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Brasil/Japón</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -13007,14 +12967,10 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Noruega</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
+          <t>Costa de Marfil/Noruega</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -13034,7 +12990,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Argentina/Cabo Verde</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -13045,14 +13001,10 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Egipto</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+          <t>Australia/Egipto</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -13083,14 +13035,10 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
+          <t>Colombia/Ghana</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -13121,14 +13069,10 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+          <t>Inglaterra/Congo</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -13159,14 +13103,10 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+          <t>España Austria</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -13186,7 +13126,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Alemania/Paraguay</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -13197,14 +13137,10 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Francia</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+          <t>Francia/Suecia</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -13238,11 +13174,7 @@
           <t>Paises Bajos</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+      <c r="H346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -13276,11 +13208,7 @@
           <t>Belgica</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+      <c r="H347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -13314,11 +13242,7 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
+      <c r="H348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -13352,7 +13276,11 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentina </t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -13386,11 +13314,7 @@
           <t xml:space="preserve">España </t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+      <c r="H350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -13424,11 +13348,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="H351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13462,11 +13382,7 @@
           <t>Brasil</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
+      <c r="H352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -13500,11 +13416,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="H353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -21851,14 +21763,22 @@
           <t>Alemania</t>
         </is>
       </c>
-      <c r="E574" t="inlineStr"/>
-      <c r="F574" t="inlineStr"/>
+      <c r="E574" t="n">
+        <v>1</v>
+      </c>
+      <c r="F574" t="n">
+        <v>2</v>
+      </c>
       <c r="G574" t="inlineStr">
         <is>
           <t>España</t>
         </is>
       </c>
-      <c r="H574" t="inlineStr"/>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -21881,14 +21801,22 @@
           <t>Brasil</t>
         </is>
       </c>
-      <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
+      <c r="E575" t="n">
+        <v>1</v>
+      </c>
+      <c r="F575" t="n">
+        <v>2</v>
+      </c>
       <c r="G575" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H575" t="inlineStr"/>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -21908,7 +21836,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Perdedor Partido 29</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="E576" t="inlineStr"/>
@@ -23198,11 +23126,7 @@
           <t>Canadá</t>
         </is>
       </c>
-      <c r="H610" t="inlineStr">
-        <is>
-          <t>Canadá</t>
-        </is>
-      </c>
+      <c r="H610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -23236,11 +23160,7 @@
           <t>Marruecos</t>
         </is>
       </c>
-      <c r="H611" t="inlineStr">
-        <is>
-          <t>Paises Bajos</t>
-        </is>
-      </c>
+      <c r="H611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -23274,11 +23194,7 @@
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="H612" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
+      <c r="H612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -23312,11 +23228,7 @@
           <t>Japón</t>
         </is>
       </c>
-      <c r="H613" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
+      <c r="H613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -23350,11 +23262,7 @@
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="H614" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="H614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -23388,11 +23296,7 @@
           <t>Argelia</t>
         </is>
       </c>
-      <c r="H615" t="inlineStr">
-        <is>
-          <t>Suiza</t>
-        </is>
-      </c>
+      <c r="H615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -23426,11 +23330,7 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="H616" t="inlineStr">
-        <is>
-          <t>Egipto</t>
-        </is>
-      </c>
+      <c r="H616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -23464,7 +23364,11 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="H617" t="inlineStr"/>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecuador </t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -23498,11 +23402,7 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="H618" t="inlineStr">
-        <is>
-          <t>Noruega</t>
-        </is>
-      </c>
+      <c r="H618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -23536,11 +23436,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr">
-        <is>
-          <t>Alemania</t>
-        </is>
-      </c>
+      <c r="H619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -23574,11 +23470,7 @@
           <t>Suecia</t>
         </is>
       </c>
-      <c r="H620" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+      <c r="H620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -23612,11 +23504,7 @@
           <t>Croacia</t>
         </is>
       </c>
-      <c r="H621" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
+      <c r="H621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -23650,11 +23538,7 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="H622" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+      <c r="H622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -23688,11 +23572,7 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="H623" t="inlineStr">
-        <is>
-          <t>Bélgica</t>
-        </is>
-      </c>
+      <c r="H623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -23726,11 +23606,7 @@
           <t>Congo</t>
         </is>
       </c>
-      <c r="H624" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+      <c r="H624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -23764,11 +23640,7 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="H625" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
+      <c r="H625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -23788,7 +23660,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Sudáfrica/Canadá</t>
         </is>
       </c>
       <c r="E626" t="n">
@@ -23799,14 +23671,10 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Paises Bajos</t>
-        </is>
-      </c>
-      <c r="H626" t="inlineStr">
-        <is>
-          <t>Paises Bajos</t>
-        </is>
-      </c>
+          <t>Paises Bajos/Marruecos</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -23826,7 +23694,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA/Bosnia &amp; Herzegovina</t>
         </is>
       </c>
       <c r="E627" t="n">
@@ -23837,14 +23705,10 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Bélgica</t>
-        </is>
-      </c>
-      <c r="H627" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
+          <t>Belgica/Senegal</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -23864,7 +23728,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Brasil/Japón</t>
         </is>
       </c>
       <c r="E628" t="n">
@@ -23875,14 +23739,10 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Noruega</t>
-        </is>
-      </c>
-      <c r="H628" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
+          <t>Costa de Marfil/Noruega</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -23902,7 +23762,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Argentina/Cabo Verde</t>
         </is>
       </c>
       <c r="E629" t="n">
@@ -23913,14 +23773,10 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>Egipto</t>
-        </is>
-      </c>
-      <c r="H629" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+          <t>Australia/Egipto</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -23940,7 +23796,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Suiza/Argelia</t>
         </is>
       </c>
       <c r="E630" t="n">
@@ -23951,14 +23807,10 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H630" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
+          <t>Colombia/Ghana</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -23989,14 +23841,10 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="H631" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
+          <t>Inglaterra/Congo</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -24016,7 +23864,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Portugal/Croacia</t>
         </is>
       </c>
       <c r="E632" t="n">
@@ -24027,14 +23875,10 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t xml:space="preserve">España </t>
-        </is>
-      </c>
-      <c r="H632" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+          <t>España Austria</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -24054,7 +23898,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Alemania/Paraguay</t>
         </is>
       </c>
       <c r="E633" t="n">
@@ -24065,14 +23909,10 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Francia</t>
-        </is>
-      </c>
-      <c r="H633" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+          <t>Francia/Suecia</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -24106,11 +23946,7 @@
           <t>Paises Bajos</t>
         </is>
       </c>
-      <c r="H634" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+      <c r="H634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -24144,11 +23980,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+      <c r="H635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -24182,11 +24014,7 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
+      <c r="H636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -24220,11 +24048,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="H637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -24258,11 +24082,7 @@
           <t xml:space="preserve">España </t>
         </is>
       </c>
-      <c r="H638" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
+      <c r="H638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -24296,11 +24116,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H639" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="H639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -24334,11 +24150,7 @@
           <t>Brasil</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+      <c r="H640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -24372,7 +24184,11 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr"/>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentina </t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">

--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3976" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="167">
   <si>
     <t>Participante</t>
   </si>
@@ -498,9 +498,6 @@
     <t>Walter Rojas</t>
   </si>
   <si>
-    <t xml:space="preserve">Canadá </t>
-  </si>
-  <si>
     <t xml:space="preserve">Países bajos </t>
   </si>
   <si>
@@ -9051,7 +9048,7 @@
         <v>21</v>
       </c>
       <c r="H325" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
@@ -9753,7 +9750,7 @@
         <v>20</v>
       </c>
       <c r="H352" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
@@ -11417,7 +11414,7 @@
         <v>56</v>
       </c>
       <c r="H416" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
@@ -15601,17 +15598,8 @@
       <c r="D578" t="s">
         <v>11</v>
       </c>
-      <c r="E578">
-        <v>0</v>
-      </c>
-      <c r="F578">
-        <v>1</v>
-      </c>
       <c r="G578" t="s">
         <v>12</v>
-      </c>
-      <c r="H578" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
@@ -15637,7 +15625,7 @@
         <v>15</v>
       </c>
       <c r="H579" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
@@ -15663,7 +15651,7 @@
         <v>18</v>
       </c>
       <c r="H580" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
@@ -15689,7 +15677,7 @@
         <v>21</v>
       </c>
       <c r="H581" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
@@ -15897,7 +15885,7 @@
         <v>45</v>
       </c>
       <c r="H589" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
@@ -16024,10 +16012,10 @@
         <v>2</v>
       </c>
       <c r="G594" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H594" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
@@ -16232,7 +16220,7 @@
         <v>1</v>
       </c>
       <c r="G602" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H602" t="s">
         <v>89</v>
@@ -16422,7 +16410,7 @@
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B610" t="s">
         <v>9</v>
@@ -16448,7 +16436,7 @@
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B611" t="s">
         <v>9</v>
@@ -16474,7 +16462,7 @@
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B612" t="s">
         <v>9</v>
@@ -16500,7 +16488,7 @@
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B613" t="s">
         <v>9</v>
@@ -16526,7 +16514,7 @@
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B614" t="s">
         <v>9</v>
@@ -16552,7 +16540,7 @@
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B615" t="s">
         <v>9</v>
@@ -16578,7 +16566,7 @@
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B616" t="s">
         <v>9</v>
@@ -16604,7 +16592,7 @@
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B617" t="s">
         <v>9</v>
@@ -16630,7 +16618,7 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B618" t="s">
         <v>9</v>
@@ -16656,7 +16644,7 @@
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B619" t="s">
         <v>9</v>
@@ -16682,7 +16670,7 @@
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B620" t="s">
         <v>9</v>
@@ -16708,7 +16696,7 @@
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B621" t="s">
         <v>9</v>
@@ -16734,7 +16722,7 @@
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B622" t="s">
         <v>9</v>
@@ -16760,7 +16748,7 @@
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B623" t="s">
         <v>9</v>
@@ -16786,7 +16774,7 @@
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B624" t="s">
         <v>9</v>
@@ -16812,7 +16800,7 @@
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -16838,7 +16826,7 @@
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B626" t="s">
         <v>58</v>
@@ -16864,7 +16852,7 @@
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B627" t="s">
         <v>58</v>
@@ -16885,12 +16873,12 @@
         <v>50</v>
       </c>
       <c r="H627" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B628" t="s">
         <v>58</v>
@@ -16916,7 +16904,7 @@
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B629" t="s">
         <v>58</v>
@@ -16942,7 +16930,7 @@
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B630" t="s">
         <v>58</v>
@@ -16968,7 +16956,7 @@
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B631" t="s">
         <v>58</v>
@@ -16994,7 +16982,7 @@
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B632" t="s">
         <v>58</v>
@@ -17020,7 +17008,7 @@
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B633" t="s">
         <v>58</v>
@@ -17046,7 +17034,7 @@
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B634" t="s">
         <v>67</v>
@@ -17072,7 +17060,7 @@
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B635" t="s">
         <v>67</v>
@@ -17098,7 +17086,7 @@
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B636" t="s">
         <v>67</v>
@@ -17124,7 +17112,7 @@
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B637" t="s">
         <v>67</v>
@@ -17150,7 +17138,7 @@
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B638" t="s">
         <v>72</v>
@@ -17176,7 +17164,7 @@
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B639" t="s">
         <v>72</v>
@@ -17202,7 +17190,7 @@
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B640" t="s">
         <v>75</v>
@@ -17228,7 +17216,7 @@
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B641" t="s">
         <v>77</v>
@@ -17254,7 +17242,7 @@
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B642" t="s">
         <v>9</v>
@@ -17280,7 +17268,7 @@
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B643" t="s">
         <v>9</v>
@@ -17306,7 +17294,7 @@
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B644" t="s">
         <v>9</v>
@@ -17332,7 +17320,7 @@
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B645" t="s">
         <v>9</v>
@@ -17358,7 +17346,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B646" t="s">
         <v>9</v>
@@ -17384,7 +17372,7 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B647" t="s">
         <v>9</v>
@@ -17410,7 +17398,7 @@
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B648" t="s">
         <v>9</v>
@@ -17436,7 +17424,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B649" t="s">
         <v>9</v>
@@ -17462,7 +17450,7 @@
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B650" t="s">
         <v>9</v>
@@ -17488,7 +17476,7 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B651" t="s">
         <v>9</v>
@@ -17514,7 +17502,7 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B652" t="s">
         <v>9</v>
@@ -17540,7 +17528,7 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B653" t="s">
         <v>9</v>
@@ -17566,7 +17554,7 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B654" t="s">
         <v>9</v>
@@ -17592,7 +17580,7 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B655" t="s">
         <v>9</v>
@@ -17618,7 +17606,7 @@
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B656" t="s">
         <v>9</v>
@@ -17644,7 +17632,7 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B657" t="s">
         <v>9</v>
@@ -17670,7 +17658,7 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B658" t="s">
         <v>58</v>
@@ -17696,7 +17684,7 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B659" t="s">
         <v>58</v>
@@ -17722,7 +17710,7 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B660" t="s">
         <v>58</v>
@@ -17748,7 +17736,7 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B661" t="s">
         <v>58</v>
@@ -17774,7 +17762,7 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B662" t="s">
         <v>58</v>
@@ -17800,7 +17788,7 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B663" t="s">
         <v>58</v>
@@ -17826,7 +17814,7 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B664" t="s">
         <v>58</v>
@@ -17852,7 +17840,7 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B665" t="s">
         <v>58</v>
@@ -17878,7 +17866,7 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B666" t="s">
         <v>67</v>
@@ -17904,7 +17892,7 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B667" t="s">
         <v>67</v>
@@ -17930,7 +17918,7 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B668" t="s">
         <v>67</v>
@@ -17956,7 +17944,7 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B669" t="s">
         <v>67</v>
@@ -17982,7 +17970,7 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B670" t="s">
         <v>72</v>
@@ -18008,7 +17996,7 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B671" t="s">
         <v>72</v>
@@ -18017,7 +18005,7 @@
         <v>74</v>
       </c>
       <c r="D671" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E671">
         <v>2</v>
@@ -18034,7 +18022,7 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B672" t="s">
         <v>75</v>
@@ -18052,7 +18040,7 @@
         <v>1</v>
       </c>
       <c r="G672" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H672" t="s">
         <v>20</v>
@@ -18060,7 +18048,7 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B673" t="s">
         <v>77</v>

--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4167" uniqueCount="168">
   <si>
     <t>Participante</t>
   </si>
@@ -521,6 +521,9 @@
   <si>
     <t>ESpaña</t>
   </si>
+  <si>
+    <t>Luis Torres</t>
+  </si>
 </sst>
 </file>
 
@@ -882,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H705"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -9781,7 +9784,7 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B354" t="s">
         <v>9</v>
@@ -9793,21 +9796,21 @@
         <v>11</v>
       </c>
       <c r="E354">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G354" t="s">
         <v>12</v>
       </c>
       <c r="H354" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B355" t="s">
         <v>9</v>
@@ -9819,21 +9822,21 @@
         <v>14</v>
       </c>
       <c r="E355">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F355">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G355" t="s">
         <v>15</v>
       </c>
       <c r="H355" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B356" t="s">
         <v>9</v>
@@ -9848,7 +9851,7 @@
         <v>2</v>
       </c>
       <c r="F356">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G356" t="s">
         <v>18</v>
@@ -9859,7 +9862,7 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B357" t="s">
         <v>9</v>
@@ -9885,7 +9888,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B358" t="s">
         <v>9</v>
@@ -9897,7 +9900,7 @@
         <v>23</v>
       </c>
       <c r="E358">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F358">
         <v>0</v>
@@ -9911,7 +9914,7 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B359" t="s">
         <v>9</v>
@@ -9923,7 +9926,7 @@
         <v>26</v>
       </c>
       <c r="E359">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F359">
         <v>1</v>
@@ -9937,7 +9940,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B360" t="s">
         <v>9</v>
@@ -9949,10 +9952,10 @@
         <v>29</v>
       </c>
       <c r="E360">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F360">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G360" t="s">
         <v>30</v>
@@ -9963,7 +9966,7 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B361" t="s">
         <v>9</v>
@@ -9975,21 +9978,21 @@
         <v>32</v>
       </c>
       <c r="E361">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F361">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G361" t="s">
         <v>33</v>
       </c>
       <c r="H361" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B362" t="s">
         <v>9</v>
@@ -10015,7 +10018,7 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B363" t="s">
         <v>9</v>
@@ -10027,10 +10030,10 @@
         <v>38</v>
       </c>
       <c r="E363">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G363" t="s">
         <v>39</v>
@@ -10041,7 +10044,7 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B364" t="s">
         <v>9</v>
@@ -10053,10 +10056,10 @@
         <v>41</v>
       </c>
       <c r="E364">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F364">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="s">
         <v>42</v>
@@ -10067,7 +10070,7 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B365" t="s">
         <v>9</v>
@@ -10079,7 +10082,7 @@
         <v>44</v>
       </c>
       <c r="E365">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F365">
         <v>1</v>
@@ -10093,7 +10096,7 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B366" t="s">
         <v>9</v>
@@ -10105,10 +10108,10 @@
         <v>47</v>
       </c>
       <c r="E366">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G366" t="s">
         <v>48</v>
@@ -10119,7 +10122,7 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B367" t="s">
         <v>9</v>
@@ -10131,7 +10134,7 @@
         <v>50</v>
       </c>
       <c r="E367">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F367">
         <v>1</v>
@@ -10145,7 +10148,7 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B368" t="s">
         <v>9</v>
@@ -10157,7 +10160,7 @@
         <v>53</v>
       </c>
       <c r="E368">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F368">
         <v>0</v>
@@ -10171,7 +10174,7 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B369" t="s">
         <v>9</v>
@@ -10197,7 +10200,7 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B370" t="s">
         <v>58</v>
@@ -10215,15 +10218,15 @@
         <v>2</v>
       </c>
       <c r="G370" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H370" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B371" t="s">
         <v>58</v>
@@ -10238,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="F371">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G371" t="s">
         <v>50</v>
@@ -10249,7 +10252,7 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B372" t="s">
         <v>58</v>
@@ -10264,7 +10267,7 @@
         <v>2</v>
       </c>
       <c r="F372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G372" t="s">
         <v>36</v>
@@ -10275,7 +10278,7 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B373" t="s">
         <v>58</v>
@@ -10287,10 +10290,10 @@
         <v>23</v>
       </c>
       <c r="E373">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F373">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G373" t="s">
         <v>30</v>
@@ -10301,7 +10304,7 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B374" t="s">
         <v>58</v>
@@ -10313,10 +10316,10 @@
         <v>26</v>
       </c>
       <c r="E374">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F374">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G374" t="s">
         <v>56</v>
@@ -10327,7 +10330,7 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B375" t="s">
         <v>58</v>
@@ -10336,7 +10339,7 @@
         <v>64</v>
       </c>
       <c r="D375" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E375">
         <v>1</v>
@@ -10353,7 +10356,7 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B376" t="s">
         <v>58</v>
@@ -10365,13 +10368,13 @@
         <v>44</v>
       </c>
       <c r="E376">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F376">
         <v>2</v>
       </c>
       <c r="G376" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="H376" t="s">
         <v>47</v>
@@ -10379,7 +10382,7 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B377" t="s">
         <v>58</v>
@@ -10394,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="F377">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G377" t="s">
         <v>41</v>
@@ -10405,7 +10408,7 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B378" t="s">
         <v>67</v>
@@ -10423,7 +10426,7 @@
         <v>1</v>
       </c>
       <c r="G378" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H378" t="s">
         <v>41</v>
@@ -10431,7 +10434,7 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B379" t="s">
         <v>67</v>
@@ -10446,7 +10449,7 @@
         <v>2</v>
       </c>
       <c r="F379">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G379" t="s">
         <v>50</v>
@@ -10457,7 +10460,7 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B380" t="s">
         <v>67</v>
@@ -10472,7 +10475,7 @@
         <v>1</v>
       </c>
       <c r="F380">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G380" t="s">
         <v>53</v>
@@ -10483,7 +10486,7 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B381" t="s">
         <v>67</v>
@@ -10495,21 +10498,21 @@
         <v>23</v>
       </c>
       <c r="E381">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F381">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G381" t="s">
         <v>56</v>
       </c>
       <c r="H381" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B382" t="s">
         <v>72</v>
@@ -10527,7 +10530,7 @@
         <v>1</v>
       </c>
       <c r="G382" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="H382" t="s">
         <v>41</v>
@@ -10535,7 +10538,7 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B383" t="s">
         <v>72</v>
@@ -10547,21 +10550,21 @@
         <v>53</v>
       </c>
       <c r="E383">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F383">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G383" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H383" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B384" t="s">
         <v>75</v>
@@ -10573,21 +10576,21 @@
         <v>47</v>
       </c>
       <c r="E384">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F384">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G384" t="s">
         <v>53</v>
       </c>
       <c r="H384" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B385" t="s">
         <v>77</v>
@@ -10599,21 +10602,21 @@
         <v>41</v>
       </c>
       <c r="E385">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F385">
         <v>1</v>
       </c>
       <c r="G385" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H385" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B386" t="s">
         <v>9</v>
@@ -10625,21 +10628,21 @@
         <v>11</v>
       </c>
       <c r="E386">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F386">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G386" t="s">
         <v>12</v>
       </c>
       <c r="H386" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B387" t="s">
         <v>9</v>
@@ -10651,21 +10654,21 @@
         <v>14</v>
       </c>
       <c r="E387">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F387">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G387" t="s">
         <v>15</v>
       </c>
       <c r="H387" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B388" t="s">
         <v>9</v>
@@ -10680,7 +10683,7 @@
         <v>2</v>
       </c>
       <c r="F388">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G388" t="s">
         <v>18</v>
@@ -10691,7 +10694,7 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B389" t="s">
         <v>9</v>
@@ -10717,7 +10720,7 @@
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B390" t="s">
         <v>9</v>
@@ -10729,7 +10732,7 @@
         <v>23</v>
       </c>
       <c r="E390">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F390">
         <v>0</v>
@@ -10743,7 +10746,7 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B391" t="s">
         <v>9</v>
@@ -10769,7 +10772,7 @@
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B392" t="s">
         <v>9</v>
@@ -10784,7 +10787,7 @@
         <v>1</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G392" t="s">
         <v>30</v>
@@ -10795,7 +10798,7 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B393" t="s">
         <v>9</v>
@@ -10807,21 +10810,21 @@
         <v>32</v>
       </c>
       <c r="E393">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F393">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G393" t="s">
         <v>33</v>
       </c>
       <c r="H393" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B394" t="s">
         <v>9</v>
@@ -10847,7 +10850,7 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B395" t="s">
         <v>9</v>
@@ -10859,7 +10862,7 @@
         <v>38</v>
       </c>
       <c r="E395">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F395">
         <v>1</v>
@@ -10873,7 +10876,7 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B396" t="s">
         <v>9</v>
@@ -10888,7 +10891,7 @@
         <v>3</v>
       </c>
       <c r="F396">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G396" t="s">
         <v>42</v>
@@ -10899,7 +10902,7 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B397" t="s">
         <v>9</v>
@@ -10914,7 +10917,7 @@
         <v>1</v>
       </c>
       <c r="F397">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G397" t="s">
         <v>45</v>
@@ -10925,7 +10928,7 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B398" t="s">
         <v>9</v>
@@ -10940,7 +10943,7 @@
         <v>3</v>
       </c>
       <c r="F398">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G398" t="s">
         <v>48</v>
@@ -10951,7 +10954,7 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B399" t="s">
         <v>9</v>
@@ -10966,18 +10969,18 @@
         <v>1</v>
       </c>
       <c r="F399">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G399" t="s">
         <v>51</v>
       </c>
       <c r="H399" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B400" t="s">
         <v>9</v>
@@ -11003,7 +11006,7 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B401" t="s">
         <v>9</v>
@@ -11029,7 +11032,7 @@
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B402" t="s">
         <v>58</v>
@@ -11047,15 +11050,15 @@
         <v>2</v>
       </c>
       <c r="G402" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H402" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B403" t="s">
         <v>58</v>
@@ -11073,7 +11076,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H403" t="s">
         <v>50</v>
@@ -11081,7 +11084,7 @@
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B404" t="s">
         <v>58</v>
@@ -11107,7 +11110,7 @@
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B405" t="s">
         <v>58</v>
@@ -11119,10 +11122,10 @@
         <v>23</v>
       </c>
       <c r="E405">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F405">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G405" t="s">
         <v>30</v>
@@ -11133,7 +11136,7 @@
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B406" t="s">
         <v>58</v>
@@ -11159,7 +11162,7 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B407" t="s">
         <v>58</v>
@@ -11168,13 +11171,13 @@
         <v>64</v>
       </c>
       <c r="D407" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E407">
         <v>1</v>
       </c>
       <c r="F407">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G407" t="s">
         <v>53</v>
@@ -11185,7 +11188,7 @@
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B408" t="s">
         <v>58</v>
@@ -11197,13 +11200,13 @@
         <v>44</v>
       </c>
       <c r="E408">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F408">
         <v>2</v>
       </c>
       <c r="G408" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="H408" t="s">
         <v>47</v>
@@ -11211,7 +11214,7 @@
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B409" t="s">
         <v>58</v>
@@ -11226,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="F409">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G409" t="s">
         <v>41</v>
@@ -11237,7 +11240,7 @@
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B410" t="s">
         <v>67</v>
@@ -11255,7 +11258,7 @@
         <v>1</v>
       </c>
       <c r="G410" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H410" t="s">
         <v>41</v>
@@ -11263,7 +11266,7 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B411" t="s">
         <v>67</v>
@@ -11289,7 +11292,7 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B412" t="s">
         <v>67</v>
@@ -11301,21 +11304,21 @@
         <v>20</v>
       </c>
       <c r="E412">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F412">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G412" t="s">
         <v>53</v>
       </c>
       <c r="H412" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B413" t="s">
         <v>67</v>
@@ -11330,7 +11333,7 @@
         <v>1</v>
       </c>
       <c r="F413">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G413" t="s">
         <v>56</v>
@@ -11341,7 +11344,7 @@
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B414" t="s">
         <v>72</v>
@@ -11359,7 +11362,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="H414" t="s">
         <v>41</v>
@@ -11367,7 +11370,7 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B415" t="s">
         <v>72</v>
@@ -11376,24 +11379,24 @@
         <v>74</v>
       </c>
       <c r="D415" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E415">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F415">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G415" t="s">
         <v>56</v>
       </c>
       <c r="H415" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B416" t="s">
         <v>75</v>
@@ -11405,21 +11408,21 @@
         <v>47</v>
       </c>
       <c r="E416">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F416">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G416" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H416" t="s">
-        <v>166</v>
+        <v>53</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B417" t="s">
         <v>77</v>
@@ -11437,7 +11440,7 @@
         <v>1</v>
       </c>
       <c r="G417" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="H417" t="s">
         <v>41</v>
@@ -11445,7 +11448,7 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B418" t="s">
         <v>9</v>
@@ -11471,7 +11474,7 @@
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B419" t="s">
         <v>9</v>
@@ -11492,12 +11495,12 @@
         <v>15</v>
       </c>
       <c r="H419" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B420" t="s">
         <v>9</v>
@@ -11509,10 +11512,10 @@
         <v>17</v>
       </c>
       <c r="E420">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F420">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G420" t="s">
         <v>18</v>
@@ -11523,7 +11526,7 @@
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B421" t="s">
         <v>9</v>
@@ -11535,7 +11538,7 @@
         <v>20</v>
       </c>
       <c r="E421">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F421">
         <v>1</v>
@@ -11549,7 +11552,7 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B422" t="s">
         <v>9</v>
@@ -11561,7 +11564,7 @@
         <v>23</v>
       </c>
       <c r="E422">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F422">
         <v>0</v>
@@ -11575,7 +11578,7 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B423" t="s">
         <v>9</v>
@@ -11601,7 +11604,7 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B424" t="s">
         <v>9</v>
@@ -11613,10 +11616,10 @@
         <v>29</v>
       </c>
       <c r="E424">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F424">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G424" t="s">
         <v>30</v>
@@ -11627,7 +11630,7 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B425" t="s">
         <v>9</v>
@@ -11642,7 +11645,7 @@
         <v>2</v>
       </c>
       <c r="F425">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G425" t="s">
         <v>33</v>
@@ -11653,7 +11656,7 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B426" t="s">
         <v>9</v>
@@ -11668,7 +11671,7 @@
         <v>1</v>
       </c>
       <c r="F426">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G426" t="s">
         <v>36</v>
@@ -11679,7 +11682,7 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B427" t="s">
         <v>9</v>
@@ -11691,10 +11694,10 @@
         <v>38</v>
       </c>
       <c r="E427">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F427">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G427" t="s">
         <v>39</v>
@@ -11705,7 +11708,7 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B428" t="s">
         <v>9</v>
@@ -11720,7 +11723,7 @@
         <v>3</v>
       </c>
       <c r="F428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G428" t="s">
         <v>42</v>
@@ -11731,7 +11734,7 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B429" t="s">
         <v>9</v>
@@ -11743,10 +11746,10 @@
         <v>44</v>
       </c>
       <c r="E429">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F429">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G429" t="s">
         <v>45</v>
@@ -11757,7 +11760,7 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B430" t="s">
         <v>9</v>
@@ -11783,7 +11786,7 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B431" t="s">
         <v>9</v>
@@ -11795,10 +11798,10 @@
         <v>50</v>
       </c>
       <c r="E431">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F431">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G431" t="s">
         <v>51</v>
@@ -11809,7 +11812,7 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B432" t="s">
         <v>9</v>
@@ -11821,10 +11824,10 @@
         <v>53</v>
       </c>
       <c r="E432">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F432">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G432" t="s">
         <v>54</v>
@@ -11835,7 +11838,7 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B433" t="s">
         <v>9</v>
@@ -11861,7 +11864,7 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B434" t="s">
         <v>58</v>
@@ -11876,18 +11879,18 @@
         <v>1</v>
       </c>
       <c r="F434">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G434" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="H434" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B435" t="s">
         <v>58</v>
@@ -11902,18 +11905,18 @@
         <v>1</v>
       </c>
       <c r="F435">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G435" t="s">
         <v>80</v>
       </c>
       <c r="H435" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B436" t="s">
         <v>58</v>
@@ -11939,7 +11942,7 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B437" t="s">
         <v>58</v>
@@ -11954,7 +11957,7 @@
         <v>2</v>
       </c>
       <c r="F437">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G437" t="s">
         <v>30</v>
@@ -11965,7 +11968,7 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B438" t="s">
         <v>58</v>
@@ -11991,7 +11994,7 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B439" t="s">
         <v>58</v>
@@ -12000,13 +12003,13 @@
         <v>64</v>
       </c>
       <c r="D439" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="E439">
         <v>1</v>
       </c>
       <c r="F439">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G439" t="s">
         <v>53</v>
@@ -12017,7 +12020,7 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B440" t="s">
         <v>58</v>
@@ -12032,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="F440">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G440" t="s">
         <v>47</v>
@@ -12043,7 +12046,7 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B441" t="s">
         <v>58</v>
@@ -12055,7 +12058,7 @@
         <v>38</v>
       </c>
       <c r="E441">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F441">
         <v>2</v>
@@ -12069,7 +12072,7 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B442" t="s">
         <v>67</v>
@@ -12084,10 +12087,10 @@
         <v>2</v>
       </c>
       <c r="F442">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G442" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="H442" t="s">
         <v>41</v>
@@ -12095,7 +12098,7 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B443" t="s">
         <v>67</v>
@@ -12110,10 +12113,10 @@
         <v>2</v>
       </c>
       <c r="F443">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G443" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H443" t="s">
         <v>47</v>
@@ -12121,7 +12124,7 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B444" t="s">
         <v>67</v>
@@ -12133,21 +12136,21 @@
         <v>20</v>
       </c>
       <c r="E444">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F444">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G444" t="s">
         <v>53</v>
       </c>
       <c r="H444" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B445" t="s">
         <v>67</v>
@@ -12168,12 +12171,12 @@
         <v>56</v>
       </c>
       <c r="H445" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B446" t="s">
         <v>72</v>
@@ -12185,21 +12188,21 @@
         <v>41</v>
       </c>
       <c r="E446">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F446">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G446" t="s">
         <v>47</v>
       </c>
       <c r="H446" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B447" t="s">
         <v>72</v>
@@ -12208,7 +12211,7 @@
         <v>74</v>
       </c>
       <c r="D447" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E447">
         <v>2</v>
@@ -12217,15 +12220,15 @@
         <v>1</v>
       </c>
       <c r="G447" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H447" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B448" t="s">
         <v>75</v>
@@ -12234,24 +12237,24 @@
         <v>76</v>
       </c>
       <c r="D448" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E448">
         <v>2</v>
       </c>
       <c r="F448">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G448" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H448" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B449" t="s">
         <v>77</v>
@@ -12260,7 +12263,7 @@
         <v>78</v>
       </c>
       <c r="D449" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E449">
         <v>2</v>
@@ -12269,15 +12272,15 @@
         <v>1</v>
       </c>
       <c r="G449" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="H449" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B450" t="s">
         <v>9</v>
@@ -12303,7 +12306,7 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B451" t="s">
         <v>9</v>
@@ -12315,7 +12318,7 @@
         <v>14</v>
       </c>
       <c r="E451">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F451">
         <v>1</v>
@@ -12324,12 +12327,12 @@
         <v>15</v>
       </c>
       <c r="H451" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B452" t="s">
         <v>9</v>
@@ -12341,7 +12344,7 @@
         <v>17</v>
       </c>
       <c r="E452">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F452">
         <v>1</v>
@@ -12355,7 +12358,7 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B453" t="s">
         <v>9</v>
@@ -12367,7 +12370,7 @@
         <v>20</v>
       </c>
       <c r="E453">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F453">
         <v>1</v>
@@ -12381,7 +12384,7 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B454" t="s">
         <v>9</v>
@@ -12393,10 +12396,10 @@
         <v>23</v>
       </c>
       <c r="E454">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F454">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G454" t="s">
         <v>24</v>
@@ -12407,7 +12410,7 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B455" t="s">
         <v>9</v>
@@ -12419,7 +12422,7 @@
         <v>26</v>
       </c>
       <c r="E455">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F455">
         <v>1</v>
@@ -12433,7 +12436,7 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B456" t="s">
         <v>9</v>
@@ -12448,7 +12451,7 @@
         <v>0</v>
       </c>
       <c r="F456">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G456" t="s">
         <v>30</v>
@@ -12459,7 +12462,7 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B457" t="s">
         <v>9</v>
@@ -12474,7 +12477,7 @@
         <v>2</v>
       </c>
       <c r="F457">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G457" t="s">
         <v>33</v>
@@ -12485,7 +12488,7 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B458" t="s">
         <v>9</v>
@@ -12500,7 +12503,7 @@
         <v>1</v>
       </c>
       <c r="F458">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G458" t="s">
         <v>36</v>
@@ -12511,7 +12514,7 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B459" t="s">
         <v>9</v>
@@ -12526,7 +12529,7 @@
         <v>2</v>
       </c>
       <c r="F459">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G459" t="s">
         <v>39</v>
@@ -12537,7 +12540,7 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B460" t="s">
         <v>9</v>
@@ -12549,10 +12552,10 @@
         <v>41</v>
       </c>
       <c r="E460">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F460">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G460" t="s">
         <v>42</v>
@@ -12563,7 +12566,7 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B461" t="s">
         <v>9</v>
@@ -12575,21 +12578,21 @@
         <v>44</v>
       </c>
       <c r="E461">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F461">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G461" t="s">
         <v>45</v>
       </c>
       <c r="H461" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B462" t="s">
         <v>9</v>
@@ -12601,10 +12604,10 @@
         <v>47</v>
       </c>
       <c r="E462">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F462">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G462" t="s">
         <v>48</v>
@@ -12615,7 +12618,7 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B463" t="s">
         <v>9</v>
@@ -12627,21 +12630,21 @@
         <v>50</v>
       </c>
       <c r="E463">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F463">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G463" t="s">
         <v>51</v>
       </c>
       <c r="H463" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B464" t="s">
         <v>9</v>
@@ -12653,10 +12656,10 @@
         <v>53</v>
       </c>
       <c r="E464">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F464">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G464" t="s">
         <v>54</v>
@@ -12667,7 +12670,7 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B465" t="s">
         <v>9</v>
@@ -12693,7 +12696,7 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B466" t="s">
         <v>58</v>
@@ -12708,18 +12711,18 @@
         <v>1</v>
       </c>
       <c r="F466">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G466" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="H466" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B467" t="s">
         <v>58</v>
@@ -12737,15 +12740,15 @@
         <v>2</v>
       </c>
       <c r="G467" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="H467" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B468" t="s">
         <v>58</v>
@@ -12771,7 +12774,7 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B469" t="s">
         <v>58</v>
@@ -12786,7 +12789,7 @@
         <v>2</v>
       </c>
       <c r="F469">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G469" t="s">
         <v>30</v>
@@ -12797,7 +12800,7 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B470" t="s">
         <v>58</v>
@@ -12809,7 +12812,7 @@
         <v>26</v>
       </c>
       <c r="E470">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F470">
         <v>2</v>
@@ -12823,7 +12826,7 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B471" t="s">
         <v>58</v>
@@ -12832,7 +12835,7 @@
         <v>64</v>
       </c>
       <c r="D471" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="E471">
         <v>1</v>
@@ -12849,7 +12852,7 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B472" t="s">
         <v>58</v>
@@ -12858,13 +12861,13 @@
         <v>65</v>
       </c>
       <c r="D472" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E472">
         <v>1</v>
       </c>
       <c r="F472">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G472" t="s">
         <v>47</v>
@@ -12875,7 +12878,7 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B473" t="s">
         <v>58</v>
@@ -12887,7 +12890,7 @@
         <v>38</v>
       </c>
       <c r="E473">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F473">
         <v>2</v>
@@ -12901,7 +12904,7 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B474" t="s">
         <v>67</v>
@@ -12916,10 +12919,10 @@
         <v>2</v>
       </c>
       <c r="F474">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G474" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="H474" t="s">
         <v>41</v>
@@ -12927,7 +12930,7 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B475" t="s">
         <v>67</v>
@@ -12939,13 +12942,13 @@
         <v>47</v>
       </c>
       <c r="E475">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F475">
         <v>1</v>
       </c>
       <c r="G475" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="H475" t="s">
         <v>47</v>
@@ -12953,7 +12956,7 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B476" t="s">
         <v>67</v>
@@ -12965,21 +12968,21 @@
         <v>20</v>
       </c>
       <c r="E476">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F476">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G476" t="s">
         <v>53</v>
       </c>
       <c r="H476" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B477" t="s">
         <v>67</v>
@@ -12991,7 +12994,7 @@
         <v>23</v>
       </c>
       <c r="E477">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F477">
         <v>1</v>
@@ -13005,10 +13008,10 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B478" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C478" t="s">
         <v>73</v>
@@ -13017,47 +13020,47 @@
         <v>41</v>
       </c>
       <c r="E478">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F478">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G478" t="s">
         <v>47</v>
       </c>
       <c r="H478" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B479" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C479" t="s">
         <v>74</v>
       </c>
       <c r="D479" t="s">
+        <v>53</v>
+      </c>
+      <c r="E479">
+        <v>2</v>
+      </c>
+      <c r="F479">
+        <v>1</v>
+      </c>
+      <c r="G479" t="s">
         <v>23</v>
       </c>
-      <c r="E479">
-        <v>2</v>
-      </c>
-      <c r="F479">
-        <v>1</v>
-      </c>
-      <c r="G479" t="s">
-        <v>20</v>
-      </c>
       <c r="H479" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B480" t="s">
         <v>75</v>
@@ -13066,7 +13069,7 @@
         <v>76</v>
       </c>
       <c r="D480" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E480">
         <v>2</v>
@@ -13075,15 +13078,15 @@
         <v>1</v>
       </c>
       <c r="G480" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H480" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B481" t="s">
         <v>77</v>
@@ -13092,7 +13095,7 @@
         <v>78</v>
       </c>
       <c r="D481" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E481">
         <v>2</v>
@@ -13101,15 +13104,15 @@
         <v>1</v>
       </c>
       <c r="G481" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="H481" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B482" t="s">
         <v>9</v>
@@ -13135,7 +13138,7 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B483" t="s">
         <v>9</v>
@@ -13147,10 +13150,10 @@
         <v>14</v>
       </c>
       <c r="E483">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F483">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G483" t="s">
         <v>15</v>
@@ -13161,7 +13164,7 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B484" t="s">
         <v>9</v>
@@ -13187,7 +13190,7 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B485" t="s">
         <v>9</v>
@@ -13199,21 +13202,21 @@
         <v>20</v>
       </c>
       <c r="E485">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F485">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G485" t="s">
         <v>21</v>
       </c>
       <c r="H485" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B486" t="s">
         <v>9</v>
@@ -13228,7 +13231,7 @@
         <v>3</v>
       </c>
       <c r="F486">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G486" t="s">
         <v>24</v>
@@ -13239,7 +13242,7 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B487" t="s">
         <v>9</v>
@@ -13251,10 +13254,10 @@
         <v>26</v>
       </c>
       <c r="E487">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F487">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G487" t="s">
         <v>27</v>
@@ -13265,7 +13268,7 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B488" t="s">
         <v>9</v>
@@ -13277,7 +13280,7 @@
         <v>29</v>
       </c>
       <c r="E488">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F488">
         <v>1</v>
@@ -13291,7 +13294,7 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B489" t="s">
         <v>9</v>
@@ -13303,21 +13306,21 @@
         <v>32</v>
       </c>
       <c r="E489">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F489">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G489" t="s">
         <v>33</v>
       </c>
       <c r="H489" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B490" t="s">
         <v>9</v>
@@ -13332,7 +13335,7 @@
         <v>1</v>
       </c>
       <c r="F490">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G490" t="s">
         <v>36</v>
@@ -13343,7 +13346,7 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B491" t="s">
         <v>9</v>
@@ -13358,18 +13361,18 @@
         <v>2</v>
       </c>
       <c r="F491">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G491" t="s">
         <v>39</v>
       </c>
       <c r="H491" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B492" t="s">
         <v>9</v>
@@ -13381,7 +13384,7 @@
         <v>41</v>
       </c>
       <c r="E492">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F492">
         <v>0</v>
@@ -13395,7 +13398,7 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B493" t="s">
         <v>9</v>
@@ -13421,7 +13424,7 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B494" t="s">
         <v>9</v>
@@ -13436,7 +13439,7 @@
         <v>2</v>
       </c>
       <c r="F494">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G494" t="s">
         <v>48</v>
@@ -13447,7 +13450,7 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B495" t="s">
         <v>9</v>
@@ -13462,18 +13465,18 @@
         <v>1</v>
       </c>
       <c r="F495">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G495" t="s">
         <v>51</v>
       </c>
       <c r="H495" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B496" t="s">
         <v>9</v>
@@ -13499,7 +13502,7 @@
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B497" t="s">
         <v>9</v>
@@ -13525,7 +13528,7 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B498" t="s">
         <v>58</v>
@@ -13551,7 +13554,7 @@
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B499" t="s">
         <v>58</v>
@@ -13569,15 +13572,15 @@
         <v>2</v>
       </c>
       <c r="G499" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H499" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B500" t="s">
         <v>58</v>
@@ -13586,24 +13589,24 @@
         <v>61</v>
       </c>
       <c r="D500" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E500">
         <v>2</v>
       </c>
       <c r="F500">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G500" t="s">
         <v>36</v>
       </c>
       <c r="H500" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B501" t="s">
         <v>58</v>
@@ -13615,10 +13618,10 @@
         <v>23</v>
       </c>
       <c r="E501">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F501">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G501" t="s">
         <v>30</v>
@@ -13629,7 +13632,7 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B502" t="s">
         <v>58</v>
@@ -13641,7 +13644,7 @@
         <v>26</v>
       </c>
       <c r="E502">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F502">
         <v>2</v>
@@ -13655,7 +13658,7 @@
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B503" t="s">
         <v>58</v>
@@ -13664,7 +13667,7 @@
         <v>64</v>
       </c>
       <c r="D503" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E503">
         <v>1</v>
@@ -13681,7 +13684,7 @@
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B504" t="s">
         <v>58</v>
@@ -13707,7 +13710,7 @@
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B505" t="s">
         <v>58</v>
@@ -13716,13 +13719,13 @@
         <v>66</v>
       </c>
       <c r="D505" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E505">
         <v>1</v>
       </c>
       <c r="F505">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G505" t="s">
         <v>41</v>
@@ -13733,7 +13736,7 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B506" t="s">
         <v>67</v>
@@ -13745,7 +13748,7 @@
         <v>41</v>
       </c>
       <c r="E506">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F506">
         <v>1</v>
@@ -13759,7 +13762,7 @@
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B507" t="s">
         <v>67</v>
@@ -13771,13 +13774,13 @@
         <v>47</v>
       </c>
       <c r="E507">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F507">
         <v>1</v>
       </c>
       <c r="G507" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H507" t="s">
         <v>47</v>
@@ -13785,7 +13788,7 @@
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B508" t="s">
         <v>67</v>
@@ -13794,24 +13797,24 @@
         <v>70</v>
       </c>
       <c r="D508" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E508">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F508">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G508" t="s">
         <v>53</v>
       </c>
       <c r="H508" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B509" t="s">
         <v>67</v>
@@ -13826,7 +13829,7 @@
         <v>2</v>
       </c>
       <c r="F509">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G509" t="s">
         <v>56</v>
@@ -13837,10 +13840,10 @@
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B510" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="C510" t="s">
         <v>73</v>
@@ -13863,25 +13866,25 @@
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B511" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="C511" t="s">
         <v>74</v>
       </c>
       <c r="D511" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="E511">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F511">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G511" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H511" t="s">
         <v>23</v>
@@ -13889,7 +13892,7 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B512" t="s">
         <v>75</v>
@@ -13907,7 +13910,7 @@
         <v>1</v>
       </c>
       <c r="G512" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="H512" t="s">
         <v>47</v>
@@ -13915,7 +13918,7 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B513" t="s">
         <v>77</v>
@@ -13927,10 +13930,10 @@
         <v>41</v>
       </c>
       <c r="E513">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F513">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G513" t="s">
         <v>23</v>
@@ -13941,7 +13944,7 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B514" t="s">
         <v>9</v>
@@ -13953,7 +13956,7 @@
         <v>11</v>
       </c>
       <c r="E514">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F514">
         <v>2</v>
@@ -13967,7 +13970,7 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B515" t="s">
         <v>9</v>
@@ -13979,7 +13982,7 @@
         <v>14</v>
       </c>
       <c r="E515">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F515">
         <v>2</v>
@@ -13993,7 +13996,7 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B516" t="s">
         <v>9</v>
@@ -14008,7 +14011,7 @@
         <v>2</v>
       </c>
       <c r="F516">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G516" t="s">
         <v>18</v>
@@ -14019,7 +14022,7 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B517" t="s">
         <v>9</v>
@@ -14031,21 +14034,21 @@
         <v>20</v>
       </c>
       <c r="E517">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F517">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G517" t="s">
         <v>21</v>
       </c>
       <c r="H517" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B518" t="s">
         <v>9</v>
@@ -14057,7 +14060,7 @@
         <v>23</v>
       </c>
       <c r="E518">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F518">
         <v>0</v>
@@ -14071,7 +14074,7 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B519" t="s">
         <v>9</v>
@@ -14086,7 +14089,7 @@
         <v>2</v>
       </c>
       <c r="F519">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G519" t="s">
         <v>27</v>
@@ -14097,7 +14100,7 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B520" t="s">
         <v>9</v>
@@ -14123,7 +14126,7 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B521" t="s">
         <v>9</v>
@@ -14135,10 +14138,10 @@
         <v>32</v>
       </c>
       <c r="E521">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F521">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G521" t="s">
         <v>33</v>
@@ -14149,7 +14152,7 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B522" t="s">
         <v>9</v>
@@ -14175,7 +14178,7 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B523" t="s">
         <v>9</v>
@@ -14190,18 +14193,18 @@
         <v>2</v>
       </c>
       <c r="F523">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G523" t="s">
         <v>39</v>
       </c>
       <c r="H523" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B524" t="s">
         <v>9</v>
@@ -14213,10 +14216,10 @@
         <v>41</v>
       </c>
       <c r="E524">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F524">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G524" t="s">
         <v>42</v>
@@ -14227,7 +14230,7 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B525" t="s">
         <v>9</v>
@@ -14239,21 +14242,21 @@
         <v>44</v>
       </c>
       <c r="E525">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F525">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G525" t="s">
         <v>45</v>
       </c>
       <c r="H525" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B526" t="s">
         <v>9</v>
@@ -14279,7 +14282,7 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B527" t="s">
         <v>9</v>
@@ -14294,18 +14297,18 @@
         <v>1</v>
       </c>
       <c r="F527">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G527" t="s">
         <v>51</v>
       </c>
       <c r="H527" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B528" t="s">
         <v>9</v>
@@ -14317,10 +14320,10 @@
         <v>53</v>
       </c>
       <c r="E528">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F528">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G528" t="s">
         <v>54</v>
@@ -14331,7 +14334,7 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B529" t="s">
         <v>9</v>
@@ -14346,7 +14349,7 @@
         <v>2</v>
       </c>
       <c r="F529">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G529" t="s">
         <v>57</v>
@@ -14357,7 +14360,7 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B530" t="s">
         <v>58</v>
@@ -14369,10 +14372,10 @@
         <v>12</v>
       </c>
       <c r="E530">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F530">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G530" t="s">
         <v>14</v>
@@ -14383,7 +14386,7 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B531" t="s">
         <v>58</v>
@@ -14395,21 +14398,21 @@
         <v>17</v>
       </c>
       <c r="E531">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F531">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G531" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="H531" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B532" t="s">
         <v>58</v>
@@ -14418,24 +14421,24 @@
         <v>61</v>
       </c>
       <c r="D532" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E532">
+        <v>2</v>
+      </c>
+      <c r="F532">
         <v>3</v>
-      </c>
-      <c r="F532">
-        <v>2</v>
       </c>
       <c r="G532" t="s">
         <v>36</v>
       </c>
       <c r="H532" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B533" t="s">
         <v>58</v>
@@ -14461,7 +14464,7 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B534" t="s">
         <v>58</v>
@@ -14487,7 +14490,7 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B535" t="s">
         <v>58</v>
@@ -14502,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="F535">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G535" t="s">
         <v>53</v>
@@ -14513,7 +14516,7 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B536" t="s">
         <v>58</v>
@@ -14522,24 +14525,24 @@
         <v>65</v>
       </c>
       <c r="D536" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E536">
         <v>1</v>
       </c>
       <c r="F536">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G536" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="H536" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B537" t="s">
         <v>58</v>
@@ -14548,7 +14551,7 @@
         <v>66</v>
       </c>
       <c r="D537" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E537">
         <v>1</v>
@@ -14565,7 +14568,7 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B538" t="s">
         <v>67</v>
@@ -14577,7 +14580,7 @@
         <v>41</v>
       </c>
       <c r="E538">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -14591,7 +14594,7 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B539" t="s">
         <v>67</v>
@@ -14600,24 +14603,24 @@
         <v>69</v>
       </c>
       <c r="D539" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="E539">
         <v>2</v>
       </c>
       <c r="F539">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G539" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="H539" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B540" t="s">
         <v>67</v>
@@ -14626,13 +14629,13 @@
         <v>70</v>
       </c>
       <c r="D540" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E540">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F540">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G540" t="s">
         <v>53</v>
@@ -14643,7 +14646,7 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B541" t="s">
         <v>67</v>
@@ -14658,7 +14661,7 @@
         <v>2</v>
       </c>
       <c r="F541">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G541" t="s">
         <v>56</v>
@@ -14669,7 +14672,7 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B542" t="s">
         <v>72</v>
@@ -14687,7 +14690,7 @@
         <v>1</v>
       </c>
       <c r="G542" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="H542" t="s">
         <v>41</v>
@@ -14695,7 +14698,7 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B543" t="s">
         <v>72</v>
@@ -14710,7 +14713,7 @@
         <v>1</v>
       </c>
       <c r="F543">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G543" t="s">
         <v>23</v>
@@ -14721,7 +14724,7 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B544" t="s">
         <v>75</v>
@@ -14730,24 +14733,24 @@
         <v>76</v>
       </c>
       <c r="D544" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="E544">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F544">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G544" t="s">
         <v>53</v>
       </c>
       <c r="H544" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B545" t="s">
         <v>77</v>
@@ -14773,7 +14776,7 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B546" t="s">
         <v>9</v>
@@ -14785,7 +14788,7 @@
         <v>11</v>
       </c>
       <c r="E546">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F546">
         <v>2</v>
@@ -14799,7 +14802,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B547" t="s">
         <v>9</v>
@@ -14811,10 +14814,10 @@
         <v>14</v>
       </c>
       <c r="E547">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F547">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G547" t="s">
         <v>15</v>
@@ -14825,7 +14828,7 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B548" t="s">
         <v>9</v>
@@ -14851,7 +14854,7 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B549" t="s">
         <v>9</v>
@@ -14866,7 +14869,7 @@
         <v>2</v>
       </c>
       <c r="F549">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G549" t="s">
         <v>21</v>
@@ -14877,7 +14880,7 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B550" t="s">
         <v>9</v>
@@ -14889,7 +14892,7 @@
         <v>23</v>
       </c>
       <c r="E550">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F550">
         <v>0</v>
@@ -14903,7 +14906,7 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B551" t="s">
         <v>9</v>
@@ -14915,10 +14918,10 @@
         <v>26</v>
       </c>
       <c r="E551">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F551">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G551" t="s">
         <v>27</v>
@@ -14929,7 +14932,7 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B552" t="s">
         <v>9</v>
@@ -14941,7 +14944,7 @@
         <v>29</v>
       </c>
       <c r="E552">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F552">
         <v>1</v>
@@ -14950,12 +14953,12 @@
         <v>30</v>
       </c>
       <c r="H552" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B553" t="s">
         <v>9</v>
@@ -14967,7 +14970,7 @@
         <v>32</v>
       </c>
       <c r="E553">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F553">
         <v>1</v>
@@ -14976,12 +14979,12 @@
         <v>33</v>
       </c>
       <c r="H553" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B554" t="s">
         <v>9</v>
@@ -14993,21 +14996,21 @@
         <v>35</v>
       </c>
       <c r="E554">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F554">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G554" t="s">
         <v>36</v>
       </c>
       <c r="H554" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B555" t="s">
         <v>9</v>
@@ -15033,7 +15036,7 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B556" t="s">
         <v>9</v>
@@ -15045,7 +15048,7 @@
         <v>41</v>
       </c>
       <c r="E556">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F556">
         <v>1</v>
@@ -15059,7 +15062,7 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B557" t="s">
         <v>9</v>
@@ -15085,7 +15088,7 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B558" t="s">
         <v>9</v>
@@ -15097,10 +15100,10 @@
         <v>47</v>
       </c>
       <c r="E558">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F558">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G558" t="s">
         <v>48</v>
@@ -15111,7 +15114,7 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B559" t="s">
         <v>9</v>
@@ -15123,21 +15126,21 @@
         <v>50</v>
       </c>
       <c r="E559">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F559">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G559" t="s">
         <v>51</v>
       </c>
       <c r="H559" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B560" t="s">
         <v>9</v>
@@ -15152,7 +15155,7 @@
         <v>3</v>
       </c>
       <c r="F560">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G560" t="s">
         <v>54</v>
@@ -15163,7 +15166,7 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B561" t="s">
         <v>9</v>
@@ -15178,7 +15181,7 @@
         <v>2</v>
       </c>
       <c r="F561">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G561" t="s">
         <v>57</v>
@@ -15189,7 +15192,7 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B562" t="s">
         <v>58</v>
@@ -15201,10 +15204,10 @@
         <v>12</v>
       </c>
       <c r="E562">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F562">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G562" t="s">
         <v>14</v>
@@ -15215,7 +15218,7 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B563" t="s">
         <v>58</v>
@@ -15233,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="G563" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H563" t="s">
         <v>17</v>
@@ -15241,7 +15244,7 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B564" t="s">
         <v>58</v>
@@ -15256,10 +15259,10 @@
         <v>3</v>
       </c>
       <c r="F564">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G564" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="H564" t="s">
         <v>20</v>
@@ -15267,7 +15270,7 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B565" t="s">
         <v>58</v>
@@ -15279,13 +15282,13 @@
         <v>23</v>
       </c>
       <c r="E565">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F565">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G565" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H565" t="s">
         <v>23</v>
@@ -15293,7 +15296,7 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B566" t="s">
         <v>58</v>
@@ -15319,7 +15322,7 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B567" t="s">
         <v>58</v>
@@ -15328,13 +15331,13 @@
         <v>64</v>
       </c>
       <c r="D567" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E567">
         <v>1</v>
       </c>
       <c r="F567">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G567" t="s">
         <v>53</v>
@@ -15345,7 +15348,7 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B568" t="s">
         <v>58</v>
@@ -15360,18 +15363,18 @@
         <v>1</v>
       </c>
       <c r="F568">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G568" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="H568" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B569" t="s">
         <v>58</v>
@@ -15383,21 +15386,21 @@
         <v>38</v>
       </c>
       <c r="E569">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F569">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G569" t="s">
         <v>41</v>
       </c>
       <c r="H569" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B570" t="s">
         <v>67</v>
@@ -15406,7 +15409,7 @@
         <v>68</v>
       </c>
       <c r="D570" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E570">
         <v>2</v>
@@ -15418,12 +15421,12 @@
         <v>14</v>
       </c>
       <c r="H570" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B571" t="s">
         <v>67</v>
@@ -15432,7 +15435,7 @@
         <v>69</v>
       </c>
       <c r="D571" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="E571">
         <v>2</v>
@@ -15444,12 +15447,12 @@
         <v>17</v>
       </c>
       <c r="H571" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B572" t="s">
         <v>67</v>
@@ -15470,12 +15473,12 @@
         <v>53</v>
       </c>
       <c r="H572" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B573" t="s">
         <v>67</v>
@@ -15501,7 +15504,7 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B574" t="s">
         <v>72</v>
@@ -15510,24 +15513,24 @@
         <v>73</v>
       </c>
       <c r="D574" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E574">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F574">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G574" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="H574" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B575" t="s">
         <v>72</v>
@@ -15536,7 +15539,7 @@
         <v>74</v>
       </c>
       <c r="D575" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E575">
         <v>1</v>
@@ -15553,7 +15556,7 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B576" t="s">
         <v>75</v>
@@ -15562,15 +15565,24 @@
         <v>76</v>
       </c>
       <c r="D576" t="s">
-        <v>38</v>
+        <v>83</v>
+      </c>
+      <c r="E576">
+        <v>1</v>
+      </c>
+      <c r="F576">
+        <v>2</v>
       </c>
       <c r="G576" t="s">
-        <v>135</v>
+        <v>53</v>
+      </c>
+      <c r="H576" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B577" t="s">
         <v>77</v>
@@ -15579,15 +15591,24 @@
         <v>78</v>
       </c>
       <c r="D577" t="s">
-        <v>136</v>
+        <v>41</v>
+      </c>
+      <c r="E577">
+        <v>3</v>
+      </c>
+      <c r="F577">
+        <v>2</v>
       </c>
       <c r="G577" t="s">
-        <v>137</v>
+        <v>23</v>
+      </c>
+      <c r="H577" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B578" t="s">
         <v>9</v>
@@ -15598,13 +15619,22 @@
       <c r="D578" t="s">
         <v>11</v>
       </c>
+      <c r="E578">
+        <v>1</v>
+      </c>
+      <c r="F578">
+        <v>2</v>
+      </c>
       <c r="G578" t="s">
         <v>12</v>
       </c>
+      <c r="H578" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B579" t="s">
         <v>9</v>
@@ -15616,7 +15646,7 @@
         <v>14</v>
       </c>
       <c r="E579">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F579">
         <v>1</v>
@@ -15625,12 +15655,12 @@
         <v>15</v>
       </c>
       <c r="H579" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B580" t="s">
         <v>9</v>
@@ -15651,12 +15681,12 @@
         <v>18</v>
       </c>
       <c r="H580" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B581" t="s">
         <v>9</v>
@@ -15668,21 +15698,21 @@
         <v>20</v>
       </c>
       <c r="E581">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F581">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G581" t="s">
         <v>21</v>
       </c>
       <c r="H581" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B582" t="s">
         <v>9</v>
@@ -15694,7 +15724,7 @@
         <v>23</v>
       </c>
       <c r="E582">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F582">
         <v>0</v>
@@ -15703,12 +15733,12 @@
         <v>24</v>
       </c>
       <c r="H582" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B583" t="s">
         <v>9</v>
@@ -15723,18 +15753,18 @@
         <v>1</v>
       </c>
       <c r="F583">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G583" t="s">
         <v>27</v>
       </c>
       <c r="H583" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B584" t="s">
         <v>9</v>
@@ -15746,21 +15776,21 @@
         <v>29</v>
       </c>
       <c r="E584">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F584">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G584" t="s">
         <v>30</v>
       </c>
       <c r="H584" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B585" t="s">
         <v>9</v>
@@ -15772,21 +15802,21 @@
         <v>32</v>
       </c>
       <c r="E585">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F585">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G585" t="s">
         <v>33</v>
       </c>
       <c r="H585" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B586" t="s">
         <v>9</v>
@@ -15798,21 +15828,21 @@
         <v>35</v>
       </c>
       <c r="E586">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F586">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G586" t="s">
         <v>36</v>
       </c>
       <c r="H586" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B587" t="s">
         <v>9</v>
@@ -15824,7 +15854,7 @@
         <v>38</v>
       </c>
       <c r="E587">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F587">
         <v>1</v>
@@ -15833,12 +15863,12 @@
         <v>39</v>
       </c>
       <c r="H587" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B588" t="s">
         <v>9</v>
@@ -15850,7 +15880,7 @@
         <v>41</v>
       </c>
       <c r="E588">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F588">
         <v>1</v>
@@ -15859,12 +15889,12 @@
         <v>42</v>
       </c>
       <c r="H588" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B589" t="s">
         <v>9</v>
@@ -15876,21 +15906,21 @@
         <v>44</v>
       </c>
       <c r="E589">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F589">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G589" t="s">
         <v>45</v>
       </c>
       <c r="H589" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B590" t="s">
         <v>9</v>
@@ -15911,12 +15941,12 @@
         <v>48</v>
       </c>
       <c r="H590" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B591" t="s">
         <v>9</v>
@@ -15937,12 +15967,12 @@
         <v>51</v>
       </c>
       <c r="H591" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B592" t="s">
         <v>9</v>
@@ -15963,12 +15993,12 @@
         <v>54</v>
       </c>
       <c r="H592" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B593" t="s">
         <v>9</v>
@@ -15983,18 +16013,18 @@
         <v>2</v>
       </c>
       <c r="F593">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G593" t="s">
         <v>57</v>
       </c>
       <c r="H593" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B594" t="s">
         <v>58</v>
@@ -16012,15 +16042,15 @@
         <v>2</v>
       </c>
       <c r="G594" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="H594" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B595" t="s">
         <v>58</v>
@@ -16032,21 +16062,21 @@
         <v>17</v>
       </c>
       <c r="E595">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F595">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G595" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H595" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B596" t="s">
         <v>58</v>
@@ -16058,21 +16088,21 @@
         <v>20</v>
       </c>
       <c r="E596">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F596">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G596" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="H596" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B597" t="s">
         <v>58</v>
@@ -16084,21 +16114,21 @@
         <v>23</v>
       </c>
       <c r="E597">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F597">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G597" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H597" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B598" t="s">
         <v>58</v>
@@ -16119,12 +16149,12 @@
         <v>56</v>
       </c>
       <c r="H598" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B599" t="s">
         <v>58</v>
@@ -16133,10 +16163,10 @@
         <v>64</v>
       </c>
       <c r="D599" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E599">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F599">
         <v>2</v>
@@ -16145,12 +16175,12 @@
         <v>53</v>
       </c>
       <c r="H599" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B600" t="s">
         <v>58</v>
@@ -16159,24 +16189,24 @@
         <v>65</v>
       </c>
       <c r="D600" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E600">
         <v>1</v>
       </c>
       <c r="F600">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G600" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="H600" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B601" t="s">
         <v>58</v>
@@ -16188,21 +16218,21 @@
         <v>38</v>
       </c>
       <c r="E601">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F601">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G601" t="s">
         <v>41</v>
       </c>
       <c r="H601" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B602" t="s">
         <v>67</v>
@@ -16211,7 +16241,7 @@
         <v>68</v>
       </c>
       <c r="D602" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="E602">
         <v>2</v>
@@ -16220,15 +16250,15 @@
         <v>1</v>
       </c>
       <c r="G602" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="H602" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B603" t="s">
         <v>67</v>
@@ -16243,18 +16273,18 @@
         <v>2</v>
       </c>
       <c r="F603">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G603" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="H603" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B604" t="s">
         <v>67</v>
@@ -16263,24 +16293,24 @@
         <v>70</v>
       </c>
       <c r="D604" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E604">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F604">
         <v>1</v>
       </c>
       <c r="G604" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="H604" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B605" t="s">
         <v>67</v>
@@ -16289,24 +16319,24 @@
         <v>71</v>
       </c>
       <c r="D605" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="E605">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F605">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G605" t="s">
         <v>56</v>
       </c>
       <c r="H605" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B606" t="s">
         <v>72</v>
@@ -16315,24 +16345,24 @@
         <v>73</v>
       </c>
       <c r="D606" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="E606">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F606">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G606" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="H606" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B607" t="s">
         <v>72</v>
@@ -16341,24 +16371,24 @@
         <v>74</v>
       </c>
       <c r="D607" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E607">
         <v>1</v>
       </c>
       <c r="F607">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G607" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H607" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B608" t="s">
         <v>75</v>
@@ -16367,24 +16397,15 @@
         <v>76</v>
       </c>
       <c r="D608" t="s">
-        <v>47</v>
-      </c>
-      <c r="E608">
-        <v>1</v>
-      </c>
-      <c r="F608">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G608" t="s">
-        <v>81</v>
-      </c>
-      <c r="H608" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B609" t="s">
         <v>77</v>
@@ -16393,24 +16414,15 @@
         <v>78</v>
       </c>
       <c r="D609" t="s">
-        <v>41</v>
-      </c>
-      <c r="E609">
-        <v>2</v>
-      </c>
-      <c r="F609">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="G609" t="s">
-        <v>56</v>
-      </c>
-      <c r="H609" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B610" t="s">
         <v>9</v>
@@ -16421,22 +16433,13 @@
       <c r="D610" t="s">
         <v>11</v>
       </c>
-      <c r="E610">
-        <v>1</v>
-      </c>
-      <c r="F610">
-        <v>1</v>
-      </c>
       <c r="G610" t="s">
         <v>12</v>
       </c>
-      <c r="H610" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B611" t="s">
         <v>9</v>
@@ -16457,12 +16460,12 @@
         <v>15</v>
       </c>
       <c r="H611" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B612" t="s">
         <v>9</v>
@@ -16483,12 +16486,12 @@
         <v>18</v>
       </c>
       <c r="H612" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B613" t="s">
         <v>9</v>
@@ -16500,21 +16503,21 @@
         <v>20</v>
       </c>
       <c r="E613">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F613">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G613" t="s">
         <v>21</v>
       </c>
       <c r="H613" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B614" t="s">
         <v>9</v>
@@ -16535,12 +16538,12 @@
         <v>24</v>
       </c>
       <c r="H614" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B615" t="s">
         <v>9</v>
@@ -16555,18 +16558,18 @@
         <v>1</v>
       </c>
       <c r="F615">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G615" t="s">
         <v>27</v>
       </c>
       <c r="H615" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B616" t="s">
         <v>9</v>
@@ -16578,7 +16581,7 @@
         <v>29</v>
       </c>
       <c r="E616">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F616">
         <v>2</v>
@@ -16587,12 +16590,12 @@
         <v>30</v>
       </c>
       <c r="H616" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B617" t="s">
         <v>9</v>
@@ -16607,7 +16610,7 @@
         <v>1</v>
       </c>
       <c r="F617">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G617" t="s">
         <v>33</v>
@@ -16618,7 +16621,7 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B618" t="s">
         <v>9</v>
@@ -16630,7 +16633,7 @@
         <v>35</v>
       </c>
       <c r="E618">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F618">
         <v>2</v>
@@ -16639,12 +16642,12 @@
         <v>36</v>
       </c>
       <c r="H618" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B619" t="s">
         <v>9</v>
@@ -16656,21 +16659,21 @@
         <v>38</v>
       </c>
       <c r="E619">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F619">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G619" t="s">
         <v>39</v>
       </c>
       <c r="H619" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B620" t="s">
         <v>9</v>
@@ -16682,7 +16685,7 @@
         <v>41</v>
       </c>
       <c r="E620">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F620">
         <v>1</v>
@@ -16691,12 +16694,12 @@
         <v>42</v>
       </c>
       <c r="H620" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B621" t="s">
         <v>9</v>
@@ -16708,21 +16711,21 @@
         <v>44</v>
       </c>
       <c r="E621">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F621">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G621" t="s">
         <v>45</v>
       </c>
       <c r="H621" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B622" t="s">
         <v>9</v>
@@ -16734,21 +16737,21 @@
         <v>47</v>
       </c>
       <c r="E622">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F622">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G622" t="s">
         <v>48</v>
       </c>
       <c r="H622" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B623" t="s">
         <v>9</v>
@@ -16760,21 +16763,21 @@
         <v>50</v>
       </c>
       <c r="E623">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F623">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G623" t="s">
         <v>51</v>
       </c>
       <c r="H623" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B624" t="s">
         <v>9</v>
@@ -16786,7 +16789,7 @@
         <v>53</v>
       </c>
       <c r="E624">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F624">
         <v>0</v>
@@ -16795,12 +16798,12 @@
         <v>54</v>
       </c>
       <c r="H624" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -16815,18 +16818,18 @@
         <v>2</v>
       </c>
       <c r="F625">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G625" t="s">
         <v>57</v>
       </c>
       <c r="H625" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B626" t="s">
         <v>58</v>
@@ -16838,21 +16841,21 @@
         <v>12</v>
       </c>
       <c r="E626">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F626">
         <v>2</v>
       </c>
       <c r="G626" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="H626" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B627" t="s">
         <v>58</v>
@@ -16864,21 +16867,21 @@
         <v>17</v>
       </c>
       <c r="E627">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F627">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G627" t="s">
         <v>50</v>
       </c>
       <c r="H627" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B628" t="s">
         <v>58</v>
@@ -16890,21 +16893,21 @@
         <v>20</v>
       </c>
       <c r="E628">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F628">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G628" t="s">
         <v>36</v>
       </c>
       <c r="H628" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B629" t="s">
         <v>58</v>
@@ -16916,7 +16919,7 @@
         <v>23</v>
       </c>
       <c r="E629">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F629">
         <v>1</v>
@@ -16925,12 +16928,12 @@
         <v>30</v>
       </c>
       <c r="H629" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B630" t="s">
         <v>58</v>
@@ -16942,7 +16945,7 @@
         <v>26</v>
       </c>
       <c r="E630">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F630">
         <v>2</v>
@@ -16951,12 +16954,12 @@
         <v>56</v>
       </c>
       <c r="H630" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B631" t="s">
         <v>58</v>
@@ -16977,12 +16980,12 @@
         <v>53</v>
       </c>
       <c r="H631" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B632" t="s">
         <v>58</v>
@@ -16991,24 +16994,24 @@
         <v>65</v>
       </c>
       <c r="D632" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E632">
         <v>1</v>
       </c>
       <c r="F632">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G632" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="H632" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B633" t="s">
         <v>58</v>
@@ -17020,7 +17023,7 @@
         <v>38</v>
       </c>
       <c r="E633">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F633">
         <v>2</v>
@@ -17029,12 +17032,12 @@
         <v>41</v>
       </c>
       <c r="H633" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B634" t="s">
         <v>67</v>
@@ -17043,7 +17046,7 @@
         <v>68</v>
       </c>
       <c r="D634" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="E634">
         <v>2</v>
@@ -17052,15 +17055,15 @@
         <v>1</v>
       </c>
       <c r="G634" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="H634" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B635" t="s">
         <v>67</v>
@@ -17078,15 +17081,15 @@
         <v>1</v>
       </c>
       <c r="G635" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="H635" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B636" t="s">
         <v>67</v>
@@ -17095,24 +17098,24 @@
         <v>70</v>
       </c>
       <c r="D636" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E636">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F636">
         <v>1</v>
       </c>
       <c r="G636" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="H636" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B637" t="s">
         <v>67</v>
@@ -17121,24 +17124,24 @@
         <v>71</v>
       </c>
       <c r="D637" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="E637">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F637">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G637" t="s">
         <v>56</v>
       </c>
       <c r="H637" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B638" t="s">
         <v>72</v>
@@ -17147,7 +17150,7 @@
         <v>73</v>
       </c>
       <c r="D638" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="E638">
         <v>2</v>
@@ -17159,12 +17162,12 @@
         <v>83</v>
       </c>
       <c r="H638" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B639" t="s">
         <v>72</v>
@@ -17173,24 +17176,24 @@
         <v>74</v>
       </c>
       <c r="D639" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E639">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F639">
         <v>1</v>
       </c>
       <c r="G639" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H639" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B640" t="s">
         <v>75</v>
@@ -17202,21 +17205,21 @@
         <v>47</v>
       </c>
       <c r="E640">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F640">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G640" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="H640" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B641" t="s">
         <v>77</v>
@@ -17228,21 +17231,21 @@
         <v>41</v>
       </c>
       <c r="E641">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F641">
         <v>1</v>
       </c>
       <c r="G641" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H641" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B642" t="s">
         <v>9</v>
@@ -17257,18 +17260,18 @@
         <v>1</v>
       </c>
       <c r="F642">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G642" t="s">
         <v>12</v>
       </c>
       <c r="H642" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B643" t="s">
         <v>9</v>
@@ -17283,7 +17286,7 @@
         <v>2</v>
       </c>
       <c r="F643">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G643" t="s">
         <v>15</v>
@@ -17294,7 +17297,7 @@
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B644" t="s">
         <v>9</v>
@@ -17320,7 +17323,7 @@
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B645" t="s">
         <v>9</v>
@@ -17335,7 +17338,7 @@
         <v>2</v>
       </c>
       <c r="F645">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G645" t="s">
         <v>21</v>
@@ -17346,7 +17349,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B646" t="s">
         <v>9</v>
@@ -17372,7 +17375,7 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B647" t="s">
         <v>9</v>
@@ -17387,18 +17390,18 @@
         <v>1</v>
       </c>
       <c r="F647">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G647" t="s">
         <v>27</v>
       </c>
       <c r="H647" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B648" t="s">
         <v>9</v>
@@ -17410,10 +17413,10 @@
         <v>29</v>
       </c>
       <c r="E648">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F648">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G648" t="s">
         <v>30</v>
@@ -17424,7 +17427,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B649" t="s">
         <v>9</v>
@@ -17439,18 +17442,18 @@
         <v>1</v>
       </c>
       <c r="F649">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G649" t="s">
         <v>33</v>
       </c>
       <c r="H649" t="s">
-        <v>32</v>
+        <v>147</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B650" t="s">
         <v>9</v>
@@ -17476,7 +17479,7 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B651" t="s">
         <v>9</v>
@@ -17488,10 +17491,10 @@
         <v>38</v>
       </c>
       <c r="E651">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F651">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G651" t="s">
         <v>39</v>
@@ -17502,7 +17505,7 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B652" t="s">
         <v>9</v>
@@ -17514,10 +17517,10 @@
         <v>41</v>
       </c>
       <c r="E652">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F652">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G652" t="s">
         <v>42</v>
@@ -17528,7 +17531,7 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B653" t="s">
         <v>9</v>
@@ -17554,7 +17557,7 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B654" t="s">
         <v>9</v>
@@ -17566,10 +17569,10 @@
         <v>47</v>
       </c>
       <c r="E654">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F654">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G654" t="s">
         <v>48</v>
@@ -17580,7 +17583,7 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B655" t="s">
         <v>9</v>
@@ -17595,18 +17598,18 @@
         <v>1</v>
       </c>
       <c r="F655">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G655" t="s">
         <v>51</v>
       </c>
       <c r="H655" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B656" t="s">
         <v>9</v>
@@ -17618,7 +17621,7 @@
         <v>53</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656">
         <v>0</v>
@@ -17632,7 +17635,7 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B657" t="s">
         <v>9</v>
@@ -17647,7 +17650,7 @@
         <v>2</v>
       </c>
       <c r="F657">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G657" t="s">
         <v>57</v>
@@ -17658,7 +17661,7 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B658" t="s">
         <v>58</v>
@@ -17670,21 +17673,21 @@
         <v>12</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F658">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G658" t="s">
         <v>14</v>
       </c>
       <c r="H658" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B659" t="s">
         <v>58</v>
@@ -17705,12 +17708,12 @@
         <v>50</v>
       </c>
       <c r="H659" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B660" t="s">
         <v>58</v>
@@ -17736,7 +17739,7 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B661" t="s">
         <v>58</v>
@@ -17748,10 +17751,10 @@
         <v>23</v>
       </c>
       <c r="E661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G661" t="s">
         <v>30</v>
@@ -17762,7 +17765,7 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B662" t="s">
         <v>58</v>
@@ -17771,10 +17774,10 @@
         <v>63</v>
       </c>
       <c r="D662" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E662">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F662">
         <v>2</v>
@@ -17788,7 +17791,7 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B663" t="s">
         <v>58</v>
@@ -17797,13 +17800,13 @@
         <v>64</v>
       </c>
       <c r="D663" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E663">
         <v>0</v>
       </c>
       <c r="F663">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G663" t="s">
         <v>53</v>
@@ -17814,7 +17817,7 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B664" t="s">
         <v>58</v>
@@ -17840,7 +17843,7 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B665" t="s">
         <v>58</v>
@@ -17852,10 +17855,10 @@
         <v>38</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G665" t="s">
         <v>41</v>
@@ -17866,7 +17869,7 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B666" t="s">
         <v>67</v>
@@ -17884,7 +17887,7 @@
         <v>1</v>
       </c>
       <c r="G666" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="H666" t="s">
         <v>41</v>
@@ -17892,7 +17895,7 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B667" t="s">
         <v>67</v>
@@ -17904,10 +17907,10 @@
         <v>47</v>
       </c>
       <c r="E667">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G667" t="s">
         <v>17</v>
@@ -17918,7 +17921,7 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B668" t="s">
         <v>67</v>
@@ -17930,7 +17933,7 @@
         <v>20</v>
       </c>
       <c r="E668">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F668">
         <v>1</v>
@@ -17944,7 +17947,7 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B669" t="s">
         <v>67</v>
@@ -17956,21 +17959,21 @@
         <v>23</v>
       </c>
       <c r="E669">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F669">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G669" t="s">
         <v>56</v>
       </c>
       <c r="H669" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B670" t="s">
         <v>72</v>
@@ -17988,7 +17991,7 @@
         <v>1</v>
       </c>
       <c r="G670" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="H670" t="s">
         <v>41</v>
@@ -17996,7 +17999,7 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B671" t="s">
         <v>72</v>
@@ -18005,24 +18008,24 @@
         <v>74</v>
       </c>
       <c r="D671" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="E671">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F671">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G671" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H671" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B672" t="s">
         <v>75</v>
@@ -18034,21 +18037,21 @@
         <v>47</v>
       </c>
       <c r="E672">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F672">
         <v>1</v>
       </c>
       <c r="G672" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="H672" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B673" t="s">
         <v>77</v>
@@ -18060,15 +18063,847 @@
         <v>41</v>
       </c>
       <c r="E673">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G673" t="s">
+        <v>23</v>
+      </c>
+      <c r="H673" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>164</v>
+      </c>
+      <c r="B674" t="s">
+        <v>9</v>
+      </c>
+      <c r="C674" t="s">
+        <v>10</v>
+      </c>
+      <c r="D674" t="s">
+        <v>11</v>
+      </c>
+      <c r="E674">
+        <v>1</v>
+      </c>
+      <c r="F674">
+        <v>2</v>
+      </c>
+      <c r="G674" t="s">
+        <v>12</v>
+      </c>
+      <c r="H674" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>164</v>
+      </c>
+      <c r="B675" t="s">
+        <v>9</v>
+      </c>
+      <c r="C675" t="s">
+        <v>13</v>
+      </c>
+      <c r="D675" t="s">
+        <v>14</v>
+      </c>
+      <c r="E675">
+        <v>2</v>
+      </c>
+      <c r="F675">
+        <v>2</v>
+      </c>
+      <c r="G675" t="s">
+        <v>15</v>
+      </c>
+      <c r="H675" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>164</v>
+      </c>
+      <c r="B676" t="s">
+        <v>9</v>
+      </c>
+      <c r="C676" t="s">
+        <v>16</v>
+      </c>
+      <c r="D676" t="s">
+        <v>17</v>
+      </c>
+      <c r="E676">
+        <v>2</v>
+      </c>
+      <c r="F676">
+        <v>0</v>
+      </c>
+      <c r="G676" t="s">
+        <v>18</v>
+      </c>
+      <c r="H676" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>164</v>
+      </c>
+      <c r="B677" t="s">
+        <v>9</v>
+      </c>
+      <c r="C677" t="s">
+        <v>19</v>
+      </c>
+      <c r="D677" t="s">
+        <v>20</v>
+      </c>
+      <c r="E677">
+        <v>2</v>
+      </c>
+      <c r="F677">
+        <v>1</v>
+      </c>
+      <c r="G677" t="s">
+        <v>21</v>
+      </c>
+      <c r="H677" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>164</v>
+      </c>
+      <c r="B678" t="s">
+        <v>9</v>
+      </c>
+      <c r="C678" t="s">
+        <v>22</v>
+      </c>
+      <c r="D678" t="s">
+        <v>23</v>
+      </c>
+      <c r="E678">
+        <v>2</v>
+      </c>
+      <c r="F678">
+        <v>0</v>
+      </c>
+      <c r="G678" t="s">
+        <v>24</v>
+      </c>
+      <c r="H678" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>164</v>
+      </c>
+      <c r="B679" t="s">
+        <v>9</v>
+      </c>
+      <c r="C679" t="s">
+        <v>25</v>
+      </c>
+      <c r="D679" t="s">
+        <v>26</v>
+      </c>
+      <c r="E679">
+        <v>1</v>
+      </c>
+      <c r="F679">
+        <v>2</v>
+      </c>
+      <c r="G679" t="s">
+        <v>27</v>
+      </c>
+      <c r="H679" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>164</v>
+      </c>
+      <c r="B680" t="s">
+        <v>9</v>
+      </c>
+      <c r="C680" t="s">
+        <v>28</v>
+      </c>
+      <c r="D680" t="s">
+        <v>29</v>
+      </c>
+      <c r="E680">
+        <v>1</v>
+      </c>
+      <c r="F680">
+        <v>3</v>
+      </c>
+      <c r="G680" t="s">
+        <v>30</v>
+      </c>
+      <c r="H680" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>164</v>
+      </c>
+      <c r="B681" t="s">
+        <v>9</v>
+      </c>
+      <c r="C681" t="s">
+        <v>31</v>
+      </c>
+      <c r="D681" t="s">
+        <v>32</v>
+      </c>
+      <c r="E681">
+        <v>1</v>
+      </c>
+      <c r="F681">
+        <v>0</v>
+      </c>
+      <c r="G681" t="s">
+        <v>33</v>
+      </c>
+      <c r="H681" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>164</v>
+      </c>
+      <c r="B682" t="s">
+        <v>9</v>
+      </c>
+      <c r="C682" t="s">
+        <v>34</v>
+      </c>
+      <c r="D682" t="s">
+        <v>35</v>
+      </c>
+      <c r="E682">
+        <v>1</v>
+      </c>
+      <c r="F682">
+        <v>2</v>
+      </c>
+      <c r="G682" t="s">
+        <v>36</v>
+      </c>
+      <c r="H682" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>164</v>
+      </c>
+      <c r="B683" t="s">
+        <v>9</v>
+      </c>
+      <c r="C683" t="s">
+        <v>37</v>
+      </c>
+      <c r="D683" t="s">
+        <v>38</v>
+      </c>
+      <c r="E683">
+        <v>3</v>
+      </c>
+      <c r="F683">
+        <v>1</v>
+      </c>
+      <c r="G683" t="s">
+        <v>39</v>
+      </c>
+      <c r="H683" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>164</v>
+      </c>
+      <c r="B684" t="s">
+        <v>9</v>
+      </c>
+      <c r="C684" t="s">
+        <v>40</v>
+      </c>
+      <c r="D684" t="s">
+        <v>41</v>
+      </c>
+      <c r="E684">
+        <v>2</v>
+      </c>
+      <c r="F684">
+        <v>0</v>
+      </c>
+      <c r="G684" t="s">
+        <v>42</v>
+      </c>
+      <c r="H684" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>164</v>
+      </c>
+      <c r="B685" t="s">
+        <v>9</v>
+      </c>
+      <c r="C685" t="s">
+        <v>43</v>
+      </c>
+      <c r="D685" t="s">
+        <v>44</v>
+      </c>
+      <c r="E685">
+        <v>2</v>
+      </c>
+      <c r="F685">
+        <v>1</v>
+      </c>
+      <c r="G685" t="s">
+        <v>45</v>
+      </c>
+      <c r="H685" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>164</v>
+      </c>
+      <c r="B686" t="s">
+        <v>9</v>
+      </c>
+      <c r="C686" t="s">
+        <v>46</v>
+      </c>
+      <c r="D686" t="s">
+        <v>47</v>
+      </c>
+      <c r="E686">
+        <v>3</v>
+      </c>
+      <c r="F686">
+        <v>1</v>
+      </c>
+      <c r="G686" t="s">
+        <v>48</v>
+      </c>
+      <c r="H686" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>164</v>
+      </c>
+      <c r="B687" t="s">
+        <v>9</v>
+      </c>
+      <c r="C687" t="s">
+        <v>49</v>
+      </c>
+      <c r="D687" t="s">
+        <v>50</v>
+      </c>
+      <c r="E687">
+        <v>1</v>
+      </c>
+      <c r="F687">
+        <v>2</v>
+      </c>
+      <c r="G687" t="s">
+        <v>51</v>
+      </c>
+      <c r="H687" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>164</v>
+      </c>
+      <c r="B688" t="s">
+        <v>9</v>
+      </c>
+      <c r="C688" t="s">
+        <v>52</v>
+      </c>
+      <c r="D688" t="s">
+        <v>53</v>
+      </c>
+      <c r="E688">
+        <v>1</v>
+      </c>
+      <c r="F688">
+        <v>0</v>
+      </c>
+      <c r="G688" t="s">
+        <v>54</v>
+      </c>
+      <c r="H688" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>164</v>
+      </c>
+      <c r="B689" t="s">
+        <v>9</v>
+      </c>
+      <c r="C689" t="s">
+        <v>55</v>
+      </c>
+      <c r="D689" t="s">
+        <v>56</v>
+      </c>
+      <c r="E689">
+        <v>2</v>
+      </c>
+      <c r="F689">
+        <v>1</v>
+      </c>
+      <c r="G689" t="s">
+        <v>57</v>
+      </c>
+      <c r="H689" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>164</v>
+      </c>
+      <c r="B690" t="s">
+        <v>58</v>
+      </c>
+      <c r="C690" t="s">
+        <v>59</v>
+      </c>
+      <c r="D690" t="s">
+        <v>12</v>
+      </c>
+      <c r="E690">
+        <v>1</v>
+      </c>
+      <c r="F690">
+        <v>0</v>
+      </c>
+      <c r="G690" t="s">
+        <v>14</v>
+      </c>
+      <c r="H690" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>164</v>
+      </c>
+      <c r="B691" t="s">
+        <v>58</v>
+      </c>
+      <c r="C691" t="s">
+        <v>60</v>
+      </c>
+      <c r="D691" t="s">
+        <v>17</v>
+      </c>
+      <c r="E691">
+        <v>2</v>
+      </c>
+      <c r="F691">
+        <v>1</v>
+      </c>
+      <c r="G691" t="s">
+        <v>50</v>
+      </c>
+      <c r="H691" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>164</v>
+      </c>
+      <c r="B692" t="s">
+        <v>58</v>
+      </c>
+      <c r="C692" t="s">
+        <v>61</v>
+      </c>
+      <c r="D692" t="s">
+        <v>20</v>
+      </c>
+      <c r="E692">
+        <v>2</v>
+      </c>
+      <c r="F692">
+        <v>1</v>
+      </c>
+      <c r="G692" t="s">
+        <v>36</v>
+      </c>
+      <c r="H692" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>164</v>
+      </c>
+      <c r="B693" t="s">
+        <v>58</v>
+      </c>
+      <c r="C693" t="s">
+        <v>62</v>
+      </c>
+      <c r="D693" t="s">
+        <v>23</v>
+      </c>
+      <c r="E693">
+        <v>1</v>
+      </c>
+      <c r="F693">
+        <v>0</v>
+      </c>
+      <c r="G693" t="s">
+        <v>30</v>
+      </c>
+      <c r="H693" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>164</v>
+      </c>
+      <c r="B694" t="s">
+        <v>58</v>
+      </c>
+      <c r="C694" t="s">
+        <v>63</v>
+      </c>
+      <c r="D694" t="s">
+        <v>27</v>
+      </c>
+      <c r="E694">
+        <v>1</v>
+      </c>
+      <c r="F694">
+        <v>2</v>
+      </c>
+      <c r="G694" t="s">
+        <v>56</v>
+      </c>
+      <c r="H694" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>164</v>
+      </c>
+      <c r="B695" t="s">
+        <v>58</v>
+      </c>
+      <c r="C695" t="s">
+        <v>64</v>
+      </c>
+      <c r="D695" t="s">
+        <v>32</v>
+      </c>
+      <c r="E695">
+        <v>0</v>
+      </c>
+      <c r="F695">
+        <v>1</v>
+      </c>
+      <c r="G695" t="s">
+        <v>53</v>
+      </c>
+      <c r="H695" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>164</v>
+      </c>
+      <c r="B696" t="s">
+        <v>58</v>
+      </c>
+      <c r="C696" t="s">
+        <v>65</v>
+      </c>
+      <c r="D696" t="s">
+        <v>44</v>
+      </c>
+      <c r="E696">
+        <v>1</v>
+      </c>
+      <c r="F696">
+        <v>2</v>
+      </c>
+      <c r="G696" t="s">
+        <v>47</v>
+      </c>
+      <c r="H696" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>164</v>
+      </c>
+      <c r="B697" t="s">
+        <v>58</v>
+      </c>
+      <c r="C697" t="s">
+        <v>66</v>
+      </c>
+      <c r="D697" t="s">
+        <v>38</v>
+      </c>
+      <c r="E697">
+        <v>0</v>
+      </c>
+      <c r="F697">
+        <v>1</v>
+      </c>
+      <c r="G697" t="s">
+        <v>41</v>
+      </c>
+      <c r="H697" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>164</v>
+      </c>
+      <c r="B698" t="s">
+        <v>67</v>
+      </c>
+      <c r="C698" t="s">
+        <v>68</v>
+      </c>
+      <c r="D698" t="s">
+        <v>41</v>
+      </c>
+      <c r="E698">
+        <v>2</v>
+      </c>
+      <c r="F698">
+        <v>1</v>
+      </c>
+      <c r="G698" t="s">
+        <v>94</v>
+      </c>
+      <c r="H698" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>164</v>
+      </c>
+      <c r="B699" t="s">
+        <v>67</v>
+      </c>
+      <c r="C699" t="s">
+        <v>69</v>
+      </c>
+      <c r="D699" t="s">
+        <v>47</v>
+      </c>
+      <c r="E699">
+        <v>1</v>
+      </c>
+      <c r="F699">
+        <v>0</v>
+      </c>
+      <c r="G699" t="s">
+        <v>17</v>
+      </c>
+      <c r="H699" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="700" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>164</v>
+      </c>
+      <c r="B700" t="s">
+        <v>67</v>
+      </c>
+      <c r="C700" t="s">
+        <v>70</v>
+      </c>
+      <c r="D700" t="s">
+        <v>20</v>
+      </c>
+      <c r="E700">
+        <v>3</v>
+      </c>
+      <c r="F700">
+        <v>1</v>
+      </c>
+      <c r="G700" t="s">
+        <v>53</v>
+      </c>
+      <c r="H700" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="701" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>164</v>
+      </c>
+      <c r="B701" t="s">
+        <v>67</v>
+      </c>
+      <c r="C701" t="s">
+        <v>71</v>
+      </c>
+      <c r="D701" t="s">
+        <v>23</v>
+      </c>
+      <c r="E701">
+        <v>1</v>
+      </c>
+      <c r="F701">
+        <v>2</v>
+      </c>
+      <c r="G701" t="s">
+        <v>56</v>
+      </c>
+      <c r="H701" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="702" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>164</v>
+      </c>
+      <c r="B702" t="s">
+        <v>72</v>
+      </c>
+      <c r="C702" t="s">
+        <v>73</v>
+      </c>
+      <c r="D702" t="s">
+        <v>41</v>
+      </c>
+      <c r="E702">
+        <v>2</v>
+      </c>
+      <c r="F702">
+        <v>1</v>
+      </c>
+      <c r="G702" t="s">
+        <v>47</v>
+      </c>
+      <c r="H702" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="703" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>164</v>
+      </c>
+      <c r="B703" t="s">
+        <v>72</v>
+      </c>
+      <c r="C703" t="s">
+        <v>74</v>
+      </c>
+      <c r="D703" t="s">
+        <v>161</v>
+      </c>
+      <c r="E703">
+        <v>2</v>
+      </c>
+      <c r="F703">
+        <v>3</v>
+      </c>
+      <c r="G703" t="s">
         <v>92</v>
       </c>
-      <c r="H673" t="s">
+      <c r="H703" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>164</v>
+      </c>
+      <c r="B704" t="s">
+        <v>75</v>
+      </c>
+      <c r="C704" t="s">
+        <v>76</v>
+      </c>
+      <c r="D704" t="s">
+        <v>47</v>
+      </c>
+      <c r="E704">
+        <v>0</v>
+      </c>
+      <c r="F704">
+        <v>1</v>
+      </c>
+      <c r="G704" t="s">
+        <v>161</v>
+      </c>
+      <c r="H704" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>164</v>
+      </c>
+      <c r="B705" t="s">
+        <v>77</v>
+      </c>
+      <c r="C705" t="s">
+        <v>78</v>
+      </c>
+      <c r="D705" t="s">
+        <v>41</v>
+      </c>
+      <c r="E705">
+        <v>0</v>
+      </c>
+      <c r="F705">
+        <v>2</v>
+      </c>
+      <c r="G705" t="s">
+        <v>92</v>
+      </c>
+      <c r="H705" t="s">
         <v>56</v>
       </c>
     </row>

--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$865</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5126" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5134" uniqueCount="162">
   <si>
     <t>Participante</t>
   </si>
@@ -339,9 +342,6 @@
     <t>GIOVANNY CRUZ</t>
   </si>
   <si>
-    <t>Belgica/Senegal</t>
-  </si>
-  <si>
     <t>Australia/Egipto</t>
   </si>
   <si>
@@ -495,9 +495,6 @@
     <t>Denilson Alvarez</t>
   </si>
   <si>
-    <t>paraguay</t>
-  </si>
-  <si>
     <t>Víctor Ardila</t>
   </si>
   <si>
@@ -508,6 +505,9 @@
   </si>
   <si>
     <t>NOruega</t>
+  </si>
+  <si>
+    <t>ARgentina</t>
   </si>
 </sst>
 </file>
@@ -949,7 +949,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -1299,12 +1299,12 @@
         <v>51</v>
       </c>
       <c r="H15" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
         <v>58</v>
@@ -1374,7 +1374,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
         <v>12</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
         <v>58</v>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
@@ -1420,10 +1420,10 @@
         <v>20</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s">
         <v>36</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B21" t="s">
         <v>58</v>
@@ -1449,18 +1449,18 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="s">
         <v>48</v>
       </c>
       <c r="H21" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s">
         <v>58</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s">
         <v>58</v>
@@ -1495,24 +1495,24 @@
         <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" t="s">
         <v>53</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
@@ -1524,21 +1524,21 @@
         <v>44</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s">
         <v>58</v>
@@ -1546,25 +1546,22 @@
       <c r="C25" t="s">
         <v>66</v>
       </c>
-      <c r="D25" t="s">
-        <v>38</v>
-      </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="s">
         <v>41</v>
       </c>
       <c r="H25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -1573,15 +1570,24 @@
         <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
       </c>
+      <c r="H26" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
         <v>67</v>
@@ -1590,15 +1596,24 @@
         <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
       </c>
       <c r="G27" t="s">
         <v>17</v>
       </c>
+      <c r="H27" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
         <v>67</v>
@@ -1609,13 +1624,22 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>53</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
@@ -1626,13 +1650,22 @@
       <c r="D29" t="s">
         <v>23</v>
       </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
       <c r="G29" t="s">
         <v>56</v>
       </c>
+      <c r="H29" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
         <v>72</v>
@@ -1641,15 +1674,24 @@
         <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>41</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>118</v>
+        <v>47</v>
+      </c>
+      <c r="H30" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
         <v>72</v>
@@ -1658,15 +1700,24 @@
         <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>20</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>120</v>
+        <v>23</v>
+      </c>
+      <c r="H31" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
         <v>75</v>
@@ -1675,15 +1726,24 @@
         <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>47</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>122</v>
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
         <v>77</v>
@@ -1692,10 +1752,19 @@
         <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>41</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>124</v>
+        <v>23</v>
+      </c>
+      <c r="H33" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -4196,7 +4265,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>9</v>
@@ -4216,7 +4285,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>9</v>
@@ -4236,7 +4305,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>9</v>
@@ -4262,7 +4331,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>9</v>
@@ -4282,7 +4351,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>9</v>
@@ -4308,7 +4377,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>9</v>
@@ -4334,7 +4403,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>9</v>
@@ -4360,7 +4429,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>9</v>
@@ -4386,7 +4455,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>9</v>
@@ -4412,7 +4481,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>9</v>
@@ -4432,7 +4501,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>9</v>
@@ -4458,7 +4527,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>9</v>
@@ -4484,7 +4553,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>9</v>
@@ -4510,7 +4579,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>9</v>
@@ -4536,7 +4605,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>9</v>
@@ -4562,7 +4631,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>9</v>
@@ -4588,7 +4657,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>58</v>
@@ -4614,7 +4683,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>58</v>
@@ -4640,7 +4709,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>58</v>
@@ -4666,7 +4735,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>58</v>
@@ -4692,7 +4761,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>58</v>
@@ -4718,7 +4787,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>58</v>
@@ -4744,7 +4813,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>58</v>
@@ -4770,7 +4839,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>58</v>
@@ -4778,9 +4847,7 @@
       <c r="C153" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D153" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="D153" s="5"/>
       <c r="E153" s="3">
         <v>0</v>
       </c>
@@ -4796,7 +4863,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>67</v>
@@ -4822,7 +4889,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>67</v>
@@ -4848,7 +4915,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>67</v>
@@ -4874,7 +4941,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>67</v>
@@ -4900,7 +4967,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>72</v>
@@ -4926,7 +4993,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>72</v>
@@ -4952,7 +5019,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>75</v>
@@ -4978,7 +5045,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>77</v>
@@ -6668,7 +6735,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B226" t="s">
         <v>9</v>
@@ -6694,7 +6761,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B227" t="s">
         <v>9</v>
@@ -6720,7 +6787,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B228" t="s">
         <v>9</v>
@@ -6746,7 +6813,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B229" t="s">
         <v>9</v>
@@ -6772,7 +6839,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B230" t="s">
         <v>9</v>
@@ -6798,7 +6865,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B231" t="s">
         <v>9</v>
@@ -6824,7 +6891,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B232" t="s">
         <v>9</v>
@@ -6850,7 +6917,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B233" t="s">
         <v>9</v>
@@ -6871,12 +6938,12 @@
         <v>33</v>
       </c>
       <c r="H233" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B234" t="s">
         <v>9</v>
@@ -6902,7 +6969,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B235" t="s">
         <v>9</v>
@@ -6928,7 +6995,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B236" t="s">
         <v>9</v>
@@ -6954,7 +7021,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B237" t="s">
         <v>9</v>
@@ -6980,7 +7047,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B238" t="s">
         <v>9</v>
@@ -7006,7 +7073,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B239" t="s">
         <v>9</v>
@@ -7032,7 +7099,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B240" t="s">
         <v>9</v>
@@ -7058,7 +7125,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B241" t="s">
         <v>9</v>
@@ -7084,7 +7151,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B242" t="s">
         <v>58</v>
@@ -7110,7 +7177,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B243" t="s">
         <v>58</v>
@@ -7136,7 +7203,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B244" t="s">
         <v>58</v>
@@ -7162,7 +7229,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B245" t="s">
         <v>58</v>
@@ -7188,7 +7255,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B246" t="s">
         <v>58</v>
@@ -7214,7 +7281,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B247" t="s">
         <v>58</v>
@@ -7235,12 +7302,12 @@
         <v>53</v>
       </c>
       <c r="H247" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B248" t="s">
         <v>58</v>
@@ -7266,7 +7333,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B249" t="s">
         <v>58</v>
@@ -7292,7 +7359,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B250" t="s">
         <v>67</v>
@@ -7318,7 +7385,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B251" t="s">
         <v>67</v>
@@ -7344,7 +7411,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B252" t="s">
         <v>67</v>
@@ -7362,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H252" t="s">
         <v>20</v>
@@ -7370,7 +7437,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B253" t="s">
         <v>67</v>
@@ -7396,7 +7463,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B254" t="s">
         <v>72</v>
@@ -7422,7 +7489,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B255" t="s">
         <v>72</v>
@@ -7448,7 +7515,7 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B256" t="s">
         <v>75</v>
@@ -7474,7 +7541,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B257" t="s">
         <v>77</v>
@@ -7500,7 +7567,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B258" t="s">
         <v>9</v>
@@ -7517,7 +7584,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B259" t="s">
         <v>9</v>
@@ -7543,7 +7610,7 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B260" t="s">
         <v>9</v>
@@ -7569,7 +7636,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B261" t="s">
         <v>9</v>
@@ -7595,7 +7662,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B262" t="s">
         <v>9</v>
@@ -7621,7 +7688,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B263" t="s">
         <v>9</v>
@@ -7647,7 +7714,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B264" t="s">
         <v>9</v>
@@ -7673,7 +7740,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B265" t="s">
         <v>9</v>
@@ -7699,7 +7766,7 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B266" t="s">
         <v>9</v>
@@ -7720,12 +7787,12 @@
         <v>36</v>
       </c>
       <c r="H266" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B267" t="s">
         <v>9</v>
@@ -7742,7 +7809,7 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B268" t="s">
         <v>9</v>
@@ -7768,7 +7835,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B269" t="s">
         <v>9</v>
@@ -7794,7 +7861,7 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B270" t="s">
         <v>9</v>
@@ -7820,7 +7887,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B271" t="s">
         <v>9</v>
@@ -7846,7 +7913,7 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B272" t="s">
         <v>9</v>
@@ -7872,7 +7939,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B273" t="s">
         <v>9</v>
@@ -7898,7 +7965,7 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B274" t="s">
         <v>58</v>
@@ -7924,7 +7991,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B275" t="s">
         <v>58</v>
@@ -7950,7 +8017,7 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B276" t="s">
         <v>58</v>
@@ -7976,7 +8043,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B277" t="s">
         <v>58</v>
@@ -8002,7 +8069,7 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B278" t="s">
         <v>58</v>
@@ -8028,7 +8095,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B279" t="s">
         <v>58</v>
@@ -8054,7 +8121,7 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B280" t="s">
         <v>58</v>
@@ -8080,7 +8147,7 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B281" t="s">
         <v>58</v>
@@ -8106,7 +8173,7 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B282" t="s">
         <v>67</v>
@@ -8124,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="G282" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H282" t="s">
         <v>41</v>
@@ -8132,7 +8199,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B283" t="s">
         <v>67</v>
@@ -8158,7 +8225,7 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B284" t="s">
         <v>67</v>
@@ -8184,7 +8251,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B285" t="s">
         <v>67</v>
@@ -8210,7 +8277,7 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B286" t="s">
         <v>72</v>
@@ -8236,7 +8303,7 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B287" t="s">
         <v>72</v>
@@ -8262,7 +8329,7 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B288" t="s">
         <v>75</v>
@@ -8288,7 +8355,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B289" t="s">
         <v>77</v>
@@ -8314,7 +8381,7 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B290" t="s">
         <v>9</v>
@@ -8340,7 +8407,7 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B291" t="s">
         <v>9</v>
@@ -8366,7 +8433,7 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B292" t="s">
         <v>9</v>
@@ -8392,7 +8459,7 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B293" t="s">
         <v>9</v>
@@ -8418,7 +8485,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B294" t="s">
         <v>9</v>
@@ -8444,7 +8511,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B295" t="s">
         <v>9</v>
@@ -8470,7 +8537,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B296" t="s">
         <v>9</v>
@@ -8496,7 +8563,7 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B297" t="s">
         <v>9</v>
@@ -8522,7 +8589,7 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B298" t="s">
         <v>9</v>
@@ -8548,7 +8615,7 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B299" t="s">
         <v>9</v>
@@ -8574,7 +8641,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B300" t="s">
         <v>9</v>
@@ -8600,7 +8667,7 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B301" t="s">
         <v>9</v>
@@ -8626,7 +8693,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B302" t="s">
         <v>9</v>
@@ -8652,7 +8719,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B303" t="s">
         <v>9</v>
@@ -8678,7 +8745,7 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B304" t="s">
         <v>9</v>
@@ -8704,7 +8771,7 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B305" t="s">
         <v>9</v>
@@ -8730,7 +8797,7 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B306" t="s">
         <v>58</v>
@@ -8756,7 +8823,7 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B307" t="s">
         <v>58</v>
@@ -8782,7 +8849,7 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B308" t="s">
         <v>58</v>
@@ -8808,7 +8875,7 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B309" t="s">
         <v>58</v>
@@ -8834,7 +8901,7 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B310" t="s">
         <v>58</v>
@@ -8860,7 +8927,7 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B311" t="s">
         <v>58</v>
@@ -8869,7 +8936,7 @@
         <v>64</v>
       </c>
       <c r="D311" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E311">
         <v>1</v>
@@ -8886,7 +8953,7 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B312" t="s">
         <v>58</v>
@@ -8912,7 +8979,7 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B313" t="s">
         <v>58</v>
@@ -8938,7 +9005,7 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B314" t="s">
         <v>67</v>
@@ -8964,7 +9031,7 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B315" t="s">
         <v>67</v>
@@ -8990,7 +9057,7 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B316" t="s">
         <v>67</v>
@@ -9016,7 +9083,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B317" t="s">
         <v>67</v>
@@ -9042,7 +9109,7 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B318" t="s">
         <v>72</v>
@@ -9068,7 +9135,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B319" t="s">
         <v>72</v>
@@ -9094,7 +9161,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B320" t="s">
         <v>75</v>
@@ -9120,7 +9187,7 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B321" t="s">
         <v>77</v>
@@ -9146,7 +9213,7 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B322" t="s">
         <v>9</v>
@@ -9172,7 +9239,7 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B323" t="s">
         <v>9</v>
@@ -9198,7 +9265,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B324" t="s">
         <v>9</v>
@@ -9224,7 +9291,7 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B325" t="s">
         <v>9</v>
@@ -9250,7 +9317,7 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B326" t="s">
         <v>9</v>
@@ -9276,7 +9343,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B327" t="s">
         <v>9</v>
@@ -9302,7 +9369,7 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B328" t="s">
         <v>9</v>
@@ -9325,7 +9392,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B329" t="s">
         <v>9</v>
@@ -9351,7 +9418,7 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B330" t="s">
         <v>9</v>
@@ -9377,7 +9444,7 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B331" t="s">
         <v>9</v>
@@ -9403,7 +9470,7 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B332" t="s">
         <v>9</v>
@@ -9429,7 +9496,7 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B333" t="s">
         <v>9</v>
@@ -9452,7 +9519,7 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B334" t="s">
         <v>9</v>
@@ -9478,7 +9545,7 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B335" t="s">
         <v>9</v>
@@ -9504,7 +9571,7 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B336" t="s">
         <v>9</v>
@@ -9530,7 +9597,7 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B337" t="s">
         <v>9</v>
@@ -9556,7 +9623,7 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B338" t="s">
         <v>58</v>
@@ -9568,12 +9635,12 @@
         <v>12</v>
       </c>
       <c r="G338" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B339" t="s">
         <v>58</v>
@@ -9590,7 +9657,7 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B340" t="s">
         <v>58</v>
@@ -9599,7 +9666,7 @@
         <v>61</v>
       </c>
       <c r="D340" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G340" t="s">
         <v>36</v>
@@ -9607,7 +9674,7 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B341" t="s">
         <v>58</v>
@@ -9619,12 +9686,12 @@
         <v>23</v>
       </c>
       <c r="G341" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B342" t="s">
         <v>58</v>
@@ -9641,7 +9708,7 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B343" t="s">
         <v>58</v>
@@ -9658,7 +9725,7 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B344" t="s">
         <v>58</v>
@@ -9667,7 +9734,7 @@
         <v>65</v>
       </c>
       <c r="D344" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G344" t="s">
         <v>47</v>
@@ -9675,7 +9742,7 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B345" t="s">
         <v>58</v>
@@ -9692,7 +9759,7 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B346" t="s">
         <v>67</v>
@@ -9701,15 +9768,15 @@
         <v>68</v>
       </c>
       <c r="D346" t="s">
+        <v>108</v>
+      </c>
+      <c r="G346" t="s">
         <v>109</v>
-      </c>
-      <c r="G346" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B347" t="s">
         <v>67</v>
@@ -9718,15 +9785,15 @@
         <v>69</v>
       </c>
       <c r="D347" t="s">
+        <v>110</v>
+      </c>
+      <c r="G347" t="s">
         <v>111</v>
-      </c>
-      <c r="G347" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B348" t="s">
         <v>67</v>
@@ -9735,15 +9802,15 @@
         <v>70</v>
       </c>
       <c r="D348" t="s">
+        <v>112</v>
+      </c>
+      <c r="G348" t="s">
         <v>113</v>
-      </c>
-      <c r="G348" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B349" t="s">
         <v>67</v>
@@ -9752,15 +9819,15 @@
         <v>71</v>
       </c>
       <c r="D349" t="s">
+        <v>114</v>
+      </c>
+      <c r="G349" t="s">
         <v>115</v>
-      </c>
-      <c r="G349" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B350" t="s">
         <v>72</v>
@@ -9769,15 +9836,15 @@
         <v>73</v>
       </c>
       <c r="D350" t="s">
+        <v>116</v>
+      </c>
+      <c r="G350" t="s">
         <v>117</v>
-      </c>
-      <c r="G350" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B351" t="s">
         <v>72</v>
@@ -9786,15 +9853,15 @@
         <v>74</v>
       </c>
       <c r="D351" t="s">
+        <v>118</v>
+      </c>
+      <c r="G351" t="s">
         <v>119</v>
-      </c>
-      <c r="G351" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B352" t="s">
         <v>75</v>
@@ -9803,15 +9870,15 @@
         <v>76</v>
       </c>
       <c r="D352" t="s">
+        <v>120</v>
+      </c>
+      <c r="G352" t="s">
         <v>121</v>
-      </c>
-      <c r="G352" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B353" t="s">
         <v>77</v>
@@ -9820,15 +9887,15 @@
         <v>78</v>
       </c>
       <c r="D353" t="s">
+        <v>122</v>
+      </c>
+      <c r="G353" t="s">
         <v>123</v>
-      </c>
-      <c r="G353" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B354" t="s">
         <v>9</v>
@@ -9854,7 +9921,7 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B355" t="s">
         <v>9</v>
@@ -9880,7 +9947,7 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B356" t="s">
         <v>9</v>
@@ -9906,7 +9973,7 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B357" t="s">
         <v>9</v>
@@ -9932,7 +9999,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B358" t="s">
         <v>9</v>
@@ -9958,7 +10025,7 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B359" t="s">
         <v>9</v>
@@ -9984,7 +10051,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B360" t="s">
         <v>9</v>
@@ -10010,7 +10077,7 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B361" t="s">
         <v>9</v>
@@ -10036,7 +10103,7 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B362" t="s">
         <v>9</v>
@@ -10062,7 +10129,7 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B363" t="s">
         <v>9</v>
@@ -10088,7 +10155,7 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B364" t="s">
         <v>9</v>
@@ -10114,7 +10181,7 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B365" t="s">
         <v>9</v>
@@ -10140,7 +10207,7 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B366" t="s">
         <v>9</v>
@@ -10166,7 +10233,7 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B367" t="s">
         <v>9</v>
@@ -10192,7 +10259,7 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B368" t="s">
         <v>9</v>
@@ -10218,7 +10285,7 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B369" t="s">
         <v>9</v>
@@ -10244,7 +10311,7 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B370" t="s">
         <v>58</v>
@@ -10270,7 +10337,7 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B371" t="s">
         <v>58</v>
@@ -10296,7 +10363,7 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B372" t="s">
         <v>58</v>
@@ -10322,7 +10389,7 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B373" t="s">
         <v>58</v>
@@ -10348,7 +10415,7 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B374" t="s">
         <v>58</v>
@@ -10374,7 +10441,7 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B375" t="s">
         <v>58</v>
@@ -10400,7 +10467,7 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B376" t="s">
         <v>58</v>
@@ -10426,7 +10493,7 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B377" t="s">
         <v>58</v>
@@ -10452,7 +10519,7 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B378" t="s">
         <v>67</v>
@@ -10478,7 +10545,7 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B379" t="s">
         <v>67</v>
@@ -10504,7 +10571,7 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B380" t="s">
         <v>67</v>
@@ -10530,7 +10597,7 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B381" t="s">
         <v>67</v>
@@ -10556,7 +10623,7 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B382" t="s">
         <v>72</v>
@@ -10582,7 +10649,7 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B383" t="s">
         <v>72</v>
@@ -10608,7 +10675,7 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B384" t="s">
         <v>75</v>
@@ -10634,7 +10701,7 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B385" t="s">
         <v>77</v>
@@ -10660,7 +10727,7 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B386" t="s">
         <v>9</v>
@@ -10686,7 +10753,7 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B387" t="s">
         <v>9</v>
@@ -10712,7 +10779,7 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B388" t="s">
         <v>9</v>
@@ -10738,7 +10805,7 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B389" t="s">
         <v>9</v>
@@ -10759,12 +10826,12 @@
         <v>21</v>
       </c>
       <c r="H389" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B390" t="s">
         <v>9</v>
@@ -10790,7 +10857,7 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B391" t="s">
         <v>9</v>
@@ -10811,12 +10878,12 @@
         <v>27</v>
       </c>
       <c r="H391" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B392" t="s">
         <v>9</v>
@@ -10842,7 +10909,7 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B393" t="s">
         <v>9</v>
@@ -10863,12 +10930,12 @@
         <v>33</v>
       </c>
       <c r="H393" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B394" t="s">
         <v>9</v>
@@ -10894,7 +10961,7 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B395" t="s">
         <v>9</v>
@@ -10920,7 +10987,7 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B396" t="s">
         <v>9</v>
@@ -10946,7 +11013,7 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B397" t="s">
         <v>9</v>
@@ -10972,7 +11039,7 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B398" t="s">
         <v>9</v>
@@ -10998,7 +11065,7 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B399" t="s">
         <v>9</v>
@@ -11024,7 +11091,7 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B400" t="s">
         <v>9</v>
@@ -11050,7 +11117,7 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B401" t="s">
         <v>9</v>
@@ -11076,7 +11143,7 @@
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B402" t="s">
         <v>58</v>
@@ -11102,7 +11169,7 @@
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B403" t="s">
         <v>58</v>
@@ -11123,12 +11190,12 @@
         <v>50</v>
       </c>
       <c r="H403" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B404" t="s">
         <v>58</v>
@@ -11154,7 +11221,7 @@
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B405" t="s">
         <v>58</v>
@@ -11180,7 +11247,7 @@
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B406" t="s">
         <v>58</v>
@@ -11206,7 +11273,7 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B407" t="s">
         <v>58</v>
@@ -11232,7 +11299,7 @@
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B408" t="s">
         <v>58</v>
@@ -11258,7 +11325,7 @@
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B409" t="s">
         <v>58</v>
@@ -11284,7 +11351,7 @@
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B410" t="s">
         <v>67</v>
@@ -11310,7 +11377,7 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B411" t="s">
         <v>67</v>
@@ -11336,7 +11403,7 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B412" t="s">
         <v>67</v>
@@ -11362,7 +11429,7 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B413" t="s">
         <v>67</v>
@@ -11388,7 +11455,7 @@
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B414" t="s">
         <v>72</v>
@@ -11414,7 +11481,7 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B415" t="s">
         <v>72</v>
@@ -11440,7 +11507,7 @@
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B416" t="s">
         <v>75</v>
@@ -11461,12 +11528,12 @@
         <v>20</v>
       </c>
       <c r="H416" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B417" t="s">
         <v>77</v>
@@ -11492,7 +11559,7 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B418" t="s">
         <v>9</v>
@@ -11518,7 +11585,7 @@
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B419" t="s">
         <v>9</v>
@@ -11544,7 +11611,7 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B420" t="s">
         <v>9</v>
@@ -11570,7 +11637,7 @@
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B421" t="s">
         <v>9</v>
@@ -11596,7 +11663,7 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B422" t="s">
         <v>9</v>
@@ -11622,7 +11689,7 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B423" t="s">
         <v>9</v>
@@ -11648,7 +11715,7 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B424" t="s">
         <v>9</v>
@@ -11674,7 +11741,7 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B425" t="s">
         <v>9</v>
@@ -11700,7 +11767,7 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B426" t="s">
         <v>9</v>
@@ -11726,7 +11793,7 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B427" t="s">
         <v>9</v>
@@ -11752,7 +11819,7 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B428" t="s">
         <v>9</v>
@@ -11778,7 +11845,7 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B429" t="s">
         <v>9</v>
@@ -11804,7 +11871,7 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B430" t="s">
         <v>9</v>
@@ -11830,7 +11897,7 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B431" t="s">
         <v>9</v>
@@ -11856,7 +11923,7 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B432" t="s">
         <v>9</v>
@@ -11882,7 +11949,7 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B433" t="s">
         <v>9</v>
@@ -11908,7 +11975,7 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B434" t="s">
         <v>58</v>
@@ -11934,7 +12001,7 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B435" t="s">
         <v>58</v>
@@ -11960,7 +12027,7 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B436" t="s">
         <v>58</v>
@@ -11986,7 +12053,7 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B437" t="s">
         <v>58</v>
@@ -12012,7 +12079,7 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B438" t="s">
         <v>58</v>
@@ -12038,7 +12105,7 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B439" t="s">
         <v>58</v>
@@ -12064,7 +12131,7 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B440" t="s">
         <v>58</v>
@@ -12090,7 +12157,7 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B441" t="s">
         <v>58</v>
@@ -12116,7 +12183,7 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B442" t="s">
         <v>67</v>
@@ -12142,7 +12209,7 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B443" t="s">
         <v>67</v>
@@ -12168,7 +12235,7 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B444" t="s">
         <v>67</v>
@@ -12194,7 +12261,7 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B445" t="s">
         <v>67</v>
@@ -12220,7 +12287,7 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B446" t="s">
         <v>72</v>
@@ -12246,7 +12313,7 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B447" t="s">
         <v>72</v>
@@ -12272,7 +12339,7 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B448" t="s">
         <v>75</v>
@@ -12298,7 +12365,7 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B449" t="s">
         <v>77</v>
@@ -12324,7 +12391,7 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B450" t="s">
         <v>9</v>
@@ -12350,7 +12417,7 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B451" t="s">
         <v>9</v>
@@ -12376,7 +12443,7 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B452" t="s">
         <v>9</v>
@@ -12402,7 +12469,7 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B453" t="s">
         <v>9</v>
@@ -12428,7 +12495,7 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B454" t="s">
         <v>9</v>
@@ -12454,7 +12521,7 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B455" t="s">
         <v>9</v>
@@ -12480,7 +12547,7 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B456" t="s">
         <v>9</v>
@@ -12506,7 +12573,7 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B457" t="s">
         <v>9</v>
@@ -12532,7 +12599,7 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B458" t="s">
         <v>9</v>
@@ -12558,7 +12625,7 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B459" t="s">
         <v>9</v>
@@ -12584,7 +12651,7 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B460" t="s">
         <v>9</v>
@@ -12610,7 +12677,7 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B461" t="s">
         <v>9</v>
@@ -12636,7 +12703,7 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B462" t="s">
         <v>9</v>
@@ -12662,7 +12729,7 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B463" t="s">
         <v>9</v>
@@ -12688,7 +12755,7 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B464" t="s">
         <v>9</v>
@@ -12714,7 +12781,7 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B465" t="s">
         <v>9</v>
@@ -12740,7 +12807,7 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B466" t="s">
         <v>58</v>
@@ -12766,7 +12833,7 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B467" t="s">
         <v>58</v>
@@ -12792,7 +12859,7 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B468" t="s">
         <v>58</v>
@@ -12818,7 +12885,7 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B469" t="s">
         <v>58</v>
@@ -12844,7 +12911,7 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B470" t="s">
         <v>58</v>
@@ -12870,7 +12937,7 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B471" t="s">
         <v>58</v>
@@ -12896,7 +12963,7 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B472" t="s">
         <v>58</v>
@@ -12922,7 +12989,7 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B473" t="s">
         <v>58</v>
@@ -12948,7 +13015,7 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B474" t="s">
         <v>67</v>
@@ -12974,7 +13041,7 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B475" t="s">
         <v>67</v>
@@ -13000,7 +13067,7 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B476" t="s">
         <v>67</v>
@@ -13026,7 +13093,7 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B477" t="s">
         <v>67</v>
@@ -13052,7 +13119,7 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B478" t="s">
         <v>72</v>
@@ -13078,7 +13145,7 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B479" t="s">
         <v>72</v>
@@ -13104,7 +13171,7 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B480" t="s">
         <v>75</v>
@@ -13130,7 +13197,7 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B481" t="s">
         <v>77</v>
@@ -13156,7 +13223,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B482" t="s">
         <v>9</v>
@@ -13173,7 +13240,7 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B483" t="s">
         <v>9</v>
@@ -13190,7 +13257,7 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B484" t="s">
         <v>9</v>
@@ -13216,7 +13283,7 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B485" t="s">
         <v>9</v>
@@ -13233,7 +13300,7 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B486" t="s">
         <v>9</v>
@@ -13259,7 +13326,7 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B487" t="s">
         <v>9</v>
@@ -13285,7 +13352,7 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B488" t="s">
         <v>9</v>
@@ -13311,7 +13378,7 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B489" t="s">
         <v>9</v>
@@ -13337,7 +13404,7 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B490" t="s">
         <v>9</v>
@@ -13363,7 +13430,7 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B491" t="s">
         <v>9</v>
@@ -13380,7 +13447,7 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B492" t="s">
         <v>9</v>
@@ -13406,7 +13473,7 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B493" t="s">
         <v>9</v>
@@ -13432,7 +13499,7 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B494" t="s">
         <v>9</v>
@@ -13458,7 +13525,7 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B495" t="s">
         <v>9</v>
@@ -13481,7 +13548,7 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B496" t="s">
         <v>9</v>
@@ -13507,7 +13574,7 @@
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B497" t="s">
         <v>9</v>
@@ -13533,7 +13600,7 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B498" t="s">
         <v>58</v>
@@ -13544,13 +13611,22 @@
       <c r="D498" t="s">
         <v>12</v>
       </c>
+      <c r="E498">
+        <v>1</v>
+      </c>
+      <c r="F498">
+        <v>3</v>
+      </c>
       <c r="G498" t="s">
         <v>15</v>
       </c>
+      <c r="H498" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B499" t="s">
         <v>58</v>
@@ -13561,13 +13637,19 @@
       <c r="D499" t="s">
         <v>17</v>
       </c>
-      <c r="G499" t="s">
-        <v>106</v>
+      <c r="E499">
+        <v>2</v>
+      </c>
+      <c r="F499">
+        <v>1</v>
+      </c>
+      <c r="H499" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B500" t="s">
         <v>58</v>
@@ -13578,13 +13660,19 @@
       <c r="D500" t="s">
         <v>20</v>
       </c>
+      <c r="E500">
+        <v>2</v>
+      </c>
+      <c r="F500">
+        <v>2</v>
+      </c>
       <c r="G500" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B501" t="s">
         <v>58</v>
@@ -13595,13 +13683,22 @@
       <c r="D501" t="s">
         <v>23</v>
       </c>
+      <c r="E501">
+        <v>2</v>
+      </c>
+      <c r="F501">
+        <v>1</v>
+      </c>
       <c r="G501" t="s">
         <v>30</v>
       </c>
+      <c r="H501" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B502" t="s">
         <v>58</v>
@@ -13612,13 +13709,22 @@
       <c r="D502" t="s">
         <v>26</v>
       </c>
+      <c r="E502">
+        <v>0</v>
+      </c>
+      <c r="F502">
+        <v>1</v>
+      </c>
       <c r="G502" t="s">
         <v>56</v>
       </c>
+      <c r="H502" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B503" t="s">
         <v>58</v>
@@ -13626,16 +13732,22 @@
       <c r="C503" t="s">
         <v>64</v>
       </c>
-      <c r="D503" t="s">
-        <v>33</v>
+      <c r="E503">
+        <v>1</v>
+      </c>
+      <c r="F503">
+        <v>3</v>
       </c>
       <c r="G503" t="s">
         <v>53</v>
       </c>
+      <c r="H503" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B504" t="s">
         <v>58</v>
@@ -13646,13 +13758,22 @@
       <c r="D504" t="s">
         <v>45</v>
       </c>
+      <c r="E504">
+        <v>1</v>
+      </c>
+      <c r="F504">
+        <v>2</v>
+      </c>
       <c r="G504" t="s">
         <v>47</v>
       </c>
+      <c r="H504" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B505" t="s">
         <v>58</v>
@@ -13660,16 +13781,22 @@
       <c r="C505" t="s">
         <v>66</v>
       </c>
-      <c r="D505" t="s">
-        <v>39</v>
+      <c r="E505">
+        <v>1</v>
+      </c>
+      <c r="F505">
+        <v>4</v>
       </c>
       <c r="G505" t="s">
         <v>41</v>
       </c>
+      <c r="H505" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B506" t="s">
         <v>67</v>
@@ -13678,15 +13805,15 @@
         <v>68</v>
       </c>
       <c r="D506" t="s">
+        <v>108</v>
+      </c>
+      <c r="G506" t="s">
         <v>109</v>
-      </c>
-      <c r="G506" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B507" t="s">
         <v>67</v>
@@ -13695,15 +13822,15 @@
         <v>69</v>
       </c>
       <c r="D507" t="s">
+        <v>110</v>
+      </c>
+      <c r="G507" t="s">
         <v>111</v>
-      </c>
-      <c r="G507" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B508" t="s">
         <v>67</v>
@@ -13712,15 +13839,15 @@
         <v>70</v>
       </c>
       <c r="D508" t="s">
+        <v>112</v>
+      </c>
+      <c r="G508" t="s">
         <v>113</v>
-      </c>
-      <c r="G508" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B509" t="s">
         <v>67</v>
@@ -13729,15 +13856,15 @@
         <v>71</v>
       </c>
       <c r="D509" t="s">
+        <v>114</v>
+      </c>
+      <c r="G509" t="s">
         <v>115</v>
-      </c>
-      <c r="G509" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B510" t="s">
         <v>72</v>
@@ -13746,15 +13873,15 @@
         <v>73</v>
       </c>
       <c r="D510" t="s">
+        <v>116</v>
+      </c>
+      <c r="G510" t="s">
         <v>117</v>
-      </c>
-      <c r="G510" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B511" t="s">
         <v>72</v>
@@ -13763,15 +13890,15 @@
         <v>74</v>
       </c>
       <c r="D511" t="s">
+        <v>118</v>
+      </c>
+      <c r="G511" t="s">
         <v>119</v>
-      </c>
-      <c r="G511" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B512" t="s">
         <v>75</v>
@@ -13780,15 +13907,15 @@
         <v>76</v>
       </c>
       <c r="D512" t="s">
+        <v>120</v>
+      </c>
+      <c r="G512" t="s">
         <v>121</v>
-      </c>
-      <c r="G512" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B513" t="s">
         <v>77</v>
@@ -13797,15 +13924,15 @@
         <v>78</v>
       </c>
       <c r="D513" t="s">
+        <v>122</v>
+      </c>
+      <c r="G513" t="s">
         <v>123</v>
-      </c>
-      <c r="G513" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B514" t="s">
         <v>9</v>
@@ -13831,7 +13958,7 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B515" t="s">
         <v>9</v>
@@ -13857,7 +13984,7 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B516" t="s">
         <v>9</v>
@@ -13883,7 +14010,7 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B517" t="s">
         <v>9</v>
@@ -13909,7 +14036,7 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B518" t="s">
         <v>9</v>
@@ -13935,7 +14062,7 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B519" t="s">
         <v>9</v>
@@ -13961,7 +14088,7 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B520" t="s">
         <v>9</v>
@@ -13987,7 +14114,7 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B521" t="s">
         <v>9</v>
@@ -14013,7 +14140,7 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B522" t="s">
         <v>9</v>
@@ -14039,7 +14166,7 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B523" t="s">
         <v>9</v>
@@ -14065,7 +14192,7 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B524" t="s">
         <v>9</v>
@@ -14091,7 +14218,7 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B525" t="s">
         <v>9</v>
@@ -14117,7 +14244,7 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B526" t="s">
         <v>9</v>
@@ -14143,7 +14270,7 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B527" t="s">
         <v>9</v>
@@ -14169,7 +14296,7 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B528" t="s">
         <v>9</v>
@@ -14195,7 +14322,7 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B529" t="s">
         <v>9</v>
@@ -14221,7 +14348,7 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B530" t="s">
         <v>58</v>
@@ -14247,7 +14374,7 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B531" t="s">
         <v>58</v>
@@ -14273,7 +14400,7 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B532" t="s">
         <v>58</v>
@@ -14299,7 +14426,7 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B533" t="s">
         <v>58</v>
@@ -14325,7 +14452,7 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B534" t="s">
         <v>58</v>
@@ -14351,7 +14478,7 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B535" t="s">
         <v>58</v>
@@ -14377,7 +14504,7 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B536" t="s">
         <v>58</v>
@@ -14403,7 +14530,7 @@
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B537" t="s">
         <v>58</v>
@@ -14429,7 +14556,7 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B538" t="s">
         <v>67</v>
@@ -14455,7 +14582,7 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B539" t="s">
         <v>67</v>
@@ -14481,7 +14608,7 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B540" t="s">
         <v>67</v>
@@ -14507,7 +14634,7 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B541" t="s">
         <v>67</v>
@@ -14533,7 +14660,7 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B542" t="s">
         <v>72</v>
@@ -14559,7 +14686,7 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B543" t="s">
         <v>72</v>
@@ -14585,7 +14712,7 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B544" t="s">
         <v>75</v>
@@ -14606,12 +14733,12 @@
         <v>56</v>
       </c>
       <c r="H544" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B545" t="s">
         <v>77</v>
@@ -14637,7 +14764,7 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B546" t="s">
         <v>9</v>
@@ -14654,7 +14781,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B547" t="s">
         <v>9</v>
@@ -14671,7 +14798,7 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B548" t="s">
         <v>9</v>
@@ -14697,7 +14824,7 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B549" t="s">
         <v>9</v>
@@ -14714,7 +14841,7 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B550" t="s">
         <v>9</v>
@@ -14740,7 +14867,7 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B551" t="s">
         <v>9</v>
@@ -14766,7 +14893,7 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B552" t="s">
         <v>9</v>
@@ -14792,7 +14919,7 @@
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B553" t="s">
         <v>9</v>
@@ -14809,7 +14936,7 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B554" t="s">
         <v>9</v>
@@ -14826,7 +14953,7 @@
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B555" t="s">
         <v>9</v>
@@ -14843,7 +14970,7 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B556" t="s">
         <v>9</v>
@@ -14860,7 +14987,7 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B557" t="s">
         <v>9</v>
@@ -14886,7 +15013,7 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B558" t="s">
         <v>9</v>
@@ -14912,7 +15039,7 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B559" t="s">
         <v>9</v>
@@ -14938,7 +15065,7 @@
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B560" t="s">
         <v>9</v>
@@ -14964,7 +15091,7 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B561" t="s">
         <v>9</v>
@@ -14990,7 +15117,7 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B562" t="s">
         <v>58</v>
@@ -15016,7 +15143,7 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B563" t="s">
         <v>58</v>
@@ -15042,7 +15169,7 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B564" t="s">
         <v>58</v>
@@ -15068,7 +15195,7 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B565" t="s">
         <v>58</v>
@@ -15094,7 +15221,7 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B566" t="s">
         <v>58</v>
@@ -15120,7 +15247,7 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B567" t="s">
         <v>58</v>
@@ -15129,7 +15256,7 @@
         <v>64</v>
       </c>
       <c r="D567" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E567">
         <v>1</v>
@@ -15146,7 +15273,7 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B568" t="s">
         <v>58</v>
@@ -15172,7 +15299,7 @@
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B569" t="s">
         <v>58</v>
@@ -15180,9 +15307,6 @@
       <c r="C569" t="s">
         <v>66</v>
       </c>
-      <c r="D569" t="s">
-        <v>39</v>
-      </c>
       <c r="E569">
         <v>1</v>
       </c>
@@ -15198,7 +15322,7 @@
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B570" t="s">
         <v>67</v>
@@ -15224,7 +15348,7 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B571" t="s">
         <v>67</v>
@@ -15250,7 +15374,7 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B572" t="s">
         <v>67</v>
@@ -15276,7 +15400,7 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B573" t="s">
         <v>67</v>
@@ -15302,7 +15426,7 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B574" t="s">
         <v>72</v>
@@ -15328,7 +15452,7 @@
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B575" t="s">
         <v>72</v>
@@ -15354,7 +15478,7 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B576" t="s">
         <v>75</v>
@@ -15380,7 +15504,7 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B577" t="s">
         <v>77</v>
@@ -15406,7 +15530,7 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B578" t="s">
         <v>9</v>
@@ -15432,7 +15556,7 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B579" t="s">
         <v>9</v>
@@ -15458,7 +15582,7 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B580" t="s">
         <v>9</v>
@@ -15484,7 +15608,7 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B581" t="s">
         <v>9</v>
@@ -15510,7 +15634,7 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B582" t="s">
         <v>9</v>
@@ -15536,7 +15660,7 @@
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B583" t="s">
         <v>9</v>
@@ -15562,7 +15686,7 @@
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B584" t="s">
         <v>9</v>
@@ -15588,7 +15712,7 @@
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B585" t="s">
         <v>9</v>
@@ -15614,7 +15738,7 @@
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B586" t="s">
         <v>9</v>
@@ -15640,7 +15764,7 @@
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B587" t="s">
         <v>9</v>
@@ -15666,7 +15790,7 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B588" t="s">
         <v>9</v>
@@ -15692,7 +15816,7 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B589" t="s">
         <v>9</v>
@@ -15718,7 +15842,7 @@
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B590" t="s">
         <v>9</v>
@@ -15744,7 +15868,7 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B591" t="s">
         <v>9</v>
@@ -15770,7 +15894,7 @@
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B592" t="s">
         <v>9</v>
@@ -15796,7 +15920,7 @@
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B593" t="s">
         <v>9</v>
@@ -15822,7 +15946,7 @@
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B594" t="s">
         <v>58</v>
@@ -15848,7 +15972,7 @@
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B595" t="s">
         <v>58</v>
@@ -15874,7 +15998,7 @@
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B596" t="s">
         <v>58</v>
@@ -15900,7 +16024,7 @@
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B597" t="s">
         <v>58</v>
@@ -15926,7 +16050,7 @@
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B598" t="s">
         <v>58</v>
@@ -15952,7 +16076,7 @@
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B599" t="s">
         <v>58</v>
@@ -15961,7 +16085,7 @@
         <v>64</v>
       </c>
       <c r="D599" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E599">
         <v>1</v>
@@ -15978,7 +16102,7 @@
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B600" t="s">
         <v>58</v>
@@ -16004,7 +16128,7 @@
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B601" t="s">
         <v>58</v>
@@ -16030,7 +16154,7 @@
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B602" t="s">
         <v>67</v>
@@ -16056,7 +16180,7 @@
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B603" t="s">
         <v>67</v>
@@ -16082,7 +16206,7 @@
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B604" t="s">
         <v>67</v>
@@ -16108,7 +16232,7 @@
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B605" t="s">
         <v>67</v>
@@ -16134,7 +16258,7 @@
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B606" t="s">
         <v>72</v>
@@ -16160,7 +16284,7 @@
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B607" t="s">
         <v>72</v>
@@ -16186,7 +16310,7 @@
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B608" t="s">
         <v>75</v>
@@ -16212,7 +16336,7 @@
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B609" t="s">
         <v>77</v>
@@ -16238,7 +16362,7 @@
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B610" t="s">
         <v>9</v>
@@ -16264,7 +16388,7 @@
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B611" t="s">
         <v>9</v>
@@ -16290,7 +16414,7 @@
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B612" t="s">
         <v>9</v>
@@ -16316,7 +16440,7 @@
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B613" t="s">
         <v>9</v>
@@ -16342,7 +16466,7 @@
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B614" t="s">
         <v>9</v>
@@ -16368,7 +16492,7 @@
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B615" t="s">
         <v>9</v>
@@ -16394,7 +16518,7 @@
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B616" t="s">
         <v>9</v>
@@ -16420,7 +16544,7 @@
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B617" t="s">
         <v>9</v>
@@ -16446,7 +16570,7 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B618" t="s">
         <v>9</v>
@@ -16472,7 +16596,7 @@
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B619" t="s">
         <v>9</v>
@@ -16498,7 +16622,7 @@
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B620" t="s">
         <v>9</v>
@@ -16524,7 +16648,7 @@
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B621" t="s">
         <v>9</v>
@@ -16550,7 +16674,7 @@
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B622" t="s">
         <v>9</v>
@@ -16576,7 +16700,7 @@
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B623" t="s">
         <v>9</v>
@@ -16602,7 +16726,7 @@
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B624" t="s">
         <v>9</v>
@@ -16628,7 +16752,7 @@
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -16654,7 +16778,7 @@
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B626" t="s">
         <v>58</v>
@@ -16680,7 +16804,7 @@
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B627" t="s">
         <v>58</v>
@@ -16706,7 +16830,7 @@
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B628" t="s">
         <v>58</v>
@@ -16732,7 +16856,7 @@
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B629" t="s">
         <v>58</v>
@@ -16758,7 +16882,7 @@
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B630" t="s">
         <v>58</v>
@@ -16784,7 +16908,7 @@
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B631" t="s">
         <v>58</v>
@@ -16810,7 +16934,7 @@
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B632" t="s">
         <v>58</v>
@@ -16836,7 +16960,7 @@
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B633" t="s">
         <v>58</v>
@@ -16862,7 +16986,7 @@
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B634" t="s">
         <v>67</v>
@@ -16888,7 +17012,7 @@
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B635" t="s">
         <v>67</v>
@@ -16914,7 +17038,7 @@
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B636" t="s">
         <v>67</v>
@@ -16940,7 +17064,7 @@
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B637" t="s">
         <v>67</v>
@@ -16966,10 +17090,10 @@
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
+        <v>138</v>
+      </c>
+      <c r="B638" t="s">
         <v>139</v>
-      </c>
-      <c r="B638" t="s">
-        <v>140</v>
       </c>
       <c r="C638" t="s">
         <v>73</v>
@@ -16992,10 +17116,10 @@
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
+        <v>138</v>
+      </c>
+      <c r="B639" t="s">
         <v>139</v>
-      </c>
-      <c r="B639" t="s">
-        <v>140</v>
       </c>
       <c r="C639" t="s">
         <v>74</v>
@@ -17018,7 +17142,7 @@
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B640" t="s">
         <v>75</v>
@@ -17044,7 +17168,7 @@
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B641" t="s">
         <v>77</v>
@@ -17070,7 +17194,7 @@
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B642" t="s">
         <v>9</v>
@@ -17096,7 +17220,7 @@
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B643" t="s">
         <v>9</v>
@@ -17122,7 +17246,7 @@
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B644" t="s">
         <v>9</v>
@@ -17148,7 +17272,7 @@
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B645" t="s">
         <v>9</v>
@@ -17174,7 +17298,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B646" t="s">
         <v>9</v>
@@ -17200,7 +17324,7 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B647" t="s">
         <v>9</v>
@@ -17226,7 +17350,7 @@
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B648" t="s">
         <v>9</v>
@@ -17252,7 +17376,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B649" t="s">
         <v>9</v>
@@ -17278,7 +17402,7 @@
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B650" t="s">
         <v>9</v>
@@ -17304,7 +17428,7 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B651" t="s">
         <v>9</v>
@@ -17330,7 +17454,7 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B652" t="s">
         <v>9</v>
@@ -17356,7 +17480,7 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B653" t="s">
         <v>9</v>
@@ -17382,7 +17506,7 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B654" t="s">
         <v>9</v>
@@ -17408,7 +17532,7 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B655" t="s">
         <v>9</v>
@@ -17434,7 +17558,7 @@
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B656" t="s">
         <v>9</v>
@@ -17460,7 +17584,7 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B657" t="s">
         <v>9</v>
@@ -17486,7 +17610,7 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B658" t="s">
         <v>58</v>
@@ -17512,7 +17636,7 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B659" t="s">
         <v>58</v>
@@ -17538,7 +17662,7 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B660" t="s">
         <v>58</v>
@@ -17564,7 +17688,7 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B661" t="s">
         <v>58</v>
@@ -17590,7 +17714,7 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B662" t="s">
         <v>58</v>
@@ -17616,7 +17740,7 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B663" t="s">
         <v>58</v>
@@ -17642,7 +17766,7 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B664" t="s">
         <v>58</v>
@@ -17668,7 +17792,7 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B665" t="s">
         <v>58</v>
@@ -17677,7 +17801,7 @@
         <v>66</v>
       </c>
       <c r="D665" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E665">
         <v>1</v>
@@ -17694,7 +17818,7 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B666" t="s">
         <v>67</v>
@@ -17720,7 +17844,7 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B667" t="s">
         <v>67</v>
@@ -17746,7 +17870,7 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B668" t="s">
         <v>67</v>
@@ -17772,7 +17896,7 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B669" t="s">
         <v>67</v>
@@ -17798,7 +17922,7 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B670" t="s">
         <v>72</v>
@@ -17824,7 +17948,7 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B671" t="s">
         <v>72</v>
@@ -17850,7 +17974,7 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B672" t="s">
         <v>75</v>
@@ -17876,7 +18000,7 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B673" t="s">
         <v>77</v>
@@ -17902,7 +18026,7 @@
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B674" t="s">
         <v>9</v>
@@ -17928,7 +18052,7 @@
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B675" t="s">
         <v>9</v>
@@ -17954,7 +18078,7 @@
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B676" t="s">
         <v>9</v>
@@ -17980,7 +18104,7 @@
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B677" t="s">
         <v>9</v>
@@ -18006,7 +18130,7 @@
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B678" t="s">
         <v>9</v>
@@ -18032,7 +18156,7 @@
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B679" t="s">
         <v>9</v>
@@ -18058,7 +18182,7 @@
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B680" t="s">
         <v>9</v>
@@ -18084,7 +18208,7 @@
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B681" t="s">
         <v>9</v>
@@ -18110,7 +18234,7 @@
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B682" t="s">
         <v>9</v>
@@ -18136,7 +18260,7 @@
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B683" t="s">
         <v>9</v>
@@ -18162,7 +18286,7 @@
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B684" t="s">
         <v>9</v>
@@ -18188,7 +18312,7 @@
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B685" t="s">
         <v>9</v>
@@ -18214,7 +18338,7 @@
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B686" t="s">
         <v>9</v>
@@ -18240,7 +18364,7 @@
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B687" t="s">
         <v>9</v>
@@ -18266,7 +18390,7 @@
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B688" t="s">
         <v>9</v>
@@ -18292,7 +18416,7 @@
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B689" t="s">
         <v>9</v>
@@ -18318,7 +18442,7 @@
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B690" t="s">
         <v>58</v>
@@ -18344,7 +18468,7 @@
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B691" t="s">
         <v>58</v>
@@ -18370,7 +18494,7 @@
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B692" t="s">
         <v>58</v>
@@ -18396,7 +18520,7 @@
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B693" t="s">
         <v>58</v>
@@ -18422,7 +18546,7 @@
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B694" t="s">
         <v>58</v>
@@ -18448,7 +18572,7 @@
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B695" t="s">
         <v>58</v>
@@ -18474,7 +18598,7 @@
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B696" t="s">
         <v>58</v>
@@ -18500,7 +18624,7 @@
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B697" t="s">
         <v>58</v>
@@ -18526,7 +18650,7 @@
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B698" t="s">
         <v>67</v>
@@ -18552,7 +18676,7 @@
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B699" t="s">
         <v>67</v>
@@ -18578,7 +18702,7 @@
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B700" t="s">
         <v>67</v>
@@ -18604,7 +18728,7 @@
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B701" t="s">
         <v>67</v>
@@ -18630,7 +18754,7 @@
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B702" t="s">
         <v>72</v>
@@ -18656,7 +18780,7 @@
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B703" t="s">
         <v>72</v>
@@ -18682,7 +18806,7 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B704" t="s">
         <v>75</v>
@@ -18708,7 +18832,7 @@
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B705" t="s">
         <v>77</v>
@@ -18734,7 +18858,7 @@
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B706" t="s">
         <v>9</v>
@@ -18751,7 +18875,7 @@
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B707" t="s">
         <v>9</v>
@@ -18768,7 +18892,7 @@
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B708" t="s">
         <v>9</v>
@@ -18794,7 +18918,7 @@
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B709" t="s">
         <v>9</v>
@@ -18811,7 +18935,7 @@
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B710" t="s">
         <v>9</v>
@@ -18837,7 +18961,7 @@
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B711" t="s">
         <v>9</v>
@@ -18863,7 +18987,7 @@
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B712" t="s">
         <v>9</v>
@@ -18889,7 +19013,7 @@
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B713" t="s">
         <v>9</v>
@@ -18915,7 +19039,7 @@
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B714" t="s">
         <v>9</v>
@@ -18941,7 +19065,7 @@
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B715" t="s">
         <v>9</v>
@@ -18958,7 +19082,7 @@
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B716" t="s">
         <v>9</v>
@@ -18984,7 +19108,7 @@
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B717" t="s">
         <v>9</v>
@@ -19010,7 +19134,7 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B718" t="s">
         <v>9</v>
@@ -19036,7 +19160,7 @@
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B719" t="s">
         <v>9</v>
@@ -19062,7 +19186,7 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B720" t="s">
         <v>9</v>
@@ -19088,7 +19212,7 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B721" t="s">
         <v>9</v>
@@ -19114,7 +19238,7 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B722" t="s">
         <v>58</v>
@@ -19140,7 +19264,7 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B723" t="s">
         <v>58</v>
@@ -19166,7 +19290,7 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B724" t="s">
         <v>58</v>
@@ -19192,7 +19316,7 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B725" t="s">
         <v>58</v>
@@ -19218,7 +19342,7 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B726" t="s">
         <v>58</v>
@@ -19244,7 +19368,7 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B727" t="s">
         <v>58</v>
@@ -19253,7 +19377,7 @@
         <v>64</v>
       </c>
       <c r="D727" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E727">
         <v>1</v>
@@ -19270,7 +19394,7 @@
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B728" t="s">
         <v>58</v>
@@ -19296,7 +19420,7 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B729" t="s">
         <v>58</v>
@@ -19304,9 +19428,6 @@
       <c r="C729" t="s">
         <v>66</v>
       </c>
-      <c r="D729" t="s">
-        <v>158</v>
-      </c>
       <c r="E729">
         <v>1</v>
       </c>
@@ -19322,7 +19443,7 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B730" t="s">
         <v>67</v>
@@ -19348,7 +19469,7 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B731" t="s">
         <v>67</v>
@@ -19374,7 +19495,7 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B732" t="s">
         <v>67</v>
@@ -19400,7 +19521,7 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B733" t="s">
         <v>67</v>
@@ -19426,7 +19547,7 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B734" t="s">
         <v>72</v>
@@ -19452,7 +19573,7 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B735" t="s">
         <v>72</v>
@@ -19478,7 +19599,7 @@
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B736" t="s">
         <v>75</v>
@@ -19504,7 +19625,7 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B737" t="s">
         <v>77</v>
@@ -19530,7 +19651,7 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B738" t="s">
         <v>9</v>
@@ -19556,7 +19677,7 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B739" t="s">
         <v>9</v>
@@ -19582,7 +19703,7 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B740" t="s">
         <v>9</v>
@@ -19608,7 +19729,7 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B741" t="s">
         <v>9</v>
@@ -19634,7 +19755,7 @@
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B742" t="s">
         <v>9</v>
@@ -19660,7 +19781,7 @@
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B743" t="s">
         <v>9</v>
@@ -19686,7 +19807,7 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B744" t="s">
         <v>9</v>
@@ -19712,7 +19833,7 @@
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B745" t="s">
         <v>9</v>
@@ -19738,7 +19859,7 @@
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B746" t="s">
         <v>9</v>
@@ -19764,7 +19885,7 @@
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B747" t="s">
         <v>9</v>
@@ -19790,7 +19911,7 @@
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B748" t="s">
         <v>9</v>
@@ -19816,7 +19937,7 @@
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B749" t="s">
         <v>9</v>
@@ -19842,7 +19963,7 @@
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B750" t="s">
         <v>9</v>
@@ -19868,7 +19989,7 @@
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B751" t="s">
         <v>9</v>
@@ -19894,7 +20015,7 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B752" t="s">
         <v>9</v>
@@ -19920,7 +20041,7 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B753" t="s">
         <v>9</v>
@@ -19946,7 +20067,7 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B754" t="s">
         <v>58</v>
@@ -19972,7 +20093,7 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B755" t="s">
         <v>58</v>
@@ -19998,7 +20119,7 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B756" t="s">
         <v>58</v>
@@ -20016,7 +20137,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H756" t="s">
         <v>20</v>
@@ -20024,7 +20145,7 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B757" t="s">
         <v>58</v>
@@ -20050,7 +20171,7 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B758" t="s">
         <v>58</v>
@@ -20076,7 +20197,7 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B759" t="s">
         <v>58</v>
@@ -20102,7 +20223,7 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B760" t="s">
         <v>58</v>
@@ -20128,7 +20249,7 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B761" t="s">
         <v>58</v>
@@ -20154,7 +20275,7 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B762" t="s">
         <v>67</v>
@@ -20180,7 +20301,7 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B763" t="s">
         <v>67</v>
@@ -20206,7 +20327,7 @@
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B764" t="s">
         <v>67</v>
@@ -20232,7 +20353,7 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B765" t="s">
         <v>67</v>
@@ -20258,7 +20379,7 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B766" t="s">
         <v>72</v>
@@ -20284,7 +20405,7 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B767" t="s">
         <v>72</v>
@@ -20310,7 +20431,7 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B768" t="s">
         <v>75</v>
@@ -20336,7 +20457,7 @@
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B769" t="s">
         <v>77</v>
@@ -20362,7 +20483,7 @@
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B770" t="s">
         <v>9</v>
@@ -20379,7 +20500,7 @@
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B771" t="s">
         <v>9</v>
@@ -20400,12 +20521,12 @@
         <v>15</v>
       </c>
       <c r="H771" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B772" t="s">
         <v>9</v>
@@ -20426,12 +20547,12 @@
         <v>18</v>
       </c>
       <c r="H772" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B773" t="s">
         <v>9</v>
@@ -20452,12 +20573,12 @@
         <v>21</v>
       </c>
       <c r="H773" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B774" t="s">
         <v>9</v>
@@ -20483,7 +20604,7 @@
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B775" t="s">
         <v>9</v>
@@ -20504,12 +20625,12 @@
         <v>27</v>
       </c>
       <c r="H775" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B776" t="s">
         <v>9</v>
@@ -20535,7 +20656,7 @@
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B777" t="s">
         <v>9</v>
@@ -20556,12 +20677,12 @@
         <v>33</v>
       </c>
       <c r="H777" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B778" t="s">
         <v>9</v>
@@ -20587,7 +20708,7 @@
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B779" t="s">
         <v>9</v>
@@ -20613,7 +20734,7 @@
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B780" t="s">
         <v>9</v>
@@ -20639,7 +20760,7 @@
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B781" t="s">
         <v>9</v>
@@ -20660,12 +20781,12 @@
         <v>45</v>
       </c>
       <c r="H781" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B782" t="s">
         <v>9</v>
@@ -20691,7 +20812,7 @@
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B783" t="s">
         <v>9</v>
@@ -20712,12 +20833,12 @@
         <v>51</v>
       </c>
       <c r="H783" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B784" t="s">
         <v>9</v>
@@ -20743,7 +20864,7 @@
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B785" t="s">
         <v>9</v>
@@ -20769,7 +20890,7 @@
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B786" t="s">
         <v>58</v>
@@ -20787,15 +20908,15 @@
         <v>2</v>
       </c>
       <c r="G786" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H786" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B787" t="s">
         <v>58</v>
@@ -20816,12 +20937,12 @@
         <v>50</v>
       </c>
       <c r="H787" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B788" t="s">
         <v>58</v>
@@ -20847,7 +20968,7 @@
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B789" t="s">
         <v>58</v>
@@ -20873,7 +20994,7 @@
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B790" t="s">
         <v>58</v>
@@ -20899,7 +21020,7 @@
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B791" t="s">
         <v>58</v>
@@ -20925,7 +21046,7 @@
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B792" t="s">
         <v>58</v>
@@ -20951,7 +21072,7 @@
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B793" t="s">
         <v>58</v>
@@ -20977,7 +21098,7 @@
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B794" t="s">
         <v>67</v>
@@ -20995,7 +21116,7 @@
         <v>1</v>
       </c>
       <c r="G794" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H794" t="s">
         <v>89</v>
@@ -21003,7 +21124,7 @@
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B795" t="s">
         <v>67</v>
@@ -21021,7 +21142,7 @@
         <v>1</v>
       </c>
       <c r="G795" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H795" t="s">
         <v>83</v>
@@ -21029,7 +21150,7 @@
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B796" t="s">
         <v>67</v>
@@ -21055,7 +21176,7 @@
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B797" t="s">
         <v>67</v>
@@ -21081,7 +21202,7 @@
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B798" t="s">
         <v>72</v>
@@ -21107,7 +21228,7 @@
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B799" t="s">
         <v>72</v>
@@ -21133,7 +21254,7 @@
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B800" t="s">
         <v>75</v>
@@ -21159,7 +21280,7 @@
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B801" t="s">
         <v>77</v>
@@ -21185,7 +21306,7 @@
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B802" t="s">
         <v>9</v>
@@ -21211,7 +21332,7 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B803" t="s">
         <v>9</v>
@@ -21237,7 +21358,7 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B804" t="s">
         <v>9</v>
@@ -21263,7 +21384,7 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B805" t="s">
         <v>9</v>
@@ -21289,7 +21410,7 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B806" t="s">
         <v>9</v>
@@ -21315,7 +21436,7 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B807" t="s">
         <v>9</v>
@@ -21341,7 +21462,7 @@
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B808" t="s">
         <v>9</v>
@@ -21367,7 +21488,7 @@
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B809" t="s">
         <v>9</v>
@@ -21388,12 +21509,12 @@
         <v>33</v>
       </c>
       <c r="H809" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B810" t="s">
         <v>9</v>
@@ -21419,7 +21540,7 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B811" t="s">
         <v>9</v>
@@ -21445,7 +21566,7 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B812" t="s">
         <v>9</v>
@@ -21471,7 +21592,7 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B813" t="s">
         <v>9</v>
@@ -21497,7 +21618,7 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B814" t="s">
         <v>9</v>
@@ -21523,7 +21644,7 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B815" t="s">
         <v>9</v>
@@ -21549,7 +21670,7 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B816" t="s">
         <v>9</v>
@@ -21575,7 +21696,7 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B817" t="s">
         <v>9</v>
@@ -21601,7 +21722,7 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B818" t="s">
         <v>58</v>
@@ -21627,7 +21748,7 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B819" t="s">
         <v>58</v>
@@ -21648,12 +21769,12 @@
         <v>50</v>
       </c>
       <c r="H819" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B820" t="s">
         <v>58</v>
@@ -21679,7 +21800,7 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B821" t="s">
         <v>58</v>
@@ -21705,7 +21826,7 @@
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B822" t="s">
         <v>58</v>
@@ -21731,7 +21852,7 @@
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B823" t="s">
         <v>58</v>
@@ -21757,7 +21878,7 @@
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B824" t="s">
         <v>58</v>
@@ -21783,7 +21904,7 @@
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B825" t="s">
         <v>58</v>
@@ -21809,7 +21930,7 @@
     </row>
     <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B826" t="s">
         <v>67</v>
@@ -21835,7 +21956,7 @@
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B827" t="s">
         <v>67</v>
@@ -21861,7 +21982,7 @@
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B828" t="s">
         <v>67</v>
@@ -21887,7 +22008,7 @@
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B829" t="s">
         <v>67</v>
@@ -21913,7 +22034,7 @@
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B830" t="s">
         <v>72</v>
@@ -21939,7 +22060,7 @@
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B831" t="s">
         <v>72</v>
@@ -21965,7 +22086,7 @@
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B832" t="s">
         <v>75</v>
@@ -21991,7 +22112,7 @@
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B833" t="s">
         <v>77</v>
@@ -22017,7 +22138,7 @@
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B834" t="s">
         <v>9</v>
@@ -22043,7 +22164,7 @@
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B835" t="s">
         <v>9</v>
@@ -22069,7 +22190,7 @@
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B836" t="s">
         <v>9</v>
@@ -22095,7 +22216,7 @@
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B837" t="s">
         <v>9</v>
@@ -22121,7 +22242,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B838" t="s">
         <v>9</v>
@@ -22147,7 +22268,7 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B839" t="s">
         <v>9</v>
@@ -22173,7 +22294,7 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B840" t="s">
         <v>9</v>
@@ -22199,7 +22320,7 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B841" t="s">
         <v>9</v>
@@ -22225,7 +22346,7 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B842" t="s">
         <v>9</v>
@@ -22251,7 +22372,7 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B843" t="s">
         <v>9</v>
@@ -22277,7 +22398,7 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B844" t="s">
         <v>9</v>
@@ -22303,7 +22424,7 @@
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B845" t="s">
         <v>9</v>
@@ -22329,7 +22450,7 @@
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B846" t="s">
         <v>9</v>
@@ -22355,7 +22476,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B847" t="s">
         <v>9</v>
@@ -22381,7 +22502,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B848" t="s">
         <v>9</v>
@@ -22407,7 +22528,7 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B849" t="s">
         <v>9</v>
@@ -22433,7 +22554,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B850" t="s">
         <v>58</v>
@@ -22459,7 +22580,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B851" t="s">
         <v>58</v>
@@ -22485,7 +22606,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B852" t="s">
         <v>58</v>
@@ -22511,7 +22632,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B853" t="s">
         <v>58</v>
@@ -22537,7 +22658,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B854" t="s">
         <v>58</v>
@@ -22563,7 +22684,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B855" t="s">
         <v>58</v>
@@ -22589,7 +22710,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B856" t="s">
         <v>58</v>
@@ -22615,7 +22736,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B857" t="s">
         <v>58</v>
@@ -22641,7 +22762,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B858" t="s">
         <v>67</v>
@@ -22667,7 +22788,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B859" t="s">
         <v>67</v>
@@ -22693,7 +22814,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B860" t="s">
         <v>67</v>
@@ -22719,7 +22840,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B861" t="s">
         <v>67</v>
@@ -22745,7 +22866,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B862" t="s">
         <v>72</v>
@@ -22771,7 +22892,7 @@
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B863" t="s">
         <v>72</v>
@@ -22780,7 +22901,7 @@
         <v>74</v>
       </c>
       <c r="D863" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E863">
         <v>2</v>
@@ -22797,7 +22918,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B864" t="s">
         <v>75</v>
@@ -22815,7 +22936,7 @@
         <v>1</v>
       </c>
       <c r="G864" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H864" t="s">
         <v>20</v>
@@ -22823,7 +22944,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B865" t="s">
         <v>77</v>
@@ -22848,6 +22969,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H865"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5134" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5161" uniqueCount="146">
   <si>
     <t>Participante</t>
   </si>
@@ -342,60 +342,6 @@
     <t>GIOVANNY CRUZ</t>
   </si>
   <si>
-    <t>Australia/Egipto</t>
-  </si>
-  <si>
-    <t>Portugal/Croacia</t>
-  </si>
-  <si>
-    <t>Ganador Partido 24</t>
-  </si>
-  <si>
-    <t>Ganador Partido 17</t>
-  </si>
-  <si>
-    <t>Ganador Partido 23</t>
-  </si>
-  <si>
-    <t>Ganador Partido 18</t>
-  </si>
-  <si>
-    <t>Ganador Partido 19</t>
-  </si>
-  <si>
-    <t>Ganador Partido 22</t>
-  </si>
-  <si>
-    <t>Ganador Partido 20</t>
-  </si>
-  <si>
-    <t>Ganador Partido 21</t>
-  </si>
-  <si>
-    <t>Ganador Partido 25</t>
-  </si>
-  <si>
-    <t>Ganador Partido 26</t>
-  </si>
-  <si>
-    <t>Ganador Partido 27</t>
-  </si>
-  <si>
-    <t>Ganador Partido 28</t>
-  </si>
-  <si>
-    <t>Perdedor Partido 29</t>
-  </si>
-  <si>
-    <t>Perdedor Partido 30</t>
-  </si>
-  <si>
-    <t>Ganador Partido 29</t>
-  </si>
-  <si>
-    <t>Ganador Partido 30</t>
-  </si>
-  <si>
     <t>Guillermo Garzon</t>
   </si>
   <si>
@@ -509,12 +455,18 @@
   <si>
     <t>ARgentina</t>
   </si>
+  <si>
+    <t>Paises bajos</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,6 +509,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -594,7 +551,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -605,6 +562,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -949,7 +907,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -966,7 +924,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -992,7 +950,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -1018,7 +976,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1044,7 +1002,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1070,7 +1028,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1096,7 +1054,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1122,7 +1080,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -1148,7 +1106,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -1174,7 +1132,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -1200,7 +1158,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -1226,7 +1184,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -1252,7 +1210,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -1278,7 +1236,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -1304,7 +1262,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -1330,7 +1288,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -1356,7 +1314,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
         <v>58</v>
@@ -1382,7 +1340,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
         <v>58</v>
@@ -1408,7 +1366,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
@@ -1434,7 +1392,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
         <v>58</v>
@@ -1455,12 +1413,12 @@
         <v>48</v>
       </c>
       <c r="H21" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s">
         <v>58</v>
@@ -1486,7 +1444,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
         <v>58</v>
@@ -1495,7 +1453,7 @@
         <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1512,7 +1470,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
@@ -1538,7 +1496,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
         <v>58</v>
@@ -1561,7 +1519,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -1587,7 +1545,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
         <v>67</v>
@@ -1613,7 +1571,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
         <v>67</v>
@@ -1639,7 +1597,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
@@ -1665,7 +1623,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
         <v>72</v>
@@ -1691,7 +1649,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
         <v>72</v>
@@ -1717,7 +1675,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
         <v>75</v>
@@ -1743,7 +1701,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B33" t="s">
         <v>77</v>
@@ -4265,7 +4223,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>9</v>
@@ -4285,7 +4243,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>9</v>
@@ -4305,7 +4263,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>9</v>
@@ -4331,7 +4289,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>9</v>
@@ -4351,7 +4309,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>9</v>
@@ -4377,7 +4335,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>9</v>
@@ -4403,7 +4361,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>9</v>
@@ -4429,7 +4387,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>9</v>
@@ -4455,7 +4413,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>9</v>
@@ -4481,7 +4439,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>9</v>
@@ -4501,7 +4459,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>9</v>
@@ -4527,7 +4485,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>9</v>
@@ -4553,7 +4511,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>9</v>
@@ -4579,7 +4537,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>9</v>
@@ -4605,7 +4563,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>9</v>
@@ -4631,7 +4589,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>9</v>
@@ -4657,7 +4615,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>58</v>
@@ -4683,7 +4641,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>58</v>
@@ -4709,7 +4667,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>58</v>
@@ -4735,7 +4693,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>58</v>
@@ -4761,7 +4719,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>58</v>
@@ -4787,7 +4745,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>58</v>
@@ -4813,7 +4771,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>58</v>
@@ -4839,7 +4797,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>58</v>
@@ -4863,7 +4821,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>67</v>
@@ -4889,7 +4847,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>67</v>
@@ -4915,7 +4873,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>67</v>
@@ -4941,7 +4899,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>67</v>
@@ -4967,7 +4925,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>72</v>
@@ -4993,7 +4951,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>72</v>
@@ -5019,7 +4977,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>75</v>
@@ -5045,7 +5003,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>77</v>
@@ -6735,7 +6693,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B226" t="s">
         <v>9</v>
@@ -6761,7 +6719,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B227" t="s">
         <v>9</v>
@@ -6787,7 +6745,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B228" t="s">
         <v>9</v>
@@ -6813,7 +6771,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B229" t="s">
         <v>9</v>
@@ -6839,7 +6797,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B230" t="s">
         <v>9</v>
@@ -6865,7 +6823,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B231" t="s">
         <v>9</v>
@@ -6891,7 +6849,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B232" t="s">
         <v>9</v>
@@ -6917,7 +6875,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B233" t="s">
         <v>9</v>
@@ -6938,12 +6896,12 @@
         <v>33</v>
       </c>
       <c r="H233" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B234" t="s">
         <v>9</v>
@@ -6969,7 +6927,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B235" t="s">
         <v>9</v>
@@ -6995,7 +6953,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B236" t="s">
         <v>9</v>
@@ -7021,7 +6979,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B237" t="s">
         <v>9</v>
@@ -7047,7 +7005,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B238" t="s">
         <v>9</v>
@@ -7073,7 +7031,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B239" t="s">
         <v>9</v>
@@ -7099,7 +7057,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B240" t="s">
         <v>9</v>
@@ -7125,7 +7083,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B241" t="s">
         <v>9</v>
@@ -7151,7 +7109,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B242" t="s">
         <v>58</v>
@@ -7177,7 +7135,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B243" t="s">
         <v>58</v>
@@ -7203,7 +7161,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B244" t="s">
         <v>58</v>
@@ -7229,7 +7187,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B245" t="s">
         <v>58</v>
@@ -7255,7 +7213,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B246" t="s">
         <v>58</v>
@@ -7281,7 +7239,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B247" t="s">
         <v>58</v>
@@ -7302,12 +7260,12 @@
         <v>53</v>
       </c>
       <c r="H247" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B248" t="s">
         <v>58</v>
@@ -7333,7 +7291,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B249" t="s">
         <v>58</v>
@@ -7359,7 +7317,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B250" t="s">
         <v>67</v>
@@ -7385,7 +7343,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B251" t="s">
         <v>67</v>
@@ -7411,7 +7369,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B252" t="s">
         <v>67</v>
@@ -7429,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="H252" t="s">
         <v>20</v>
@@ -7437,7 +7395,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B253" t="s">
         <v>67</v>
@@ -7463,7 +7421,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B254" t="s">
         <v>72</v>
@@ -7489,7 +7447,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B255" t="s">
         <v>72</v>
@@ -7515,7 +7473,7 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B256" t="s">
         <v>75</v>
@@ -7541,7 +7499,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B257" t="s">
         <v>77</v>
@@ -7567,7 +7525,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B258" t="s">
         <v>9</v>
@@ -7584,7 +7542,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B259" t="s">
         <v>9</v>
@@ -7610,7 +7568,7 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B260" t="s">
         <v>9</v>
@@ -7636,7 +7594,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B261" t="s">
         <v>9</v>
@@ -7662,7 +7620,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B262" t="s">
         <v>9</v>
@@ -7688,7 +7646,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B263" t="s">
         <v>9</v>
@@ -7714,7 +7672,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B264" t="s">
         <v>9</v>
@@ -7740,7 +7698,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B265" t="s">
         <v>9</v>
@@ -7766,7 +7724,7 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B266" t="s">
         <v>9</v>
@@ -7787,12 +7745,12 @@
         <v>36</v>
       </c>
       <c r="H266" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B267" t="s">
         <v>9</v>
@@ -7809,7 +7767,7 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B268" t="s">
         <v>9</v>
@@ -7835,7 +7793,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B269" t="s">
         <v>9</v>
@@ -7861,7 +7819,7 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B270" t="s">
         <v>9</v>
@@ -7887,7 +7845,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B271" t="s">
         <v>9</v>
@@ -7913,7 +7871,7 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B272" t="s">
         <v>9</v>
@@ -7939,7 +7897,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B273" t="s">
         <v>9</v>
@@ -7965,7 +7923,7 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B274" t="s">
         <v>58</v>
@@ -7991,7 +7949,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B275" t="s">
         <v>58</v>
@@ -8017,7 +7975,7 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B276" t="s">
         <v>58</v>
@@ -8043,7 +8001,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B277" t="s">
         <v>58</v>
@@ -8069,7 +8027,7 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B278" t="s">
         <v>58</v>
@@ -8095,7 +8053,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B279" t="s">
         <v>58</v>
@@ -8121,7 +8079,7 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B280" t="s">
         <v>58</v>
@@ -8147,7 +8105,7 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B281" t="s">
         <v>58</v>
@@ -8173,7 +8131,7 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B282" t="s">
         <v>67</v>
@@ -8191,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="G282" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="H282" t="s">
         <v>41</v>
@@ -8199,7 +8157,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B283" t="s">
         <v>67</v>
@@ -8225,7 +8183,7 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B284" t="s">
         <v>67</v>
@@ -8251,7 +8209,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B285" t="s">
         <v>67</v>
@@ -8277,7 +8235,7 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B286" t="s">
         <v>72</v>
@@ -8303,7 +8261,7 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B287" t="s">
         <v>72</v>
@@ -8329,7 +8287,7 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B288" t="s">
         <v>75</v>
@@ -8355,7 +8313,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B289" t="s">
         <v>77</v>
@@ -8381,7 +8339,7 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B290" t="s">
         <v>9</v>
@@ -8407,7 +8365,7 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B291" t="s">
         <v>9</v>
@@ -8433,7 +8391,7 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B292" t="s">
         <v>9</v>
@@ -8459,7 +8417,7 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B293" t="s">
         <v>9</v>
@@ -8485,7 +8443,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B294" t="s">
         <v>9</v>
@@ -8511,7 +8469,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B295" t="s">
         <v>9</v>
@@ -8537,7 +8495,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B296" t="s">
         <v>9</v>
@@ -8563,7 +8521,7 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B297" t="s">
         <v>9</v>
@@ -8589,7 +8547,7 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B298" t="s">
         <v>9</v>
@@ -8615,7 +8573,7 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B299" t="s">
         <v>9</v>
@@ -8641,7 +8599,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B300" t="s">
         <v>9</v>
@@ -8667,7 +8625,7 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B301" t="s">
         <v>9</v>
@@ -8693,7 +8651,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B302" t="s">
         <v>9</v>
@@ -8719,7 +8677,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B303" t="s">
         <v>9</v>
@@ -8745,7 +8703,7 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B304" t="s">
         <v>9</v>
@@ -8771,7 +8729,7 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B305" t="s">
         <v>9</v>
@@ -8797,7 +8755,7 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B306" t="s">
         <v>58</v>
@@ -8823,7 +8781,7 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B307" t="s">
         <v>58</v>
@@ -8849,7 +8807,7 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B308" t="s">
         <v>58</v>
@@ -8875,7 +8833,7 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B309" t="s">
         <v>58</v>
@@ -8901,7 +8859,7 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B310" t="s">
         <v>58</v>
@@ -8927,7 +8885,7 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B311" t="s">
         <v>58</v>
@@ -8936,7 +8894,7 @@
         <v>64</v>
       </c>
       <c r="D311" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E311">
         <v>1</v>
@@ -8953,7 +8911,7 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B312" t="s">
         <v>58</v>
@@ -8979,7 +8937,7 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B313" t="s">
         <v>58</v>
@@ -9005,7 +8963,7 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B314" t="s">
         <v>67</v>
@@ -9031,7 +8989,7 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B315" t="s">
         <v>67</v>
@@ -9057,7 +9015,7 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B316" t="s">
         <v>67</v>
@@ -9083,7 +9041,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B317" t="s">
         <v>67</v>
@@ -9109,7 +9067,7 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B318" t="s">
         <v>72</v>
@@ -9135,7 +9093,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B319" t="s">
         <v>72</v>
@@ -9161,7 +9119,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B320" t="s">
         <v>75</v>
@@ -9187,7 +9145,7 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B321" t="s">
         <v>77</v>
@@ -9213,7 +9171,7 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B322" t="s">
         <v>9</v>
@@ -9239,7 +9197,7 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B323" t="s">
         <v>9</v>
@@ -9265,7 +9223,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B324" t="s">
         <v>9</v>
@@ -9291,7 +9249,7 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B325" t="s">
         <v>9</v>
@@ -9317,7 +9275,7 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B326" t="s">
         <v>9</v>
@@ -9343,7 +9301,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B327" t="s">
         <v>9</v>
@@ -9369,7 +9327,7 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B328" t="s">
         <v>9</v>
@@ -9392,7 +9350,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B329" t="s">
         <v>9</v>
@@ -9418,7 +9376,7 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B330" t="s">
         <v>9</v>
@@ -9444,7 +9402,7 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B331" t="s">
         <v>9</v>
@@ -9470,7 +9428,7 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B332" t="s">
         <v>9</v>
@@ -9496,7 +9454,7 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B333" t="s">
         <v>9</v>
@@ -9519,7 +9477,7 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B334" t="s">
         <v>9</v>
@@ -9545,7 +9503,7 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B335" t="s">
         <v>9</v>
@@ -9571,7 +9529,7 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B336" t="s">
         <v>9</v>
@@ -9597,7 +9555,7 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B337" t="s">
         <v>9</v>
@@ -9623,7 +9581,7 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B338" t="s">
         <v>58</v>
@@ -9631,16 +9589,25 @@
       <c r="C338" t="s">
         <v>59</v>
       </c>
-      <c r="D338" t="s">
-        <v>12</v>
-      </c>
-      <c r="G338" t="s">
-        <v>159</v>
+      <c r="D338" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E338" s="6">
+        <v>1</v>
+      </c>
+      <c r="F338" s="6">
+        <v>2</v>
+      </c>
+      <c r="G338" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H338" s="6" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B339" t="s">
         <v>58</v>
@@ -9648,16 +9615,25 @@
       <c r="C339" t="s">
         <v>60</v>
       </c>
-      <c r="D339" t="s">
+      <c r="D339" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G339" t="s">
-        <v>80</v>
+      <c r="E339" s="6">
+        <v>1</v>
+      </c>
+      <c r="F339" s="6">
+        <v>2</v>
+      </c>
+      <c r="G339" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H339" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B340" t="s">
         <v>58</v>
@@ -9665,16 +9641,25 @@
       <c r="C340" t="s">
         <v>61</v>
       </c>
-      <c r="D340" t="s">
-        <v>151</v>
-      </c>
-      <c r="G340" t="s">
+      <c r="D340" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E340" s="6">
+        <v>3</v>
+      </c>
+      <c r="F340" s="6">
+        <v>1</v>
+      </c>
+      <c r="G340" s="6" t="s">
         <v>36</v>
+      </c>
+      <c r="H340" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B341" t="s">
         <v>58</v>
@@ -9682,16 +9667,25 @@
       <c r="C341" t="s">
         <v>62</v>
       </c>
-      <c r="D341" t="s">
+      <c r="D341" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G341" t="s">
-        <v>106</v>
+      <c r="E341" s="6">
+        <v>2</v>
+      </c>
+      <c r="F341" s="6">
+        <v>0</v>
+      </c>
+      <c r="G341" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H341" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B342" t="s">
         <v>58</v>
@@ -9699,16 +9693,25 @@
       <c r="C342" t="s">
         <v>63</v>
       </c>
-      <c r="D342" t="s">
+      <c r="D342" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G342" t="s">
+      <c r="E342" s="6">
+        <v>1</v>
+      </c>
+      <c r="F342" s="6">
+        <v>2</v>
+      </c>
+      <c r="G342" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H342" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B343" t="s">
         <v>58</v>
@@ -9716,16 +9719,25 @@
       <c r="C343" t="s">
         <v>64</v>
       </c>
-      <c r="D343" t="s">
+      <c r="D343" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G343" t="s">
+      <c r="E343" s="6">
+        <v>1</v>
+      </c>
+      <c r="F343" s="6">
+        <v>2</v>
+      </c>
+      <c r="G343" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H343" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B344" t="s">
         <v>58</v>
@@ -9733,16 +9745,25 @@
       <c r="C344" t="s">
         <v>65</v>
       </c>
-      <c r="D344" t="s">
-        <v>107</v>
-      </c>
-      <c r="G344" t="s">
+      <c r="D344" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E344" s="6">
+        <v>1</v>
+      </c>
+      <c r="F344" s="6">
+        <v>1</v>
+      </c>
+      <c r="G344" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H344" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B345" t="s">
         <v>58</v>
@@ -9750,16 +9771,25 @@
       <c r="C345" t="s">
         <v>66</v>
       </c>
-      <c r="D345" t="s">
+      <c r="D345" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G345" t="s">
+      <c r="E345" s="6">
+        <v>1</v>
+      </c>
+      <c r="F345" s="6">
+        <v>2</v>
+      </c>
+      <c r="G345" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H345" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B346" t="s">
         <v>67</v>
@@ -9767,16 +9797,25 @@
       <c r="C346" t="s">
         <v>68</v>
       </c>
-      <c r="D346" t="s">
-        <v>108</v>
-      </c>
-      <c r="G346" t="s">
-        <v>109</v>
+      <c r="D346" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E346" s="6">
+        <v>2</v>
+      </c>
+      <c r="F346" s="6">
+        <v>1</v>
+      </c>
+      <c r="G346" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H346" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B347" t="s">
         <v>67</v>
@@ -9784,16 +9823,25 @@
       <c r="C347" t="s">
         <v>69</v>
       </c>
-      <c r="D347" t="s">
-        <v>110</v>
-      </c>
-      <c r="G347" t="s">
-        <v>111</v>
+      <c r="D347" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E347" s="6">
+        <v>2</v>
+      </c>
+      <c r="F347" s="6">
+        <v>1</v>
+      </c>
+      <c r="G347" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H347" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B348" t="s">
         <v>67</v>
@@ -9801,16 +9849,25 @@
       <c r="C348" t="s">
         <v>70</v>
       </c>
-      <c r="D348" t="s">
-        <v>112</v>
-      </c>
-      <c r="G348" t="s">
-        <v>113</v>
+      <c r="D348" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E348" s="6">
+        <v>1</v>
+      </c>
+      <c r="F348" s="6">
+        <v>2</v>
+      </c>
+      <c r="G348" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H348" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B349" t="s">
         <v>67</v>
@@ -9818,16 +9875,25 @@
       <c r="C349" t="s">
         <v>71</v>
       </c>
-      <c r="D349" t="s">
-        <v>114</v>
-      </c>
-      <c r="G349" t="s">
-        <v>115</v>
+      <c r="D349" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E349" s="6">
+        <v>2</v>
+      </c>
+      <c r="F349" s="6">
+        <v>1</v>
+      </c>
+      <c r="G349" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H349" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B350" t="s">
         <v>72</v>
@@ -9835,16 +9901,25 @@
       <c r="C350" t="s">
         <v>73</v>
       </c>
-      <c r="D350" t="s">
-        <v>116</v>
-      </c>
-      <c r="G350" t="s">
-        <v>117</v>
+      <c r="D350" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E350" s="6">
+        <v>1</v>
+      </c>
+      <c r="F350" s="6">
+        <v>2</v>
+      </c>
+      <c r="G350" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H350" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B351" t="s">
         <v>72</v>
@@ -9852,16 +9927,25 @@
       <c r="C351" t="s">
         <v>74</v>
       </c>
-      <c r="D351" t="s">
-        <v>118</v>
-      </c>
-      <c r="G351" t="s">
-        <v>119</v>
+      <c r="D351" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E351" s="6">
+        <v>1</v>
+      </c>
+      <c r="F351" s="6">
+        <v>2</v>
+      </c>
+      <c r="G351" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H351" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B352" t="s">
         <v>75</v>
@@ -9869,16 +9953,25 @@
       <c r="C352" t="s">
         <v>76</v>
       </c>
-      <c r="D352" t="s">
-        <v>120</v>
-      </c>
-      <c r="G352" t="s">
-        <v>121</v>
+      <c r="D352" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E352" s="6">
+        <v>2</v>
+      </c>
+      <c r="F352" s="6">
+        <v>1</v>
+      </c>
+      <c r="G352" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H352" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B353" t="s">
         <v>77</v>
@@ -9886,16 +9979,25 @@
       <c r="C353" t="s">
         <v>78</v>
       </c>
-      <c r="D353" t="s">
-        <v>122</v>
-      </c>
-      <c r="G353" t="s">
-        <v>123</v>
+      <c r="D353" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E353" s="6">
+        <v>1</v>
+      </c>
+      <c r="F353" s="6">
+        <v>2</v>
+      </c>
+      <c r="G353" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H353" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B354" t="s">
         <v>9</v>
@@ -9921,7 +10023,7 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B355" t="s">
         <v>9</v>
@@ -9947,7 +10049,7 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B356" t="s">
         <v>9</v>
@@ -9973,7 +10075,7 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B357" t="s">
         <v>9</v>
@@ -9999,7 +10101,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B358" t="s">
         <v>9</v>
@@ -10025,7 +10127,7 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B359" t="s">
         <v>9</v>
@@ -10051,7 +10153,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B360" t="s">
         <v>9</v>
@@ -10077,7 +10179,7 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B361" t="s">
         <v>9</v>
@@ -10103,7 +10205,7 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B362" t="s">
         <v>9</v>
@@ -10129,7 +10231,7 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B363" t="s">
         <v>9</v>
@@ -10155,7 +10257,7 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B364" t="s">
         <v>9</v>
@@ -10181,7 +10283,7 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B365" t="s">
         <v>9</v>
@@ -10207,7 +10309,7 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B366" t="s">
         <v>9</v>
@@ -10233,7 +10335,7 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B367" t="s">
         <v>9</v>
@@ -10259,7 +10361,7 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B368" t="s">
         <v>9</v>
@@ -10285,7 +10387,7 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B369" t="s">
         <v>9</v>
@@ -10311,7 +10413,7 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B370" t="s">
         <v>58</v>
@@ -10337,7 +10439,7 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B371" t="s">
         <v>58</v>
@@ -10363,7 +10465,7 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B372" t="s">
         <v>58</v>
@@ -10389,7 +10491,7 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B373" t="s">
         <v>58</v>
@@ -10415,7 +10517,7 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B374" t="s">
         <v>58</v>
@@ -10441,7 +10543,7 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B375" t="s">
         <v>58</v>
@@ -10467,7 +10569,7 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B376" t="s">
         <v>58</v>
@@ -10493,7 +10595,7 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B377" t="s">
         <v>58</v>
@@ -10519,7 +10621,7 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B378" t="s">
         <v>67</v>
@@ -10545,7 +10647,7 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B379" t="s">
         <v>67</v>
@@ -10571,7 +10673,7 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B380" t="s">
         <v>67</v>
@@ -10597,7 +10699,7 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B381" t="s">
         <v>67</v>
@@ -10623,7 +10725,7 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B382" t="s">
         <v>72</v>
@@ -10649,7 +10751,7 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B383" t="s">
         <v>72</v>
@@ -10675,7 +10777,7 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B384" t="s">
         <v>75</v>
@@ -10701,7 +10803,7 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B385" t="s">
         <v>77</v>
@@ -10727,7 +10829,7 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B386" t="s">
         <v>9</v>
@@ -10753,7 +10855,7 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B387" t="s">
         <v>9</v>
@@ -10779,7 +10881,7 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B388" t="s">
         <v>9</v>
@@ -10805,7 +10907,7 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B389" t="s">
         <v>9</v>
@@ -10826,12 +10928,12 @@
         <v>21</v>
       </c>
       <c r="H389" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B390" t="s">
         <v>9</v>
@@ -10857,7 +10959,7 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B391" t="s">
         <v>9</v>
@@ -10878,12 +10980,12 @@
         <v>27</v>
       </c>
       <c r="H391" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B392" t="s">
         <v>9</v>
@@ -10909,7 +11011,7 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B393" t="s">
         <v>9</v>
@@ -10930,12 +11032,12 @@
         <v>33</v>
       </c>
       <c r="H393" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B394" t="s">
         <v>9</v>
@@ -10961,7 +11063,7 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B395" t="s">
         <v>9</v>
@@ -10987,7 +11089,7 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B396" t="s">
         <v>9</v>
@@ -11013,7 +11115,7 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B397" t="s">
         <v>9</v>
@@ -11039,7 +11141,7 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B398" t="s">
         <v>9</v>
@@ -11065,7 +11167,7 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B399" t="s">
         <v>9</v>
@@ -11091,7 +11193,7 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B400" t="s">
         <v>9</v>
@@ -11117,7 +11219,7 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B401" t="s">
         <v>9</v>
@@ -11143,7 +11245,7 @@
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B402" t="s">
         <v>58</v>
@@ -11169,7 +11271,7 @@
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B403" t="s">
         <v>58</v>
@@ -11190,12 +11292,12 @@
         <v>50</v>
       </c>
       <c r="H403" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B404" t="s">
         <v>58</v>
@@ -11221,7 +11323,7 @@
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B405" t="s">
         <v>58</v>
@@ -11247,7 +11349,7 @@
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B406" t="s">
         <v>58</v>
@@ -11273,7 +11375,7 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B407" t="s">
         <v>58</v>
@@ -11299,7 +11401,7 @@
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B408" t="s">
         <v>58</v>
@@ -11325,7 +11427,7 @@
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B409" t="s">
         <v>58</v>
@@ -11351,7 +11453,7 @@
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B410" t="s">
         <v>67</v>
@@ -11377,7 +11479,7 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B411" t="s">
         <v>67</v>
@@ -11403,7 +11505,7 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B412" t="s">
         <v>67</v>
@@ -11429,7 +11531,7 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B413" t="s">
         <v>67</v>
@@ -11455,7 +11557,7 @@
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B414" t="s">
         <v>72</v>
@@ -11481,7 +11583,7 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B415" t="s">
         <v>72</v>
@@ -11507,7 +11609,7 @@
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B416" t="s">
         <v>75</v>
@@ -11528,12 +11630,12 @@
         <v>20</v>
       </c>
       <c r="H416" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B417" t="s">
         <v>77</v>
@@ -11559,7 +11661,7 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B418" t="s">
         <v>9</v>
@@ -11585,7 +11687,7 @@
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B419" t="s">
         <v>9</v>
@@ -11611,7 +11713,7 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B420" t="s">
         <v>9</v>
@@ -11637,7 +11739,7 @@
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B421" t="s">
         <v>9</v>
@@ -11663,7 +11765,7 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B422" t="s">
         <v>9</v>
@@ -11689,7 +11791,7 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B423" t="s">
         <v>9</v>
@@ -11715,7 +11817,7 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B424" t="s">
         <v>9</v>
@@ -11741,7 +11843,7 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B425" t="s">
         <v>9</v>
@@ -11767,7 +11869,7 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B426" t="s">
         <v>9</v>
@@ -11793,7 +11895,7 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B427" t="s">
         <v>9</v>
@@ -11819,7 +11921,7 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B428" t="s">
         <v>9</v>
@@ -11845,7 +11947,7 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B429" t="s">
         <v>9</v>
@@ -11871,7 +11973,7 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B430" t="s">
         <v>9</v>
@@ -11897,7 +11999,7 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B431" t="s">
         <v>9</v>
@@ -11923,7 +12025,7 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B432" t="s">
         <v>9</v>
@@ -11949,7 +12051,7 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B433" t="s">
         <v>9</v>
@@ -11975,7 +12077,7 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B434" t="s">
         <v>58</v>
@@ -12001,7 +12103,7 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B435" t="s">
         <v>58</v>
@@ -12027,7 +12129,7 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B436" t="s">
         <v>58</v>
@@ -12053,7 +12155,7 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B437" t="s">
         <v>58</v>
@@ -12079,7 +12181,7 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B438" t="s">
         <v>58</v>
@@ -12105,7 +12207,7 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B439" t="s">
         <v>58</v>
@@ -12131,7 +12233,7 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B440" t="s">
         <v>58</v>
@@ -12157,7 +12259,7 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B441" t="s">
         <v>58</v>
@@ -12183,7 +12285,7 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B442" t="s">
         <v>67</v>
@@ -12209,7 +12311,7 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B443" t="s">
         <v>67</v>
@@ -12235,7 +12337,7 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B444" t="s">
         <v>67</v>
@@ -12261,7 +12363,7 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B445" t="s">
         <v>67</v>
@@ -12287,7 +12389,7 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B446" t="s">
         <v>72</v>
@@ -12313,7 +12415,7 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B447" t="s">
         <v>72</v>
@@ -12339,7 +12441,7 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B448" t="s">
         <v>75</v>
@@ -12365,7 +12467,7 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B449" t="s">
         <v>77</v>
@@ -12391,7 +12493,7 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B450" t="s">
         <v>9</v>
@@ -12417,7 +12519,7 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B451" t="s">
         <v>9</v>
@@ -12443,7 +12545,7 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B452" t="s">
         <v>9</v>
@@ -12469,7 +12571,7 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B453" t="s">
         <v>9</v>
@@ -12495,7 +12597,7 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B454" t="s">
         <v>9</v>
@@ -12521,7 +12623,7 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B455" t="s">
         <v>9</v>
@@ -12547,7 +12649,7 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B456" t="s">
         <v>9</v>
@@ -12573,7 +12675,7 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B457" t="s">
         <v>9</v>
@@ -12599,7 +12701,7 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B458" t="s">
         <v>9</v>
@@ -12625,7 +12727,7 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B459" t="s">
         <v>9</v>
@@ -12651,7 +12753,7 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B460" t="s">
         <v>9</v>
@@ -12677,7 +12779,7 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B461" t="s">
         <v>9</v>
@@ -12703,7 +12805,7 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B462" t="s">
         <v>9</v>
@@ -12729,7 +12831,7 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B463" t="s">
         <v>9</v>
@@ -12755,7 +12857,7 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B464" t="s">
         <v>9</v>
@@ -12781,7 +12883,7 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B465" t="s">
         <v>9</v>
@@ -12807,7 +12909,7 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B466" t="s">
         <v>58</v>
@@ -12833,7 +12935,7 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B467" t="s">
         <v>58</v>
@@ -12859,7 +12961,7 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B468" t="s">
         <v>58</v>
@@ -12885,7 +12987,7 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B469" t="s">
         <v>58</v>
@@ -12911,7 +13013,7 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B470" t="s">
         <v>58</v>
@@ -12937,7 +13039,7 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B471" t="s">
         <v>58</v>
@@ -12963,7 +13065,7 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B472" t="s">
         <v>58</v>
@@ -12989,7 +13091,7 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B473" t="s">
         <v>58</v>
@@ -13015,7 +13117,7 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B474" t="s">
         <v>67</v>
@@ -13041,7 +13143,7 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B475" t="s">
         <v>67</v>
@@ -13067,7 +13169,7 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B476" t="s">
         <v>67</v>
@@ -13093,7 +13195,7 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B477" t="s">
         <v>67</v>
@@ -13119,7 +13221,7 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B478" t="s">
         <v>72</v>
@@ -13145,7 +13247,7 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B479" t="s">
         <v>72</v>
@@ -13171,7 +13273,7 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B480" t="s">
         <v>75</v>
@@ -13197,7 +13299,7 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B481" t="s">
         <v>77</v>
@@ -13223,7 +13325,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B482" t="s">
         <v>9</v>
@@ -13240,7 +13342,7 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B483" t="s">
         <v>9</v>
@@ -13257,7 +13359,7 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B484" t="s">
         <v>9</v>
@@ -13283,7 +13385,7 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B485" t="s">
         <v>9</v>
@@ -13300,7 +13402,7 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B486" t="s">
         <v>9</v>
@@ -13326,7 +13428,7 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B487" t="s">
         <v>9</v>
@@ -13352,7 +13454,7 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B488" t="s">
         <v>9</v>
@@ -13378,7 +13480,7 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B489" t="s">
         <v>9</v>
@@ -13404,7 +13506,7 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B490" t="s">
         <v>9</v>
@@ -13430,7 +13532,7 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B491" t="s">
         <v>9</v>
@@ -13447,7 +13549,7 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B492" t="s">
         <v>9</v>
@@ -13473,7 +13575,7 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B493" t="s">
         <v>9</v>
@@ -13499,7 +13601,7 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B494" t="s">
         <v>9</v>
@@ -13525,7 +13627,7 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B495" t="s">
         <v>9</v>
@@ -13548,7 +13650,7 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B496" t="s">
         <v>9</v>
@@ -13574,7 +13676,7 @@
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B497" t="s">
         <v>9</v>
@@ -13600,7 +13702,7 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B498" t="s">
         <v>58</v>
@@ -13626,7 +13728,7 @@
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B499" t="s">
         <v>58</v>
@@ -13643,13 +13745,16 @@
       <c r="F499">
         <v>1</v>
       </c>
+      <c r="G499" t="s">
+        <v>50</v>
+      </c>
       <c r="H499" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B500" t="s">
         <v>58</v>
@@ -13672,7 +13777,7 @@
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B501" t="s">
         <v>58</v>
@@ -13698,7 +13803,7 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B502" t="s">
         <v>58</v>
@@ -13724,7 +13829,7 @@
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B503" t="s">
         <v>58</v>
@@ -13732,6 +13837,9 @@
       <c r="C503" t="s">
         <v>64</v>
       </c>
+      <c r="D503" t="s">
+        <v>32</v>
+      </c>
       <c r="E503">
         <v>1</v>
       </c>
@@ -13747,7 +13855,7 @@
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B504" t="s">
         <v>58</v>
@@ -13756,7 +13864,7 @@
         <v>65</v>
       </c>
       <c r="D504" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E504">
         <v>1</v>
@@ -13773,7 +13881,7 @@
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B505" t="s">
         <v>58</v>
@@ -13781,6 +13889,9 @@
       <c r="C505" t="s">
         <v>66</v>
       </c>
+      <c r="D505" t="s">
+        <v>39</v>
+      </c>
       <c r="E505">
         <v>1</v>
       </c>
@@ -13796,7 +13907,7 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B506" t="s">
         <v>67</v>
@@ -13805,15 +13916,24 @@
         <v>68</v>
       </c>
       <c r="D506" t="s">
-        <v>108</v>
+        <v>41</v>
+      </c>
+      <c r="E506">
+        <v>3</v>
+      </c>
+      <c r="F506">
+        <v>1</v>
       </c>
       <c r="G506" t="s">
-        <v>109</v>
+        <v>15</v>
+      </c>
+      <c r="H506" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B507" t="s">
         <v>67</v>
@@ -13822,15 +13942,24 @@
         <v>69</v>
       </c>
       <c r="D507" t="s">
-        <v>110</v>
+        <v>47</v>
+      </c>
+      <c r="E507">
+        <v>3</v>
+      </c>
+      <c r="F507">
+        <v>0</v>
       </c>
       <c r="G507" t="s">
-        <v>111</v>
+        <v>145</v>
+      </c>
+      <c r="H507" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B508" t="s">
         <v>67</v>
@@ -13839,15 +13968,24 @@
         <v>70</v>
       </c>
       <c r="D508" t="s">
-        <v>112</v>
+        <v>36</v>
+      </c>
+      <c r="E508">
+        <v>1</v>
+      </c>
+      <c r="F508">
+        <v>2</v>
       </c>
       <c r="G508" t="s">
-        <v>113</v>
+        <v>53</v>
+      </c>
+      <c r="H508" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B509" t="s">
         <v>67</v>
@@ -13856,15 +13994,24 @@
         <v>71</v>
       </c>
       <c r="D509" t="s">
-        <v>114</v>
+        <v>23</v>
+      </c>
+      <c r="E509">
+        <v>1</v>
+      </c>
+      <c r="F509">
+        <v>2</v>
       </c>
       <c r="G509" t="s">
-        <v>115</v>
+        <v>56</v>
+      </c>
+      <c r="H509" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B510" t="s">
         <v>72</v>
@@ -13873,15 +14020,24 @@
         <v>73</v>
       </c>
       <c r="D510" t="s">
-        <v>116</v>
+        <v>41</v>
+      </c>
+      <c r="E510">
+        <v>2</v>
+      </c>
+      <c r="F510">
+        <v>0</v>
       </c>
       <c r="G510" t="s">
-        <v>117</v>
+        <v>47</v>
+      </c>
+      <c r="H510" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B511" t="s">
         <v>72</v>
@@ -13890,15 +14046,24 @@
         <v>74</v>
       </c>
       <c r="D511" t="s">
-        <v>118</v>
+        <v>53</v>
+      </c>
+      <c r="E511">
+        <v>1</v>
+      </c>
+      <c r="F511">
+        <v>1</v>
       </c>
       <c r="G511" t="s">
-        <v>119</v>
+        <v>56</v>
+      </c>
+      <c r="H511" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B512" t="s">
         <v>75</v>
@@ -13907,15 +14072,24 @@
         <v>76</v>
       </c>
       <c r="D512" t="s">
-        <v>120</v>
+        <v>47</v>
+      </c>
+      <c r="E512">
+        <v>2</v>
+      </c>
+      <c r="F512">
+        <v>1</v>
       </c>
       <c r="G512" t="s">
-        <v>121</v>
+        <v>53</v>
+      </c>
+      <c r="H512" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B513" t="s">
         <v>77</v>
@@ -13924,15 +14098,24 @@
         <v>78</v>
       </c>
       <c r="D513" t="s">
-        <v>122</v>
+        <v>41</v>
+      </c>
+      <c r="E513">
+        <v>1</v>
+      </c>
+      <c r="F513">
+        <v>3</v>
       </c>
       <c r="G513" t="s">
-        <v>123</v>
+        <v>56</v>
+      </c>
+      <c r="H513" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B514" t="s">
         <v>9</v>
@@ -13958,7 +14141,7 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B515" t="s">
         <v>9</v>
@@ -13984,7 +14167,7 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B516" t="s">
         <v>9</v>
@@ -14010,7 +14193,7 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B517" t="s">
         <v>9</v>
@@ -14036,7 +14219,7 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B518" t="s">
         <v>9</v>
@@ -14062,7 +14245,7 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B519" t="s">
         <v>9</v>
@@ -14088,7 +14271,7 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B520" t="s">
         <v>9</v>
@@ -14114,7 +14297,7 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B521" t="s">
         <v>9</v>
@@ -14140,7 +14323,7 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B522" t="s">
         <v>9</v>
@@ -14166,7 +14349,7 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B523" t="s">
         <v>9</v>
@@ -14192,7 +14375,7 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B524" t="s">
         <v>9</v>
@@ -14218,7 +14401,7 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B525" t="s">
         <v>9</v>
@@ -14244,7 +14427,7 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B526" t="s">
         <v>9</v>
@@ -14270,7 +14453,7 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B527" t="s">
         <v>9</v>
@@ -14296,7 +14479,7 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B528" t="s">
         <v>9</v>
@@ -14322,7 +14505,7 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B529" t="s">
         <v>9</v>
@@ -14348,7 +14531,7 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B530" t="s">
         <v>58</v>
@@ -14374,7 +14557,7 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B531" t="s">
         <v>58</v>
@@ -14400,7 +14583,7 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B532" t="s">
         <v>58</v>
@@ -14426,7 +14609,7 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B533" t="s">
         <v>58</v>
@@ -14452,7 +14635,7 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B534" t="s">
         <v>58</v>
@@ -14478,7 +14661,7 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B535" t="s">
         <v>58</v>
@@ -14504,7 +14687,7 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B536" t="s">
         <v>58</v>
@@ -14530,7 +14713,7 @@
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B537" t="s">
         <v>58</v>
@@ -14556,7 +14739,7 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B538" t="s">
         <v>67</v>
@@ -14582,7 +14765,7 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B539" t="s">
         <v>67</v>
@@ -14608,7 +14791,7 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B540" t="s">
         <v>67</v>
@@ -14634,7 +14817,7 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B541" t="s">
         <v>67</v>
@@ -14660,7 +14843,7 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B542" t="s">
         <v>72</v>
@@ -14686,7 +14869,7 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B543" t="s">
         <v>72</v>
@@ -14712,7 +14895,7 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B544" t="s">
         <v>75</v>
@@ -14733,12 +14916,12 @@
         <v>56</v>
       </c>
       <c r="H544" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B545" t="s">
         <v>77</v>
@@ -14764,7 +14947,7 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B546" t="s">
         <v>9</v>
@@ -14781,7 +14964,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B547" t="s">
         <v>9</v>
@@ -14798,7 +14981,7 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B548" t="s">
         <v>9</v>
@@ -14824,7 +15007,7 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B549" t="s">
         <v>9</v>
@@ -14841,7 +15024,7 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B550" t="s">
         <v>9</v>
@@ -14867,7 +15050,7 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B551" t="s">
         <v>9</v>
@@ -14893,7 +15076,7 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B552" t="s">
         <v>9</v>
@@ -14919,7 +15102,7 @@
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B553" t="s">
         <v>9</v>
@@ -14936,7 +15119,7 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B554" t="s">
         <v>9</v>
@@ -14953,7 +15136,7 @@
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B555" t="s">
         <v>9</v>
@@ -14970,7 +15153,7 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B556" t="s">
         <v>9</v>
@@ -14987,7 +15170,7 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B557" t="s">
         <v>9</v>
@@ -15013,7 +15196,7 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B558" t="s">
         <v>9</v>
@@ -15039,7 +15222,7 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B559" t="s">
         <v>9</v>
@@ -15065,7 +15248,7 @@
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B560" t="s">
         <v>9</v>
@@ -15091,7 +15274,7 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B561" t="s">
         <v>9</v>
@@ -15117,7 +15300,7 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B562" t="s">
         <v>58</v>
@@ -15143,7 +15326,7 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B563" t="s">
         <v>58</v>
@@ -15169,7 +15352,7 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B564" t="s">
         <v>58</v>
@@ -15195,7 +15378,7 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B565" t="s">
         <v>58</v>
@@ -15221,7 +15404,7 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B566" t="s">
         <v>58</v>
@@ -15247,7 +15430,7 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B567" t="s">
         <v>58</v>
@@ -15256,7 +15439,7 @@
         <v>64</v>
       </c>
       <c r="D567" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E567">
         <v>1</v>
@@ -15273,7 +15456,7 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B568" t="s">
         <v>58</v>
@@ -15299,7 +15482,7 @@
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B569" t="s">
         <v>58</v>
@@ -15322,7 +15505,7 @@
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B570" t="s">
         <v>67</v>
@@ -15348,7 +15531,7 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B571" t="s">
         <v>67</v>
@@ -15374,7 +15557,7 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B572" t="s">
         <v>67</v>
@@ -15400,7 +15583,7 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B573" t="s">
         <v>67</v>
@@ -15426,7 +15609,7 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B574" t="s">
         <v>72</v>
@@ -15452,7 +15635,7 @@
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B575" t="s">
         <v>72</v>
@@ -15478,7 +15661,7 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B576" t="s">
         <v>75</v>
@@ -15504,7 +15687,7 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B577" t="s">
         <v>77</v>
@@ -15530,7 +15713,7 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B578" t="s">
         <v>9</v>
@@ -15556,7 +15739,7 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B579" t="s">
         <v>9</v>
@@ -15582,7 +15765,7 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B580" t="s">
         <v>9</v>
@@ -15608,7 +15791,7 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B581" t="s">
         <v>9</v>
@@ -15634,7 +15817,7 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B582" t="s">
         <v>9</v>
@@ -15660,7 +15843,7 @@
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B583" t="s">
         <v>9</v>
@@ -15686,7 +15869,7 @@
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B584" t="s">
         <v>9</v>
@@ -15712,7 +15895,7 @@
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B585" t="s">
         <v>9</v>
@@ -15738,7 +15921,7 @@
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B586" t="s">
         <v>9</v>
@@ -15764,7 +15947,7 @@
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B587" t="s">
         <v>9</v>
@@ -15790,7 +15973,7 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B588" t="s">
         <v>9</v>
@@ -15816,7 +15999,7 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B589" t="s">
         <v>9</v>
@@ -15842,7 +16025,7 @@
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B590" t="s">
         <v>9</v>
@@ -15868,7 +16051,7 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B591" t="s">
         <v>9</v>
@@ -15894,7 +16077,7 @@
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B592" t="s">
         <v>9</v>
@@ -15920,7 +16103,7 @@
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B593" t="s">
         <v>9</v>
@@ -15946,7 +16129,7 @@
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B594" t="s">
         <v>58</v>
@@ -15972,7 +16155,7 @@
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B595" t="s">
         <v>58</v>
@@ -15998,7 +16181,7 @@
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B596" t="s">
         <v>58</v>
@@ -16024,7 +16207,7 @@
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B597" t="s">
         <v>58</v>
@@ -16050,7 +16233,7 @@
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B598" t="s">
         <v>58</v>
@@ -16076,7 +16259,7 @@
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B599" t="s">
         <v>58</v>
@@ -16085,7 +16268,7 @@
         <v>64</v>
       </c>
       <c r="D599" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E599">
         <v>1</v>
@@ -16102,7 +16285,7 @@
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B600" t="s">
         <v>58</v>
@@ -16128,7 +16311,7 @@
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B601" t="s">
         <v>58</v>
@@ -16154,7 +16337,7 @@
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B602" t="s">
         <v>67</v>
@@ -16180,7 +16363,7 @@
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B603" t="s">
         <v>67</v>
@@ -16206,7 +16389,7 @@
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B604" t="s">
         <v>67</v>
@@ -16232,7 +16415,7 @@
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B605" t="s">
         <v>67</v>
@@ -16258,7 +16441,7 @@
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B606" t="s">
         <v>72</v>
@@ -16284,7 +16467,7 @@
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B607" t="s">
         <v>72</v>
@@ -16310,7 +16493,7 @@
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B608" t="s">
         <v>75</v>
@@ -16336,7 +16519,7 @@
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B609" t="s">
         <v>77</v>
@@ -16362,7 +16545,7 @@
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B610" t="s">
         <v>9</v>
@@ -16388,7 +16571,7 @@
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B611" t="s">
         <v>9</v>
@@ -16414,7 +16597,7 @@
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B612" t="s">
         <v>9</v>
@@ -16440,7 +16623,7 @@
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B613" t="s">
         <v>9</v>
@@ -16466,7 +16649,7 @@
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B614" t="s">
         <v>9</v>
@@ -16492,7 +16675,7 @@
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B615" t="s">
         <v>9</v>
@@ -16518,7 +16701,7 @@
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B616" t="s">
         <v>9</v>
@@ -16544,7 +16727,7 @@
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B617" t="s">
         <v>9</v>
@@ -16570,7 +16753,7 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B618" t="s">
         <v>9</v>
@@ -16596,7 +16779,7 @@
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B619" t="s">
         <v>9</v>
@@ -16622,7 +16805,7 @@
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B620" t="s">
         <v>9</v>
@@ -16648,7 +16831,7 @@
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B621" t="s">
         <v>9</v>
@@ -16674,7 +16857,7 @@
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B622" t="s">
         <v>9</v>
@@ -16700,7 +16883,7 @@
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B623" t="s">
         <v>9</v>
@@ -16726,7 +16909,7 @@
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B624" t="s">
         <v>9</v>
@@ -16752,7 +16935,7 @@
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -16778,7 +16961,7 @@
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B626" t="s">
         <v>58</v>
@@ -16804,7 +16987,7 @@
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B627" t="s">
         <v>58</v>
@@ -16830,7 +17013,7 @@
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B628" t="s">
         <v>58</v>
@@ -16856,7 +17039,7 @@
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B629" t="s">
         <v>58</v>
@@ -16882,7 +17065,7 @@
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B630" t="s">
         <v>58</v>
@@ -16908,7 +17091,7 @@
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B631" t="s">
         <v>58</v>
@@ -16934,7 +17117,7 @@
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B632" t="s">
         <v>58</v>
@@ -16960,7 +17143,7 @@
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B633" t="s">
         <v>58</v>
@@ -16986,7 +17169,7 @@
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B634" t="s">
         <v>67</v>
@@ -17012,7 +17195,7 @@
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B635" t="s">
         <v>67</v>
@@ -17038,7 +17221,7 @@
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B636" t="s">
         <v>67</v>
@@ -17064,7 +17247,7 @@
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B637" t="s">
         <v>67</v>
@@ -17090,10 +17273,10 @@
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B638" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C638" t="s">
         <v>73</v>
@@ -17116,10 +17299,10 @@
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B639" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C639" t="s">
         <v>74</v>
@@ -17142,7 +17325,7 @@
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B640" t="s">
         <v>75</v>
@@ -17168,7 +17351,7 @@
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B641" t="s">
         <v>77</v>
@@ -17194,7 +17377,7 @@
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B642" t="s">
         <v>9</v>
@@ -17220,7 +17403,7 @@
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B643" t="s">
         <v>9</v>
@@ -17246,7 +17429,7 @@
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B644" t="s">
         <v>9</v>
@@ -17272,7 +17455,7 @@
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B645" t="s">
         <v>9</v>
@@ -17298,7 +17481,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B646" t="s">
         <v>9</v>
@@ -17324,7 +17507,7 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B647" t="s">
         <v>9</v>
@@ -17350,7 +17533,7 @@
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B648" t="s">
         <v>9</v>
@@ -17376,7 +17559,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B649" t="s">
         <v>9</v>
@@ -17402,7 +17585,7 @@
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B650" t="s">
         <v>9</v>
@@ -17428,7 +17611,7 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B651" t="s">
         <v>9</v>
@@ -17454,7 +17637,7 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B652" t="s">
         <v>9</v>
@@ -17480,7 +17663,7 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B653" t="s">
         <v>9</v>
@@ -17506,7 +17689,7 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B654" t="s">
         <v>9</v>
@@ -17532,7 +17715,7 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B655" t="s">
         <v>9</v>
@@ -17558,7 +17741,7 @@
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B656" t="s">
         <v>9</v>
@@ -17584,7 +17767,7 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B657" t="s">
         <v>9</v>
@@ -17610,7 +17793,7 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B658" t="s">
         <v>58</v>
@@ -17636,7 +17819,7 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B659" t="s">
         <v>58</v>
@@ -17662,7 +17845,7 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B660" t="s">
         <v>58</v>
@@ -17688,7 +17871,7 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B661" t="s">
         <v>58</v>
@@ -17714,7 +17897,7 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B662" t="s">
         <v>58</v>
@@ -17740,7 +17923,7 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B663" t="s">
         <v>58</v>
@@ -17766,7 +17949,7 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B664" t="s">
         <v>58</v>
@@ -17792,7 +17975,7 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B665" t="s">
         <v>58</v>
@@ -17818,7 +18001,7 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B666" t="s">
         <v>67</v>
@@ -17844,7 +18027,7 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B667" t="s">
         <v>67</v>
@@ -17870,7 +18053,7 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B668" t="s">
         <v>67</v>
@@ -17896,7 +18079,7 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B669" t="s">
         <v>67</v>
@@ -17922,7 +18105,7 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B670" t="s">
         <v>72</v>
@@ -17948,7 +18131,7 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B671" t="s">
         <v>72</v>
@@ -17974,7 +18157,7 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B672" t="s">
         <v>75</v>
@@ -18000,7 +18183,7 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B673" t="s">
         <v>77</v>
@@ -18026,7 +18209,7 @@
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B674" t="s">
         <v>9</v>
@@ -18052,7 +18235,7 @@
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B675" t="s">
         <v>9</v>
@@ -18078,7 +18261,7 @@
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B676" t="s">
         <v>9</v>
@@ -18104,7 +18287,7 @@
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B677" t="s">
         <v>9</v>
@@ -18130,7 +18313,7 @@
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B678" t="s">
         <v>9</v>
@@ -18156,7 +18339,7 @@
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B679" t="s">
         <v>9</v>
@@ -18182,7 +18365,7 @@
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B680" t="s">
         <v>9</v>
@@ -18208,7 +18391,7 @@
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B681" t="s">
         <v>9</v>
@@ -18234,7 +18417,7 @@
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B682" t="s">
         <v>9</v>
@@ -18260,7 +18443,7 @@
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B683" t="s">
         <v>9</v>
@@ -18286,7 +18469,7 @@
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B684" t="s">
         <v>9</v>
@@ -18312,7 +18495,7 @@
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B685" t="s">
         <v>9</v>
@@ -18338,7 +18521,7 @@
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B686" t="s">
         <v>9</v>
@@ -18364,7 +18547,7 @@
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B687" t="s">
         <v>9</v>
@@ -18390,7 +18573,7 @@
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B688" t="s">
         <v>9</v>
@@ -18416,7 +18599,7 @@
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B689" t="s">
         <v>9</v>
@@ -18442,7 +18625,7 @@
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B690" t="s">
         <v>58</v>
@@ -18468,7 +18651,7 @@
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B691" t="s">
         <v>58</v>
@@ -18494,7 +18677,7 @@
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B692" t="s">
         <v>58</v>
@@ -18520,7 +18703,7 @@
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B693" t="s">
         <v>58</v>
@@ -18546,7 +18729,7 @@
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B694" t="s">
         <v>58</v>
@@ -18572,7 +18755,7 @@
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B695" t="s">
         <v>58</v>
@@ -18598,7 +18781,7 @@
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B696" t="s">
         <v>58</v>
@@ -18624,7 +18807,7 @@
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B697" t="s">
         <v>58</v>
@@ -18650,7 +18833,7 @@
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B698" t="s">
         <v>67</v>
@@ -18676,7 +18859,7 @@
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B699" t="s">
         <v>67</v>
@@ -18702,7 +18885,7 @@
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B700" t="s">
         <v>67</v>
@@ -18728,7 +18911,7 @@
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B701" t="s">
         <v>67</v>
@@ -18754,7 +18937,7 @@
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B702" t="s">
         <v>72</v>
@@ -18780,7 +18963,7 @@
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B703" t="s">
         <v>72</v>
@@ -18806,7 +18989,7 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B704" t="s">
         <v>75</v>
@@ -18832,7 +19015,7 @@
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B705" t="s">
         <v>77</v>
@@ -18858,7 +19041,7 @@
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B706" t="s">
         <v>9</v>
@@ -18875,7 +19058,7 @@
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B707" t="s">
         <v>9</v>
@@ -18892,7 +19075,7 @@
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B708" t="s">
         <v>9</v>
@@ -18918,7 +19101,7 @@
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B709" t="s">
         <v>9</v>
@@ -18935,7 +19118,7 @@
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B710" t="s">
         <v>9</v>
@@ -18961,7 +19144,7 @@
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B711" t="s">
         <v>9</v>
@@ -18987,7 +19170,7 @@
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B712" t="s">
         <v>9</v>
@@ -19013,7 +19196,7 @@
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B713" t="s">
         <v>9</v>
@@ -19039,7 +19222,7 @@
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B714" t="s">
         <v>9</v>
@@ -19065,7 +19248,7 @@
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B715" t="s">
         <v>9</v>
@@ -19082,7 +19265,7 @@
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B716" t="s">
         <v>9</v>
@@ -19108,7 +19291,7 @@
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B717" t="s">
         <v>9</v>
@@ -19134,7 +19317,7 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B718" t="s">
         <v>9</v>
@@ -19160,7 +19343,7 @@
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B719" t="s">
         <v>9</v>
@@ -19186,7 +19369,7 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B720" t="s">
         <v>9</v>
@@ -19212,7 +19395,7 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B721" t="s">
         <v>9</v>
@@ -19238,7 +19421,7 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B722" t="s">
         <v>58</v>
@@ -19264,7 +19447,7 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B723" t="s">
         <v>58</v>
@@ -19290,7 +19473,7 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B724" t="s">
         <v>58</v>
@@ -19316,7 +19499,7 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B725" t="s">
         <v>58</v>
@@ -19342,7 +19525,7 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B726" t="s">
         <v>58</v>
@@ -19368,7 +19551,7 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B727" t="s">
         <v>58</v>
@@ -19377,7 +19560,7 @@
         <v>64</v>
       </c>
       <c r="D727" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E727">
         <v>1</v>
@@ -19394,7 +19577,7 @@
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B728" t="s">
         <v>58</v>
@@ -19420,7 +19603,7 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B729" t="s">
         <v>58</v>
@@ -19443,7 +19626,7 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B730" t="s">
         <v>67</v>
@@ -19469,7 +19652,7 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B731" t="s">
         <v>67</v>
@@ -19495,7 +19678,7 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B732" t="s">
         <v>67</v>
@@ -19521,7 +19704,7 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B733" t="s">
         <v>67</v>
@@ -19547,7 +19730,7 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B734" t="s">
         <v>72</v>
@@ -19573,7 +19756,7 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B735" t="s">
         <v>72</v>
@@ -19599,7 +19782,7 @@
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B736" t="s">
         <v>75</v>
@@ -19625,7 +19808,7 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B737" t="s">
         <v>77</v>
@@ -19651,7 +19834,7 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B738" t="s">
         <v>9</v>
@@ -19677,7 +19860,7 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B739" t="s">
         <v>9</v>
@@ -19703,7 +19886,7 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B740" t="s">
         <v>9</v>
@@ -19729,7 +19912,7 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B741" t="s">
         <v>9</v>
@@ -19755,7 +19938,7 @@
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B742" t="s">
         <v>9</v>
@@ -19781,7 +19964,7 @@
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B743" t="s">
         <v>9</v>
@@ -19807,7 +19990,7 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B744" t="s">
         <v>9</v>
@@ -19833,7 +20016,7 @@
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B745" t="s">
         <v>9</v>
@@ -19859,7 +20042,7 @@
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B746" t="s">
         <v>9</v>
@@ -19885,7 +20068,7 @@
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B747" t="s">
         <v>9</v>
@@ -19911,7 +20094,7 @@
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B748" t="s">
         <v>9</v>
@@ -19937,7 +20120,7 @@
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B749" t="s">
         <v>9</v>
@@ -19963,7 +20146,7 @@
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B750" t="s">
         <v>9</v>
@@ -19989,7 +20172,7 @@
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B751" t="s">
         <v>9</v>
@@ -20015,7 +20198,7 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B752" t="s">
         <v>9</v>
@@ -20041,7 +20224,7 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B753" t="s">
         <v>9</v>
@@ -20067,7 +20250,7 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B754" t="s">
         <v>58</v>
@@ -20093,7 +20276,7 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B755" t="s">
         <v>58</v>
@@ -20119,7 +20302,7 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B756" t="s">
         <v>58</v>
@@ -20137,7 +20320,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="H756" t="s">
         <v>20</v>
@@ -20145,7 +20328,7 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B757" t="s">
         <v>58</v>
@@ -20171,7 +20354,7 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B758" t="s">
         <v>58</v>
@@ -20197,7 +20380,7 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B759" t="s">
         <v>58</v>
@@ -20223,7 +20406,7 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B760" t="s">
         <v>58</v>
@@ -20249,7 +20432,7 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B761" t="s">
         <v>58</v>
@@ -20275,7 +20458,7 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B762" t="s">
         <v>67</v>
@@ -20301,7 +20484,7 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B763" t="s">
         <v>67</v>
@@ -20327,7 +20510,7 @@
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B764" t="s">
         <v>67</v>
@@ -20353,7 +20536,7 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B765" t="s">
         <v>67</v>
@@ -20379,7 +20562,7 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B766" t="s">
         <v>72</v>
@@ -20405,7 +20588,7 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B767" t="s">
         <v>72</v>
@@ -20431,7 +20614,7 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B768" t="s">
         <v>75</v>
@@ -20457,7 +20640,7 @@
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B769" t="s">
         <v>77</v>
@@ -20483,7 +20666,7 @@
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B770" t="s">
         <v>9</v>
@@ -20500,7 +20683,7 @@
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B771" t="s">
         <v>9</v>
@@ -20521,12 +20704,12 @@
         <v>15</v>
       </c>
       <c r="H771" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B772" t="s">
         <v>9</v>
@@ -20547,12 +20730,12 @@
         <v>18</v>
       </c>
       <c r="H772" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B773" t="s">
         <v>9</v>
@@ -20573,12 +20756,12 @@
         <v>21</v>
       </c>
       <c r="H773" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B774" t="s">
         <v>9</v>
@@ -20604,7 +20787,7 @@
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B775" t="s">
         <v>9</v>
@@ -20625,12 +20808,12 @@
         <v>27</v>
       </c>
       <c r="H775" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B776" t="s">
         <v>9</v>
@@ -20656,7 +20839,7 @@
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B777" t="s">
         <v>9</v>
@@ -20677,12 +20860,12 @@
         <v>33</v>
       </c>
       <c r="H777" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B778" t="s">
         <v>9</v>
@@ -20708,7 +20891,7 @@
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B779" t="s">
         <v>9</v>
@@ -20734,7 +20917,7 @@
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B780" t="s">
         <v>9</v>
@@ -20760,7 +20943,7 @@
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B781" t="s">
         <v>9</v>
@@ -20781,12 +20964,12 @@
         <v>45</v>
       </c>
       <c r="H781" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B782" t="s">
         <v>9</v>
@@ -20812,7 +20995,7 @@
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B783" t="s">
         <v>9</v>
@@ -20833,12 +21016,12 @@
         <v>51</v>
       </c>
       <c r="H783" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B784" t="s">
         <v>9</v>
@@ -20864,7 +21047,7 @@
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B785" t="s">
         <v>9</v>
@@ -20890,7 +21073,7 @@
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B786" t="s">
         <v>58</v>
@@ -20908,15 +21091,15 @@
         <v>2</v>
       </c>
       <c r="G786" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="H786" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B787" t="s">
         <v>58</v>
@@ -20937,12 +21120,12 @@
         <v>50</v>
       </c>
       <c r="H787" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B788" t="s">
         <v>58</v>
@@ -20968,7 +21151,7 @@
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B789" t="s">
         <v>58</v>
@@ -20994,7 +21177,7 @@
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B790" t="s">
         <v>58</v>
@@ -21020,7 +21203,7 @@
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B791" t="s">
         <v>58</v>
@@ -21046,7 +21229,7 @@
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B792" t="s">
         <v>58</v>
@@ -21072,7 +21255,7 @@
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B793" t="s">
         <v>58</v>
@@ -21098,7 +21281,7 @@
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B794" t="s">
         <v>67</v>
@@ -21116,7 +21299,7 @@
         <v>1</v>
       </c>
       <c r="G794" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="H794" t="s">
         <v>89</v>
@@ -21124,7 +21307,7 @@
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B795" t="s">
         <v>67</v>
@@ -21142,7 +21325,7 @@
         <v>1</v>
       </c>
       <c r="G795" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H795" t="s">
         <v>83</v>
@@ -21150,7 +21333,7 @@
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B796" t="s">
         <v>67</v>
@@ -21176,7 +21359,7 @@
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B797" t="s">
         <v>67</v>
@@ -21202,7 +21385,7 @@
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B798" t="s">
         <v>72</v>
@@ -21228,7 +21411,7 @@
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B799" t="s">
         <v>72</v>
@@ -21254,7 +21437,7 @@
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B800" t="s">
         <v>75</v>
@@ -21280,7 +21463,7 @@
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B801" t="s">
         <v>77</v>
@@ -21306,7 +21489,7 @@
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B802" t="s">
         <v>9</v>
@@ -21332,7 +21515,7 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B803" t="s">
         <v>9</v>
@@ -21358,7 +21541,7 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B804" t="s">
         <v>9</v>
@@ -21384,7 +21567,7 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B805" t="s">
         <v>9</v>
@@ -21410,7 +21593,7 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B806" t="s">
         <v>9</v>
@@ -21436,7 +21619,7 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B807" t="s">
         <v>9</v>
@@ -21462,7 +21645,7 @@
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B808" t="s">
         <v>9</v>
@@ -21488,7 +21671,7 @@
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B809" t="s">
         <v>9</v>
@@ -21509,12 +21692,12 @@
         <v>33</v>
       </c>
       <c r="H809" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B810" t="s">
         <v>9</v>
@@ -21540,7 +21723,7 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B811" t="s">
         <v>9</v>
@@ -21566,7 +21749,7 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B812" t="s">
         <v>9</v>
@@ -21592,7 +21775,7 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B813" t="s">
         <v>9</v>
@@ -21618,7 +21801,7 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B814" t="s">
         <v>9</v>
@@ -21644,7 +21827,7 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B815" t="s">
         <v>9</v>
@@ -21670,7 +21853,7 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B816" t="s">
         <v>9</v>
@@ -21696,7 +21879,7 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B817" t="s">
         <v>9</v>
@@ -21722,7 +21905,7 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B818" t="s">
         <v>58</v>
@@ -21748,7 +21931,7 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B819" t="s">
         <v>58</v>
@@ -21769,12 +21952,12 @@
         <v>50</v>
       </c>
       <c r="H819" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B820" t="s">
         <v>58</v>
@@ -21800,7 +21983,7 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B821" t="s">
         <v>58</v>
@@ -21826,7 +22009,7 @@
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B822" t="s">
         <v>58</v>
@@ -21852,7 +22035,7 @@
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B823" t="s">
         <v>58</v>
@@ -21878,7 +22061,7 @@
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B824" t="s">
         <v>58</v>
@@ -21904,7 +22087,7 @@
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B825" t="s">
         <v>58</v>
@@ -21930,7 +22113,7 @@
     </row>
     <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B826" t="s">
         <v>67</v>
@@ -21956,7 +22139,7 @@
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B827" t="s">
         <v>67</v>
@@ -21982,7 +22165,7 @@
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B828" t="s">
         <v>67</v>
@@ -22008,7 +22191,7 @@
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B829" t="s">
         <v>67</v>
@@ -22034,7 +22217,7 @@
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B830" t="s">
         <v>72</v>
@@ -22060,7 +22243,7 @@
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B831" t="s">
         <v>72</v>
@@ -22086,7 +22269,7 @@
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B832" t="s">
         <v>75</v>
@@ -22112,7 +22295,7 @@
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B833" t="s">
         <v>77</v>
@@ -22138,7 +22321,7 @@
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B834" t="s">
         <v>9</v>
@@ -22164,7 +22347,7 @@
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B835" t="s">
         <v>9</v>
@@ -22190,7 +22373,7 @@
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B836" t="s">
         <v>9</v>
@@ -22216,7 +22399,7 @@
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B837" t="s">
         <v>9</v>
@@ -22242,7 +22425,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B838" t="s">
         <v>9</v>
@@ -22268,7 +22451,7 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B839" t="s">
         <v>9</v>
@@ -22294,7 +22477,7 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B840" t="s">
         <v>9</v>
@@ -22320,7 +22503,7 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B841" t="s">
         <v>9</v>
@@ -22346,7 +22529,7 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B842" t="s">
         <v>9</v>
@@ -22372,7 +22555,7 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B843" t="s">
         <v>9</v>
@@ -22398,7 +22581,7 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B844" t="s">
         <v>9</v>
@@ -22424,7 +22607,7 @@
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B845" t="s">
         <v>9</v>
@@ -22450,7 +22633,7 @@
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B846" t="s">
         <v>9</v>
@@ -22476,7 +22659,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B847" t="s">
         <v>9</v>
@@ -22502,7 +22685,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B848" t="s">
         <v>9</v>
@@ -22528,7 +22711,7 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B849" t="s">
         <v>9</v>
@@ -22554,7 +22737,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B850" t="s">
         <v>58</v>
@@ -22580,7 +22763,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B851" t="s">
         <v>58</v>
@@ -22606,7 +22789,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B852" t="s">
         <v>58</v>
@@ -22632,7 +22815,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B853" t="s">
         <v>58</v>
@@ -22658,7 +22841,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B854" t="s">
         <v>58</v>
@@ -22684,7 +22867,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B855" t="s">
         <v>58</v>
@@ -22710,7 +22893,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B856" t="s">
         <v>58</v>
@@ -22736,7 +22919,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B857" t="s">
         <v>58</v>
@@ -22762,7 +22945,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B858" t="s">
         <v>67</v>
@@ -22788,7 +22971,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B859" t="s">
         <v>67</v>
@@ -22814,7 +22997,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B860" t="s">
         <v>67</v>
@@ -22840,7 +23023,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B861" t="s">
         <v>67</v>
@@ -22866,7 +23049,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B862" t="s">
         <v>72</v>
@@ -22892,7 +23075,7 @@
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B863" t="s">
         <v>72</v>
@@ -22901,7 +23084,7 @@
         <v>74</v>
       </c>
       <c r="D863" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="E863">
         <v>2</v>
@@ -22918,7 +23101,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B864" t="s">
         <v>75</v>
@@ -22936,7 +23119,7 @@
         <v>1</v>
       </c>
       <c r="G864" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="H864" t="s">
         <v>20</v>
@@ -22944,7 +23127,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B865" t="s">
         <v>77</v>

--- a/consolidado_mundial.xlsx
+++ b/consolidado_mundial.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$865</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -315,9 +315,6 @@
     <t xml:space="preserve">argentina </t>
   </si>
   <si>
-    <t>colombia</t>
-  </si>
-  <si>
     <t>francia</t>
   </si>
   <si>
@@ -433,6 +430,9 @@
   </si>
   <si>
     <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>Países bajos</t>
   </si>
 </sst>
 </file>
@@ -880,7 +880,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1053,7 +1053,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -1235,7 +1235,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
         <v>56</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
         <v>56</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
         <v>56</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
         <v>56</v>
@@ -1386,12 +1386,12 @@
         <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
         <v>56</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
         <v>56</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
         <v>56</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
         <v>56</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
         <v>65</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
         <v>65</v>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
         <v>65</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
         <v>65</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
         <v>70</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
         <v>70</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
         <v>73</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" t="s">
         <v>75</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>9</v>
@@ -4216,7 +4216,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>9</v>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>9</v>
@@ -4262,7 +4262,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>9</v>
@@ -4282,7 +4282,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>9</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>9</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>9</v>
@@ -4360,7 +4360,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>9</v>
@@ -4386,7 +4386,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>9</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>9</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>9</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>9</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>9</v>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>9</v>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>9</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>9</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>56</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>56</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>56</v>
@@ -4666,7 +4666,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>56</v>
@@ -4692,7 +4692,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>56</v>
@@ -4718,7 +4718,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>56</v>
@@ -4744,7 +4744,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>56</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>56</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>65</v>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>65</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>65</v>
@@ -4872,7 +4872,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>65</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>70</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>70</v>
@@ -4950,7 +4950,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>73</v>
@@ -4976,7 +4976,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>75</v>
@@ -5439,7 +5439,7 @@
         <v>80</v>
       </c>
       <c r="H178" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -5517,7 +5517,7 @@
         <v>29</v>
       </c>
       <c r="H181" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -5543,7 +5543,7 @@
         <v>54</v>
       </c>
       <c r="H182" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -5621,7 +5621,7 @@
         <v>40</v>
       </c>
       <c r="H185" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -5647,7 +5647,7 @@
         <v>94</v>
       </c>
       <c r="H186" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -5751,7 +5751,7 @@
         <v>46</v>
       </c>
       <c r="H190" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -5826,7 +5826,7 @@
         <v>1</v>
       </c>
       <c r="G193" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H193" t="s">
         <v>40</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B194" t="s">
         <v>9</v>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B195" t="s">
         <v>9</v>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B196" t="s">
         <v>9</v>
@@ -5912,7 +5912,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B197" t="s">
         <v>9</v>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B198" t="s">
         <v>9</v>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B199" t="s">
         <v>9</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B200" t="s">
         <v>9</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B201" t="s">
         <v>9</v>
@@ -6042,7 +6042,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B202" t="s">
         <v>9</v>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B203" t="s">
         <v>9</v>
@@ -6094,7 +6094,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B204" t="s">
         <v>9</v>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B205" t="s">
         <v>9</v>
@@ -6146,7 +6146,7 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B206" t="s">
         <v>9</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B207" t="s">
         <v>9</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B208" t="s">
         <v>9</v>
@@ -6224,7 +6224,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B209" t="s">
         <v>9</v>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B210" t="s">
         <v>56</v>
@@ -6276,7 +6276,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B211" t="s">
         <v>56</v>
@@ -6302,7 +6302,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B212" t="s">
         <v>56</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B213" t="s">
         <v>56</v>
@@ -6354,7 +6354,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B214" t="s">
         <v>56</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B215" t="s">
         <v>56</v>
@@ -6406,7 +6406,7 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B216" t="s">
         <v>56</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B217" t="s">
         <v>56</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B218" t="s">
         <v>65</v>
@@ -6484,7 +6484,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B219" t="s">
         <v>65</v>
@@ -6510,7 +6510,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B220" t="s">
         <v>65</v>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B221" t="s">
         <v>65</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B222" t="s">
         <v>70</v>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B223" t="s">
         <v>70</v>
@@ -6614,7 +6614,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B224" t="s">
         <v>73</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B225" t="s">
         <v>75</v>
@@ -6666,7 +6666,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B226" t="s">
         <v>9</v>
@@ -6692,7 +6692,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B227" t="s">
         <v>9</v>
@@ -6718,7 +6718,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B228" t="s">
         <v>9</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B229" t="s">
         <v>9</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B230" t="s">
         <v>9</v>
@@ -6796,7 +6796,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B231" t="s">
         <v>9</v>
@@ -6822,7 +6822,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B232" t="s">
         <v>9</v>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B233" t="s">
         <v>9</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B234" t="s">
         <v>9</v>
@@ -6900,7 +6900,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B235" t="s">
         <v>9</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B236" t="s">
         <v>9</v>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B237" t="s">
         <v>9</v>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B238" t="s">
         <v>9</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B239" t="s">
         <v>9</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B240" t="s">
         <v>9</v>
@@ -7056,7 +7056,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B241" t="s">
         <v>9</v>
@@ -7082,7 +7082,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B242" t="s">
         <v>56</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B243" t="s">
         <v>56</v>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B244" t="s">
         <v>56</v>
@@ -7160,7 +7160,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B245" t="s">
         <v>56</v>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B246" t="s">
         <v>56</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B247" t="s">
         <v>56</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B248" t="s">
         <v>56</v>
@@ -7264,7 +7264,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B249" t="s">
         <v>56</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B250" t="s">
         <v>65</v>
@@ -7316,7 +7316,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B251" t="s">
         <v>65</v>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B252" t="s">
         <v>65</v>
@@ -7368,7 +7368,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B253" t="s">
         <v>65</v>
@@ -7394,7 +7394,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B254" t="s">
         <v>70</v>
@@ -7420,7 +7420,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B255" t="s">
         <v>70</v>
@@ -7446,7 +7446,7 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B256" t="s">
         <v>73</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B257" t="s">
         <v>75</v>
@@ -7498,7 +7498,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B258" t="s">
         <v>9</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B259" t="s">
         <v>9</v>
@@ -7541,7 +7541,7 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B260" t="s">
         <v>9</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B261" t="s">
         <v>9</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B262" t="s">
         <v>9</v>
@@ -7619,7 +7619,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B263" t="s">
         <v>9</v>
@@ -7645,7 +7645,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B264" t="s">
         <v>9</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B265" t="s">
         <v>9</v>
@@ -7697,7 +7697,7 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B266" t="s">
         <v>9</v>
@@ -7718,12 +7718,12 @@
         <v>35</v>
       </c>
       <c r="H266" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B267" t="s">
         <v>9</v>
@@ -7740,7 +7740,7 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B268" t="s">
         <v>9</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B269" t="s">
         <v>9</v>
@@ -7792,7 +7792,7 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B270" t="s">
         <v>9</v>
@@ -7818,7 +7818,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B271" t="s">
         <v>9</v>
@@ -7844,7 +7844,7 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B272" t="s">
         <v>9</v>
@@ -7870,7 +7870,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B273" t="s">
         <v>9</v>
@@ -7896,7 +7896,7 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B274" t="s">
         <v>56</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B275" t="s">
         <v>56</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B276" t="s">
         <v>56</v>
@@ -7974,7 +7974,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B277" t="s">
         <v>56</v>
@@ -8000,7 +8000,7 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B278" t="s">
         <v>56</v>
@@ -8026,7 +8026,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B279" t="s">
         <v>56</v>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B280" t="s">
         <v>56</v>
@@ -8078,7 +8078,7 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B281" t="s">
         <v>56</v>
@@ -8104,7 +8104,7 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B282" t="s">
         <v>65</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B283" t="s">
         <v>65</v>
@@ -8156,7 +8156,7 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B284" t="s">
         <v>65</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B285" t="s">
         <v>65</v>
@@ -8208,7 +8208,7 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B286" t="s">
         <v>70</v>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B287" t="s">
         <v>70</v>
@@ -8260,7 +8260,7 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B288" t="s">
         <v>73</v>
@@ -8286,7 +8286,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B289" t="s">
         <v>75</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B290" t="s">
         <v>9</v>
@@ -8338,7 +8338,7 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B291" t="s">
         <v>9</v>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B292" t="s">
         <v>9</v>
@@ -8390,7 +8390,7 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B293" t="s">
         <v>9</v>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B294" t="s">
         <v>9</v>
@@ -8442,7 +8442,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B295" t="s">
         <v>9</v>
@@ -8468,7 +8468,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B296" t="s">
         <v>9</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B297" t="s">
         <v>9</v>
@@ -8520,7 +8520,7 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B298" t="s">
         <v>9</v>
@@ -8546,7 +8546,7 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B299" t="s">
         <v>9</v>
@@ -8572,7 +8572,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B300" t="s">
         <v>9</v>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B301" t="s">
         <v>9</v>
@@ -8624,7 +8624,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B302" t="s">
         <v>9</v>
@@ -8650,7 +8650,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B303" t="s">
         <v>9</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B304" t="s">
         <v>9</v>
@@ -8702,7 +8702,7 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B305" t="s">
         <v>9</v>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B306" t="s">
         <v>56</v>
@@ -8754,7 +8754,7 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B307" t="s">
         <v>56</v>
@@ -8780,7 +8780,7 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B308" t="s">
         <v>56</v>
@@ -8806,7 +8806,7 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B309" t="s">
         <v>56</v>
@@ -8832,7 +8832,7 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B310" t="s">
         <v>56</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B311" t="s">
         <v>56</v>
@@ -8867,7 +8867,7 @@
         <v>62</v>
       </c>
       <c r="D311" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E311">
         <v>1</v>
@@ -8884,7 +8884,7 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B312" t="s">
         <v>56</v>
@@ -8910,7 +8910,7 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B313" t="s">
         <v>56</v>
@@ -8936,7 +8936,7 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B314" t="s">
         <v>65</v>
@@ -8962,7 +8962,7 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B315" t="s">
         <v>65</v>
@@ -8988,7 +8988,7 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B316" t="s">
         <v>65</v>
@@ -9014,7 +9014,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B317" t="s">
         <v>65</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B318" t="s">
         <v>70</v>
@@ -9066,7 +9066,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B319" t="s">
         <v>70</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B320" t="s">
         <v>73</v>
@@ -9118,7 +9118,7 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B321" t="s">
         <v>75</v>
@@ -9144,7 +9144,7 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B322" t="s">
         <v>9</v>
@@ -9170,7 +9170,7 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B323" t="s">
         <v>9</v>
@@ -9196,7 +9196,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B324" t="s">
         <v>9</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B325" t="s">
         <v>9</v>
@@ -9248,7 +9248,7 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B326" t="s">
         <v>9</v>
@@ -9274,7 +9274,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B327" t="s">
         <v>9</v>
@@ -9300,7 +9300,7 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B328" t="s">
         <v>9</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B329" t="s">
         <v>9</v>
@@ -9349,7 +9349,7 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B330" t="s">
         <v>9</v>
@@ -9375,7 +9375,7 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B331" t="s">
         <v>9</v>
@@ -9401,7 +9401,7 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B332" t="s">
         <v>9</v>
@@ -9427,7 +9427,7 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B333" t="s">
         <v>9</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B334" t="s">
         <v>9</v>
@@ -9476,7 +9476,7 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B335" t="s">
         <v>9</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B336" t="s">
         <v>9</v>
@@ -9528,7 +9528,7 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B337" t="s">
         <v>9</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B338" t="s">
         <v>56</v>
@@ -9580,7 +9580,7 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B339" t="s">
         <v>56</v>
@@ -9606,7 +9606,7 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B340" t="s">
         <v>56</v>
@@ -9632,7 +9632,7 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B341" t="s">
         <v>56</v>
@@ -9658,7 +9658,7 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B342" t="s">
         <v>56</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B343" t="s">
         <v>56</v>
@@ -9710,7 +9710,7 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B344" t="s">
         <v>56</v>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B345" t="s">
         <v>56</v>
@@ -9762,7 +9762,7 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B346" t="s">
         <v>65</v>
@@ -9788,7 +9788,7 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B347" t="s">
         <v>65</v>
@@ -9814,7 +9814,7 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B348" t="s">
         <v>65</v>
@@ -9840,7 +9840,7 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B349" t="s">
         <v>65</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B350" t="s">
         <v>70</v>
@@ -9892,7 +9892,7 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B351" t="s">
         <v>70</v>
@@ -9918,7 +9918,7 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B352" t="s">
         <v>73</v>
@@ -9944,7 +9944,7 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B353" t="s">
         <v>75</v>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B354" t="s">
         <v>9</v>
@@ -9996,7 +9996,7 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B355" t="s">
         <v>9</v>
@@ -10022,7 +10022,7 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B356" t="s">
         <v>9</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B357" t="s">
         <v>9</v>
@@ -10074,7 +10074,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B358" t="s">
         <v>9</v>
@@ -10100,7 +10100,7 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B359" t="s">
         <v>9</v>
@@ -10126,7 +10126,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B360" t="s">
         <v>9</v>
@@ -10152,7 +10152,7 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B361" t="s">
         <v>9</v>
@@ -10178,7 +10178,7 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B362" t="s">
         <v>9</v>
@@ -10204,7 +10204,7 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B363" t="s">
         <v>9</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B364" t="s">
         <v>9</v>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B365" t="s">
         <v>9</v>
@@ -10282,7 +10282,7 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B366" t="s">
         <v>9</v>
@@ -10308,7 +10308,7 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B367" t="s">
         <v>9</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B368" t="s">
         <v>9</v>
@@ -10360,7 +10360,7 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B369" t="s">
         <v>9</v>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B370" t="s">
         <v>56</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B371" t="s">
         <v>56</v>
@@ -10438,7 +10438,7 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B372" t="s">
         <v>56</v>
@@ -10464,7 +10464,7 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B373" t="s">
         <v>56</v>
@@ -10490,7 +10490,7 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B374" t="s">
         <v>56</v>
@@ -10516,7 +10516,7 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B375" t="s">
         <v>56</v>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B376" t="s">
         <v>56</v>
@@ -10568,7 +10568,7 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B377" t="s">
         <v>56</v>
@@ -10594,7 +10594,7 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B378" t="s">
         <v>65</v>
@@ -10620,7 +10620,7 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B379" t="s">
         <v>65</v>
@@ -10646,7 +10646,7 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B380" t="s">
         <v>65</v>
@@ -10672,7 +10672,7 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B381" t="s">
         <v>65</v>
@@ -10698,7 +10698,7 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B382" t="s">
         <v>70</v>
@@ -10724,7 +10724,7 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B383" t="s">
         <v>70</v>
@@ -10750,7 +10750,7 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B384" t="s">
         <v>73</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B385" t="s">
         <v>75</v>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B386" t="s">
         <v>9</v>
@@ -10828,7 +10828,7 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B387" t="s">
         <v>9</v>
@@ -10854,7 +10854,7 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B388" t="s">
         <v>9</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B389" t="s">
         <v>9</v>
@@ -10901,12 +10901,12 @@
         <v>20</v>
       </c>
       <c r="H389" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B390" t="s">
         <v>9</v>
@@ -10932,7 +10932,7 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B391" t="s">
         <v>9</v>
@@ -10953,12 +10953,12 @@
         <v>26</v>
       </c>
       <c r="H391" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B392" t="s">
         <v>9</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B393" t="s">
         <v>9</v>
@@ -11005,12 +11005,12 @@
         <v>32</v>
       </c>
       <c r="H393" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B394" t="s">
         <v>9</v>
@@ -11036,7 +11036,7 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B395" t="s">
         <v>9</v>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B396" t="s">
         <v>9</v>
@@ -11088,7 +11088,7 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B397" t="s">
         <v>9</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B398" t="s">
         <v>9</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B399" t="s">
         <v>9</v>
@@ -11166,7 +11166,7 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B400" t="s">
         <v>9</v>
@@ -11192,7 +11192,7 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B401" t="s">
         <v>9</v>
@@ -11218,7 +11218,7 @@
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B402" t="s">
         <v>56</v>
@@ -11244,7 +11244,7 @@
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B403" t="s">
         <v>56</v>
@@ -11265,12 +11265,12 @@
         <v>78</v>
       </c>
       <c r="H403" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B404" t="s">
         <v>56</v>
@@ -11296,7 +11296,7 @@
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B405" t="s">
         <v>56</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B406" t="s">
         <v>56</v>
@@ -11348,7 +11348,7 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B407" t="s">
         <v>56</v>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B408" t="s">
         <v>56</v>
@@ -11400,7 +11400,7 @@
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B409" t="s">
         <v>56</v>
@@ -11426,7 +11426,7 @@
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B410" t="s">
         <v>65</v>
@@ -11452,7 +11452,7 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B411" t="s">
         <v>65</v>
@@ -11478,7 +11478,7 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B412" t="s">
         <v>65</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B413" t="s">
         <v>65</v>
@@ -11530,7 +11530,7 @@
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B414" t="s">
         <v>70</v>
@@ -11556,7 +11556,7 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B415" t="s">
         <v>70</v>
@@ -11582,7 +11582,7 @@
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B416" t="s">
         <v>73</v>
@@ -11603,12 +11603,12 @@
         <v>19</v>
       </c>
       <c r="H416" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B417" t="s">
         <v>75</v>
@@ -11634,7 +11634,7 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B418" t="s">
         <v>9</v>
@@ -11660,7 +11660,7 @@
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B419" t="s">
         <v>9</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B420" t="s">
         <v>9</v>
@@ -11712,7 +11712,7 @@
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B421" t="s">
         <v>9</v>
@@ -11738,7 +11738,7 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B422" t="s">
         <v>9</v>
@@ -11764,7 +11764,7 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B423" t="s">
         <v>9</v>
@@ -11790,7 +11790,7 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B424" t="s">
         <v>9</v>
@@ -11816,7 +11816,7 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B425" t="s">
         <v>9</v>
@@ -11842,7 +11842,7 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B426" t="s">
         <v>9</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B427" t="s">
         <v>9</v>
@@ -11894,7 +11894,7 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B428" t="s">
         <v>9</v>
@@ -11920,7 +11920,7 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B429" t="s">
         <v>9</v>
@@ -11946,7 +11946,7 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B430" t="s">
         <v>9</v>
@@ -11972,7 +11972,7 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B431" t="s">
         <v>9</v>
@@ -11998,7 +11998,7 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B432" t="s">
         <v>9</v>
@@ -12024,7 +12024,7 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B433" t="s">
         <v>9</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B434" t="s">
         <v>56</v>
@@ -12076,7 +12076,7 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B435" t="s">
         <v>56</v>
@@ -12102,7 +12102,7 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B436" t="s">
         <v>56</v>
@@ -12128,7 +12128,7 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B437" t="s">
         <v>56</v>
@@ -12154,7 +12154,7 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B438" t="s">
         <v>56</v>
@@ -12180,7 +12180,7 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B439" t="s">
         <v>56</v>
@@ -12206,7 +12206,7 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B440" t="s">
         <v>56</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B441" t="s">
         <v>56</v>
@@ -12258,7 +12258,7 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B442" t="s">
         <v>65</v>
@@ -12284,7 +12284,7 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B443" t="s">
         <v>65</v>
@@ -12310,7 +12310,7 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B444" t="s">
         <v>65</v>
@@ -12336,7 +12336,7 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B445" t="s">
         <v>65</v>
@@ -12362,7 +12362,7 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B446" t="s">
         <v>70</v>
@@ -12388,7 +12388,7 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B447" t="s">
         <v>70</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B448" t="s">
         <v>73</v>
@@ -12440,7 +12440,7 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B449" t="s">
         <v>75</v>
@@ -12466,7 +12466,7 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B450" t="s">
         <v>9</v>
@@ -12492,7 +12492,7 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B451" t="s">
         <v>9</v>
@@ -12518,7 +12518,7 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B452" t="s">
         <v>9</v>
@@ -12544,7 +12544,7 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B453" t="s">
         <v>9</v>
@@ -12570,7 +12570,7 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B454" t="s">
         <v>9</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B455" t="s">
         <v>9</v>
@@ -12622,7 +12622,7 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B456" t="s">
         <v>9</v>
@@ -12648,7 +12648,7 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B457" t="s">
         <v>9</v>
@@ -12674,7 +12674,7 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B458" t="s">
         <v>9</v>
@@ -12700,7 +12700,7 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B459" t="s">
         <v>9</v>
@@ -12726,7 +12726,7 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B460" t="s">
         <v>9</v>
@@ -12752,7 +12752,7 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B461" t="s">
         <v>9</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B462" t="s">
         <v>9</v>
@@ -12804,7 +12804,7 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B463" t="s">
         <v>9</v>
@@ -12830,7 +12830,7 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B464" t="s">
         <v>9</v>
@@ -12856,7 +12856,7 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B465" t="s">
         <v>9</v>
@@ -12882,7 +12882,7 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B466" t="s">
         <v>56</v>
@@ -12908,7 +12908,7 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B467" t="s">
         <v>56</v>
@@ -12934,7 +12934,7 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B468" t="s">
         <v>56</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B469" t="s">
         <v>56</v>
@@ -12986,7 +12986,7 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B470" t="s">
         <v>56</v>
@@ -13012,7 +13012,7 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B471" t="s">
         <v>56</v>
@@ -13038,7 +13038,7 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B472" t="s">
         <v>56</v>
@@ -13064,7 +13064,7 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B473" t="s">
         <v>56</v>
@@ -13090,7 +13090,7 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B474" t="s">
         <v>65</v>
@@ -13116,7 +13116,7 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B475" t="s">
         <v>65</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B476" t="s">
         <v>65</v>
@@ -13168,7 +13168,7 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B477" t="s">
         <v>65</v>
@@ -13194,7 +13194,7 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B478" t="s">
         <v>70</v>
@@ -13220,7 +13220,7 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B479" t="s">
         <v>70</v>
@@ -13246,7 +13246,7 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B480" t="s">
         <v>73</v>
@@ -13272,7 +13272,7 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B481" t="s">
         <v>75</v>
@@ -13298,7 +13298,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B482" t="s">
         <v>9</v>
@@ -13315,7 +13315,7 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B483" t="s">
         <v>9</v>
@@ -13332,7 +13332,7 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B484" t="s">
         <v>9</v>
@@ -13358,7 +13358,7 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B485" t="s">
         <v>9</v>
@@ -13375,7 +13375,7 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B486" t="s">
         <v>9</v>
@@ -13401,7 +13401,7 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B487" t="s">
         <v>9</v>
@@ -13427,7 +13427,7 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B488" t="s">
         <v>9</v>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B489" t="s">
         <v>9</v>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B490" t="s">
         <v>9</v>
@@ -13505,7 +13505,7 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B491" t="s">
         <v>9</v>
@@ -13522,7 +13522,7 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B492" t="s">
         <v>9</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B493" t="s">
         <v>9</v>
@@ -13574,7 +13574,7 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B494" t="s">
         <v>9</v>
@@ -13600,7 +13600,7 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B495" t="s">
         <v>9</v>
@@ -13623,7 +13623,7 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B496" t="s">
         <v>9</v>
@@ -13649,7 +13649,7 @@
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B497" t="s">
         <v>9</v>
@@ -13675,7 +13675,7 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B498" t="s">
         <v>56</v>
@@ -13701,7 +13701,7 @@
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B499" t="s">
         <v>56</v>
@@ -13727,7 +13727,7 @@
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B500" t="s">
         <v>56</v>
@@ -13750,7 +13750,7 @@
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B501" t="s">
         <v>56</v>
@@ -13776,7 +13776,7 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B502" t="s">
         <v>56</v>
@@ -13802,7 +13802,7 @@
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B503" t="s">
         <v>56</v>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B504" t="s">
         <v>56</v>
@@ -13854,7 +13854,7 @@
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B505" t="s">
         <v>56</v>
@@ -13880,7 +13880,7 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B506" t="s">
         <v>65</v>
@@ -13906,7 +13906,7 @@
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B507" t="s">
         <v>65</v>
@@ -13924,7 +13924,7 @@
         <v>0</v>
       </c>
       <c r="G507" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H507" t="s">
         <v>46</v>
@@ -13932,7 +13932,7 @@
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B508" t="s">
         <v>65</v>
@@ -13958,7 +13958,7 @@
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B509" t="s">
         <v>65</v>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B510" t="s">
         <v>70</v>
@@ -14010,7 +14010,7 @@
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B511" t="s">
         <v>70</v>
@@ -14036,7 +14036,7 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B512" t="s">
         <v>73</v>
@@ -14062,7 +14062,7 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B513" t="s">
         <v>75</v>
@@ -14088,7 +14088,7 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B514" t="s">
         <v>9</v>
@@ -14114,7 +14114,7 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B515" t="s">
         <v>9</v>
@@ -14140,7 +14140,7 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B516" t="s">
         <v>9</v>
@@ -14166,7 +14166,7 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B517" t="s">
         <v>9</v>
@@ -14192,7 +14192,7 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B518" t="s">
         <v>9</v>
@@ -14218,7 +14218,7 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B519" t="s">
         <v>9</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B520" t="s">
         <v>9</v>
@@ -14270,7 +14270,7 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B521" t="s">
         <v>9</v>
@@ -14296,7 +14296,7 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B522" t="s">
         <v>9</v>
@@ -14322,7 +14322,7 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B523" t="s">
         <v>9</v>
@@ -14348,7 +14348,7 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B524" t="s">
         <v>9</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B525" t="s">
         <v>9</v>
@@ -14400,7 +14400,7 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B526" t="s">
         <v>9</v>
@@ -14426,7 +14426,7 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B527" t="s">
         <v>9</v>
@@ -14452,7 +14452,7 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B528" t="s">
         <v>9</v>
@@ -14478,7 +14478,7 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B529" t="s">
         <v>9</v>
@@ -14504,7 +14504,7 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B530" t="s">
         <v>56</v>
@@ -14530,7 +14530,7 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B531" t="s">
         <v>56</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B532" t="s">
         <v>56</v>
@@ -14582,7 +14582,7 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B533" t="s">
         <v>56</v>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B534" t="s">
         <v>56</v>
@@ -14634,7 +14634,7 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B535" t="s">
         <v>56</v>
@@ -14660,7 +14660,7 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B536" t="s">
         <v>56</v>
@@ -14686,7 +14686,7 @@
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B537" t="s">
         <v>56</v>
@@ -14712,7 +14712,7 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B538" t="s">
         <v>65</v>
@@ -14738,7 +14738,7 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B539" t="s">
         <v>65</v>
@@ -14764,7 +14764,7 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B540" t="s">
         <v>65</v>
@@ -14790,7 +14790,7 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B541" t="s">
         <v>65</v>
@@ -14816,7 +14816,7 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B542" t="s">
         <v>70</v>
@@ -14842,7 +14842,7 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B543" t="s">
         <v>70</v>
@@ -14868,7 +14868,7 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B544" t="s">
         <v>73</v>
@@ -14894,7 +14894,7 @@
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B545" t="s">
         <v>75</v>
@@ -14920,7 +14920,7 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B546" t="s">
         <v>9</v>
@@ -14937,7 +14937,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B547" t="s">
         <v>9</v>
@@ -14954,7 +14954,7 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B548" t="s">
         <v>9</v>
@@ -14980,7 +14980,7 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B549" t="s">
         <v>9</v>
@@ -14997,7 +14997,7 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B550" t="s">
         <v>9</v>
@@ -15023,7 +15023,7 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B551" t="s">
         <v>9</v>
@@ -15049,7 +15049,7 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B552" t="s">
         <v>9</v>
@@ -15075,7 +15075,7 @@
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B553" t="s">
         <v>9</v>
@@ -15092,7 +15092,7 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B554" t="s">
         <v>9</v>
@@ -15109,7 +15109,7 @@
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B555" t="s">
         <v>9</v>
@@ -15126,7 +15126,7 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B556" t="s">
         <v>9</v>
@@ -15143,7 +15143,7 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B557" t="s">
         <v>9</v>
@@ -15169,7 +15169,7 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B558" t="s">
         <v>9</v>
@@ -15195,7 +15195,7 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B559" t="s">
         <v>9</v>
@@ -15221,7 +15221,7 @@
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B560" t="s">
         <v>9</v>
@@ -15247,7 +15247,7 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B561" t="s">
         <v>9</v>
@@ -15273,7 +15273,7 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B562" t="s">
         <v>56</v>
@@ -15299,7 +15299,7 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B563" t="s">
         <v>56</v>
@@ -15325,7 +15325,7 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B564" t="s">
         <v>56</v>
@@ -15351,7 +15351,7 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B565" t="s">
         <v>56</v>
@@ -15377,7 +15377,7 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B566" t="s">
         <v>56</v>
@@ -15403,7 +15403,7 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B567" t="s">
         <v>56</v>
@@ -15429,7 +15429,7 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B568" t="s">
         <v>56</v>
@@ -15455,7 +15455,7 @@
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B569" t="s">
         <v>56</v>
@@ -15478,7 +15478,7 @@
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B570" t="s">
         <v>65</v>
@@ -15504,7 +15504,7 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B571" t="s">
         <v>65</v>
@@ -15530,7 +15530,7 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B572" t="s">
         <v>65</v>
@@ -15556,7 +15556,7 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B573" t="s">
         <v>65</v>
@@ -15582,7 +15582,7 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B574" t="s">
         <v>70</v>
@@ -15608,7 +15608,7 @@
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B575" t="s">
         <v>70</v>
@@ -15634,7 +15634,7 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B576" t="s">
         <v>73</v>
@@ -15660,7 +15660,7 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B577" t="s">
         <v>75</v>
@@ -15686,7 +15686,7 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B578" t="s">
         <v>9</v>
@@ -15712,7 +15712,7 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B579" t="s">
         <v>9</v>
@@ -15738,7 +15738,7 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B580" t="s">
         <v>9</v>
@@ -15764,7 +15764,7 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B581" t="s">
         <v>9</v>
@@ -15790,7 +15790,7 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B582" t="s">
         <v>9</v>
@@ -15816,7 +15816,7 @@
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B583" t="s">
         <v>9</v>
@@ -15842,7 +15842,7 @@
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B584" t="s">
         <v>9</v>
@@ -15868,7 +15868,7 @@
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B585" t="s">
         <v>9</v>
@@ -15894,7 +15894,7 @@
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B586" t="s">
         <v>9</v>
@@ -15920,7 +15920,7 @@
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B587" t="s">
         <v>9</v>
@@ -15946,7 +15946,7 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B588" t="s">
         <v>9</v>
@@ -15972,7 +15972,7 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B589" t="s">
         <v>9</v>
@@ -15998,7 +15998,7 @@
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B590" t="s">
         <v>9</v>
@@ -16024,7 +16024,7 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B591" t="s">
         <v>9</v>
@@ -16050,7 +16050,7 @@
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B592" t="s">
         <v>9</v>
@@ -16076,7 +16076,7 @@
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B593" t="s">
         <v>9</v>
@@ -16102,7 +16102,7 @@
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B594" t="s">
         <v>56</v>
@@ -16128,7 +16128,7 @@
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B595" t="s">
         <v>56</v>
@@ -16154,7 +16154,7 @@
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B596" t="s">
         <v>56</v>
@@ -16180,7 +16180,7 @@
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B597" t="s">
         <v>56</v>
@@ -16206,7 +16206,7 @@
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B598" t="s">
         <v>56</v>
@@ -16232,7 +16232,7 @@
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B599" t="s">
         <v>56</v>
@@ -16241,7 +16241,7 @@
         <v>62</v>
       </c>
       <c r="D599" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E599">
         <v>1</v>
@@ -16258,7 +16258,7 @@
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B600" t="s">
         <v>56</v>
@@ -16284,7 +16284,7 @@
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B601" t="s">
         <v>56</v>
@@ -16310,7 +16310,7 @@
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B602" t="s">
         <v>65</v>
@@ -16336,7 +16336,7 @@
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B603" t="s">
         <v>65</v>
@@ -16362,7 +16362,7 @@
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B604" t="s">
         <v>65</v>
@@ -16388,7 +16388,7 @@
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B605" t="s">
         <v>65</v>
@@ -16414,7 +16414,7 @@
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B606" t="s">
         <v>70</v>
@@ -16440,7 +16440,7 @@
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B607" t="s">
         <v>70</v>
@@ -16466,7 +16466,7 @@
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B608" t="s">
         <v>73</v>
@@ -16492,7 +16492,7 @@
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B609" t="s">
         <v>75</v>
@@ -16518,7 +16518,7 @@
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B610" t="s">
         <v>9</v>
@@ -16544,7 +16544,7 @@
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B611" t="s">
         <v>9</v>
@@ -16570,7 +16570,7 @@
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B612" t="s">
         <v>9</v>
@@ -16596,7 +16596,7 @@
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B613" t="s">
         <v>9</v>
@@ -16622,7 +16622,7 @@
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B614" t="s">
         <v>9</v>
@@ -16648,7 +16648,7 @@
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B615" t="s">
         <v>9</v>
@@ -16674,7 +16674,7 @@
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B616" t="s">
         <v>9</v>
@@ -16700,7 +16700,7 @@
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B617" t="s">
         <v>9</v>
@@ -16726,7 +16726,7 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B618" t="s">
         <v>9</v>
@@ -16752,7 +16752,7 @@
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B619" t="s">
         <v>9</v>
@@ -16778,7 +16778,7 @@
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B620" t="s">
         <v>9</v>
@@ -16804,7 +16804,7 @@
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B621" t="s">
         <v>9</v>
@@ -16830,7 +16830,7 @@
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B622" t="s">
         <v>9</v>
@@ -16856,7 +16856,7 @@
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B623" t="s">
         <v>9</v>
@@ -16882,7 +16882,7 @@
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B624" t="s">
         <v>9</v>
@@ -16908,7 +16908,7 @@
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -16934,7 +16934,7 @@
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B626" t="s">
         <v>56</v>
@@ -16960,7 +16960,7 @@
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B627" t="s">
         <v>56</v>
@@ -16986,7 +16986,7 @@
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B628" t="s">
         <v>56</v>
@@ -17012,7 +17012,7 @@
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B629" t="s">
         <v>56</v>
@@ -17038,7 +17038,7 @@
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B630" t="s">
         <v>56</v>
@@ -17064,7 +17064,7 @@
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B631" t="s">
         <v>56</v>
@@ -17090,7 +17090,7 @@
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B632" t="s">
         <v>56</v>
@@ -17116,7 +17116,7 @@
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B633" t="s">
         <v>56</v>
@@ -17142,7 +17142,7 @@
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B634" t="s">
         <v>65</v>
@@ -17168,7 +17168,7 @@
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B635" t="s">
         <v>65</v>
@@ -17194,7 +17194,7 @@
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B636" t="s">
         <v>65</v>
@@ -17220,7 +17220,7 @@
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B637" t="s">
         <v>65</v>
@@ -17246,10 +17246,10 @@
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
+        <v>113</v>
+      </c>
+      <c r="B638" t="s">
         <v>114</v>
-      </c>
-      <c r="B638" t="s">
-        <v>115</v>
       </c>
       <c r="C638" t="s">
         <v>71</v>
@@ -17272,10 +17272,10 @@
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
+        <v>113</v>
+      </c>
+      <c r="B639" t="s">
         <v>114</v>
-      </c>
-      <c r="B639" t="s">
-        <v>115</v>
       </c>
       <c r="C639" t="s">
         <v>72</v>
@@ -17298,7 +17298,7 @@
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B640" t="s">
         <v>73</v>
@@ -17324,7 +17324,7 @@
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B641" t="s">
         <v>75</v>
@@ -17350,7 +17350,7 @@
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B642" t="s">
         <v>9</v>
@@ -17376,7 +17376,7 @@
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B643" t="s">
         <v>9</v>
@@ -17402,7 +17402,7 @@
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B644" t="s">
         <v>9</v>
@@ -17428,7 +17428,7 @@
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B645" t="s">
         <v>9</v>
@@ -17454,7 +17454,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B646" t="s">
         <v>9</v>
@@ -17480,7 +17480,7 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B647" t="s">
         <v>9</v>
@@ -17506,7 +17506,7 @@
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B648" t="s">
         <v>9</v>
@@ -17532,7 +17532,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B649" t="s">
         <v>9</v>
@@ -17558,7 +17558,7 @@
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B650" t="s">
         <v>9</v>
@@ -17584,7 +17584,7 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B651" t="s">
         <v>9</v>
@@ -17610,7 +17610,7 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B652" t="s">
         <v>9</v>
@@ -17636,7 +17636,7 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B653" t="s">
         <v>9</v>
@@ -17662,7 +17662,7 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B654" t="s">
         <v>9</v>
@@ -17688,7 +17688,7 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B655" t="s">
         <v>9</v>
@@ -17714,7 +17714,7 @@
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B656" t="s">
         <v>9</v>
@@ -17740,7 +17740,7 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B657" t="s">
         <v>9</v>
@@ -17766,7 +17766,7 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B658" t="s">
         <v>56</v>
@@ -17792,7 +17792,7 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B659" t="s">
         <v>56</v>
@@ -17818,7 +17818,7 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B660" t="s">
         <v>56</v>
@@ -17844,7 +17844,7 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B661" t="s">
         <v>56</v>
@@ -17870,7 +17870,7 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B662" t="s">
         <v>56</v>
@@ -17896,7 +17896,7 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B663" t="s">
         <v>56</v>
@@ -17922,7 +17922,7 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B664" t="s">
         <v>56</v>
@@ -17948,7 +17948,7 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B665" t="s">
         <v>56</v>
@@ -17974,7 +17974,7 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B666" t="s">
         <v>65</v>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B667" t="s">
         <v>65</v>
@@ -18026,7 +18026,7 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B668" t="s">
         <v>65</v>
@@ -18052,7 +18052,7 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B669" t="s">
         <v>65</v>
@@ -18078,7 +18078,7 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B670" t="s">
         <v>70</v>
@@ -18104,7 +18104,7 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B671" t="s">
         <v>70</v>
@@ -18130,7 +18130,7 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B672" t="s">
         <v>73</v>
@@ -18156,7 +18156,7 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B673" t="s">
         <v>75</v>
@@ -18182,7 +18182,7 @@
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B674" t="s">
         <v>9</v>
@@ -18208,7 +18208,7 @@
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B675" t="s">
         <v>9</v>
@@ -18234,7 +18234,7 @@
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B676" t="s">
         <v>9</v>
@@ -18260,7 +18260,7 @@
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B677" t="s">
         <v>9</v>
@@ -18286,7 +18286,7 @@
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B678" t="s">
         <v>9</v>
@@ -18312,7 +18312,7 @@
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B679" t="s">
         <v>9</v>
@@ -18338,7 +18338,7 @@
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B680" t="s">
         <v>9</v>
@@ -18364,7 +18364,7 @@
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B681" t="s">
         <v>9</v>
@@ -18390,7 +18390,7 @@
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B682" t="s">
         <v>9</v>
@@ -18416,7 +18416,7 @@
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B683" t="s">
         <v>9</v>
@@ -18442,7 +18442,7 @@
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B684" t="s">
         <v>9</v>
@@ -18468,7 +18468,7 @@
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B685" t="s">
         <v>9</v>
@@ -18494,7 +18494,7 @@
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B686" t="s">
         <v>9</v>
@@ -18520,7 +18520,7 @@
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B687" t="s">
         <v>9</v>
@@ -18546,7 +18546,7 @@
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B688" t="s">
         <v>9</v>
@@ -18572,7 +18572,7 @@
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B689" t="s">
         <v>9</v>
@@ -18598,7 +18598,7 @@
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B690" t="s">
         <v>56</v>
@@ -18624,7 +18624,7 @@
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B691" t="s">
         <v>56</v>
@@ -18650,7 +18650,7 @@
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B692" t="s">
         <v>56</v>
@@ -18676,7 +18676,7 @@
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B693" t="s">
         <v>56</v>
@@ -18702,7 +18702,7 @@
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B694" t="s">
         <v>56</v>
@@ -18728,7 +18728,7 @@
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B695" t="s">
         <v>56</v>
@@ -18754,7 +18754,7 @@
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B696" t="s">
         <v>56</v>
@@ -18780,7 +18780,7 @@
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B697" t="s">
         <v>56</v>
@@ -18806,7 +18806,7 @@
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B698" t="s">
         <v>65</v>
@@ -18832,7 +18832,7 @@
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B699" t="s">
         <v>65</v>
@@ -18858,7 +18858,7 @@
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B700" t="s">
         <v>65</v>
@@ -18884,7 +18884,7 @@
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B701" t="s">
         <v>65</v>
@@ -18910,7 +18910,7 @@
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B702" t="s">
         <v>70</v>
@@ -18936,7 +18936,7 @@
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B703" t="s">
         <v>70</v>
@@ -18962,7 +18962,7 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B704" t="s">
         <v>73</v>
@@ -18988,7 +18988,7 @@
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B705" t="s">
         <v>75</v>
@@ -19014,7 +19014,7 @@
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B706" t="s">
         <v>9</v>
@@ -19031,7 +19031,7 @@
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B707" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B708" t="s">
         <v>9</v>
@@ -19074,7 +19074,7 @@
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B709" t="s">
         <v>9</v>
@@ -19091,7 +19091,7 @@
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B710" t="s">
         <v>9</v>
@@ -19117,7 +19117,7 @@
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B711" t="s">
         <v>9</v>
@@ -19143,7 +19143,7 @@
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B712" t="s">
         <v>9</v>
@@ -19169,7 +19169,7 @@
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B713" t="s">
         <v>9</v>
@@ -19195,7 +19195,7 @@
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B714" t="s">
         <v>9</v>
@@ -19221,7 +19221,7 @@
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B715" t="s">
         <v>9</v>
@@ -19238,7 +19238,7 @@
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B716" t="s">
         <v>9</v>
@@ -19264,7 +19264,7 @@
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B717" t="s">
         <v>9</v>
@@ -19290,7 +19290,7 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B718" t="s">
         <v>9</v>
@@ -19316,7 +19316,7 @@
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B719" t="s">
         <v>9</v>
@@ -19342,7 +19342,7 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B720" t="s">
         <v>9</v>
@@ -19368,7 +19368,7 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B721" t="s">
         <v>9</v>
@@ -19394,7 +19394,7 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B722" t="s">
         <v>56</v>
@@ -19420,7 +19420,7 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B723" t="s">
         <v>56</v>
@@ -19446,7 +19446,7 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B724" t="s">
         <v>56</v>
@@ -19472,7 +19472,7 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B725" t="s">
         <v>56</v>
@@ -19498,7 +19498,7 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B726" t="s">
         <v>56</v>
@@ -19524,7 +19524,7 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B727" t="s">
         <v>56</v>
@@ -19550,7 +19550,7 @@
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B728" t="s">
         <v>56</v>
@@ -19576,7 +19576,7 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B729" t="s">
         <v>56</v>
@@ -19599,7 +19599,7 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B730" t="s">
         <v>65</v>
@@ -19625,7 +19625,7 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B731" t="s">
         <v>65</v>
@@ -19651,7 +19651,7 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B732" t="s">
         <v>65</v>
@@ -19677,7 +19677,7 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B733" t="s">
         <v>65</v>
@@ -19703,7 +19703,7 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B734" t="s">
         <v>70</v>
@@ -19729,7 +19729,7 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B735" t="s">
         <v>70</v>
@@ -19755,7 +19755,7 @@
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B736" t="s">
         <v>73</v>
@@ -19781,7 +19781,7 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B737" t="s">
         <v>75</v>
@@ -19807,7 +19807,7 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B738" t="s">
         <v>9</v>
@@ -19833,7 +19833,7 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B739" t="s">
         <v>9</v>
@@ -19859,7 +19859,7 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B740" t="s">
         <v>9</v>
@@ -19885,7 +19885,7 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B741" t="s">
         <v>9</v>
@@ -19911,7 +19911,7 @@
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B742" t="s">
         <v>9</v>
@@ -19937,7 +19937,7 @@
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B743" t="s">
         <v>9</v>
@@ -19963,7 +19963,7 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B744" t="s">
         <v>9</v>
@@ -19989,7 +19989,7 @@
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B745" t="s">
         <v>9</v>
@@ -20015,7 +20015,7 @@
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B746" t="s">
         <v>9</v>
@@ -20041,7 +20041,7 @@
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B747" t="s">
         <v>9</v>
@@ -20067,7 +20067,7 @@
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B748" t="s">
         <v>9</v>
@@ -20093,7 +20093,7 @@
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B749" t="s">
         <v>9</v>
@@ -20119,7 +20119,7 @@
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B750" t="s">
         <v>9</v>
@@ -20145,7 +20145,7 @@
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B751" t="s">
         <v>9</v>
@@ -20171,7 +20171,7 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B752" t="s">
         <v>9</v>
@@ -20197,7 +20197,7 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B753" t="s">
         <v>9</v>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B754" t="s">
         <v>56</v>
@@ -20249,7 +20249,7 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B755" t="s">
         <v>56</v>
@@ -20275,7 +20275,7 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B756" t="s">
         <v>56</v>
@@ -20293,7 +20293,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H756" t="s">
         <v>19</v>
@@ -20301,7 +20301,7 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B757" t="s">
         <v>56</v>
@@ -20327,7 +20327,7 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B758" t="s">
         <v>56</v>
@@ -20353,7 +20353,7 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B759" t="s">
         <v>56</v>
@@ -20379,7 +20379,7 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B760" t="s">
         <v>56</v>
@@ -20405,7 +20405,7 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B761" t="s">
         <v>56</v>
@@ -20431,7 +20431,7 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B762" t="s">
         <v>65</v>
@@ -20457,7 +20457,7 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B763" t="s">
         <v>65</v>
@@ -20483,7 +20483,7 @@
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B764" t="s">
         <v>65</v>
@@ -20509,7 +20509,7 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B765" t="s">
         <v>65</v>
@@ -20535,7 +20535,7 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B766" t="s">
         <v>70</v>
@@ -20561,7 +20561,7 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B767" t="s">
         <v>70</v>
@@ -20587,7 +20587,7 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B768" t="s">
         <v>73</v>
@@ -20613,7 +20613,7 @@
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B769" t="s">
         <v>75</v>
@@ -20639,7 +20639,7 @@
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B770" t="s">
         <v>9</v>
@@ -20656,7 +20656,7 @@
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B771" t="s">
         <v>9</v>
@@ -20677,12 +20677,12 @@
         <v>14</v>
       </c>
       <c r="H771" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B772" t="s">
         <v>9</v>
@@ -20703,12 +20703,12 @@
         <v>17</v>
       </c>
       <c r="H772" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B773" t="s">
         <v>9</v>
@@ -20729,12 +20729,12 @@
         <v>20</v>
       </c>
       <c r="H773" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B774" t="s">
         <v>9</v>
@@ -20760,7 +20760,7 @@
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B775" t="s">
         <v>9</v>
@@ -20781,12 +20781,12 @@
         <v>26</v>
       </c>
       <c r="H775" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B776" t="s">
         <v>9</v>
@@ -20812,7 +20812,7 @@
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B777" t="s">
         <v>9</v>
@@ -20833,12 +20833,12 @@
         <v>32</v>
       </c>
       <c r="H777" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B778" t="s">
         <v>9</v>
@@ -20864,7 +20864,7 @@
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B779" t="s">
         <v>9</v>
@@ -20890,7 +20890,7 @@
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B780" t="s">
         <v>9</v>
@@ -20916,7 +20916,7 @@
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B781" t="s">
         <v>9</v>
@@ -20937,12 +20937,12 @@
         <v>44</v>
       </c>
       <c r="H781" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B782" t="s">
         <v>9</v>
@@ -20968,7 +20968,7 @@
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B783" t="s">
         <v>9</v>
@@ -20989,12 +20989,12 @@
         <v>49</v>
       </c>
       <c r="H783" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B784" t="s">
         <v>9</v>
@@ -21020,7 +21020,7 @@
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B785" t="s">
         <v>9</v>
@@ -21046,7 +21046,7 @@
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B786" t="s">
         <v>56</v>
@@ -21064,15 +21064,15 @@
         <v>2</v>
       </c>
       <c r="G786" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H786" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B787" t="s">
         <v>56</v>
@@ -21093,12 +21093,12 @@
         <v>78</v>
       </c>
       <c r="H787" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B788" t="s">
         <v>56</v>
@@ -21124,7 +21124,7 @@
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B789" t="s">
         <v>56</v>
@@ -21150,7 +21150,7 @@
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B790" t="s">
         <v>56</v>
@@ -21176,7 +21176,7 @@
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B791" t="s">
         <v>56</v>
@@ -21202,7 +21202,7 @@
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B792" t="s">
         <v>56</v>
@@ -21228,7 +21228,7 @@
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B793" t="s">
         <v>56</v>
@@ -21254,7 +21254,7 @@
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B794" t="s">
         <v>65</v>
@@ -21272,7 +21272,7 @@
         <v>1</v>
       </c>
       <c r="G794" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H794" t="s">
         <v>87</v>
@@ -21280,7 +21280,7 @@
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B795" t="s">
         <v>65</v>
@@ -21298,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="G795" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H795" t="s">
         <v>81</v>
@@ -21306,7 +21306,7 @@
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B796" t="s">
         <v>65</v>
@@ -21332,7 +21332,7 @@
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B797" t="s">
         <v>65</v>
@@ -21358,7 +21358,7 @@
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B798" t="s">
         <v>70</v>
@@ -21384,7 +21384,7 @@
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B799" t="s">
         <v>70</v>
@@ -21410,7 +21410,7 @@
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B800" t="s">
         <v>73</v>
@@ -21436,7 +21436,7 @@
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B801" t="s">
         <v>75</v>
@@ -21462,7 +21462,7 @@
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B802" t="s">
         <v>9</v>
@@ -21488,7 +21488,7 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B803" t="s">
         <v>9</v>
@@ -21514,7 +21514,7 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B804" t="s">
         <v>9</v>
@@ -21540,7 +21540,7 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B805" t="s">
         <v>9</v>
@@ -21566,7 +21566,7 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B806" t="s">
         <v>9</v>
@@ -21592,7 +21592,7 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B807" t="s">
         <v>9</v>
@@ -21618,7 +21618,7 @@
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B808" t="s">
         <v>9</v>
@@ -21644,7 +21644,7 @@
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B809" t="s">
         <v>9</v>
@@ -21665,12 +21665,12 @@
         <v>32</v>
       </c>
       <c r="H809" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B810" t="s">
         <v>9</v>
@@ -21696,7 +21696,7 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B811" t="s">
         <v>9</v>
@@ -21722,7 +21722,7 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B812" t="s">
         <v>9</v>
@@ -21748,7 +21748,7 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B813" t="s">
         <v>9</v>
@@ -21774,7 +21774,7 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B814" t="s">
         <v>9</v>
@@ -21800,7 +21800,7 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B815" t="s">
         <v>9</v>
@@ -21826,7 +21826,7 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B816" t="s">
         <v>9</v>
@@ -21852,7 +21852,7 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B817" t="s">
         <v>9</v>
@@ -21878,7 +21878,7 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B818" t="s">
         <v>56</v>
@@ -21904,7 +21904,7 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B819" t="s">
         <v>56</v>
@@ -21925,12 +21925,12 @@
         <v>78</v>
       </c>
       <c r="H819" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B820" t="s">
         <v>56</v>
@@ -21956,7 +21956,7 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B821" t="s">
         <v>56</v>
@@ -21982,7 +21982,7 @@
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B822" t="s">
         <v>56</v>
@@ -22008,7 +22008,7 @@
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B823" t="s">
         <v>56</v>
@@ -22034,7 +22034,7 @@
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B824" t="s">
         <v>56</v>
@@ -22060,7 +22060,7 @@
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B825" t="s">
         <v>56</v>
@@ -22086,7 +22086,7 @@
     </row>
     <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B826" t="s">
         <v>65</v>
@@ -22112,7 +22112,7 @@
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B827" t="s">
         <v>65</v>
@@ -22138,7 +22138,7 @@
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B828" t="s">
         <v>65</v>
@@ -22164,7 +22164,7 @@
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B829" t="s">
         <v>65</v>
@@ -22190,7 +22190,7 @@
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B830" t="s">
         <v>70</v>
@@ -22216,7 +22216,7 @@
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B831" t="s">
         <v>70</v>
@@ -22242,7 +22242,7 @@
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B832" t="s">
         <v>73</v>
@@ -22268,7 +22268,7 @@
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B833" t="s">
         <v>75</v>
@@ -22294,7 +22294,7 @@
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B834" t="s">
         <v>9</v>
@@ -22320,7 +22320,7 @@
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B835" t="s">
         <v>9</v>
@@ -22346,7 +22346,7 @@
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B836" t="s">
         <v>9</v>
@@ -22372,7 +22372,7 @@
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B837" t="s">
         <v>9</v>
@@ -22398,7 +22398,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B838" t="s">
         <v>9</v>
@@ -22424,7 +22424,7 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B839" t="s">
         <v>9</v>
@@ -22450,7 +22450,7 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B840" t="s">
         <v>9</v>
@@ -22476,7 +22476,7 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B841" t="s">
         <v>9</v>
@@ -22502,7 +22502,7 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B842" t="s">
         <v>9</v>
@@ -22528,7 +22528,7 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B843" t="s">
         <v>9</v>
@@ -22554,7 +22554,7 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B844" t="s">
         <v>9</v>
@@ -22580,7 +22580,7 @@
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B845" t="s">
         <v>9</v>
@@ -22606,7 +22606,7 @@
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B846" t="s">
         <v>9</v>
@@ -22632,7 +22632,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B847" t="s">
         <v>9</v>
@@ -22658,7 +22658,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B848" t="s">
         <v>9</v>
@@ -22684,7 +22684,7 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B849" t="s">
         <v>9</v>
@@ -22710,7 +22710,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B850" t="s">
         <v>56</v>
@@ -22736,7 +22736,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B851" t="s">
         <v>56</v>
@@ -22762,7 +22762,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B852" t="s">
         <v>56</v>
@@ -22788,7 +22788,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B853" t="s">
         <v>56</v>
@@ -22814,7 +22814,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B854" t="s">
         <v>56</v>
@@ -22840,7 +22840,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B855" t="s">
         <v>56</v>
@@ -22866,7 +22866,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B856" t="s">
         <v>56</v>
@@ -22892,7 +22892,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B857" t="s">
         <v>56</v>
@@ -22918,7 +22918,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B858" t="s">
         <v>65</v>
@@ -22944,7 +22944,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B859" t="s">
         <v>65</v>
@@ -22970,7 +22970,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B860" t="s">
         <v>65</v>
@@ -22996,7 +22996,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B861" t="s">
         <v>65</v>
@@ -23022,7 +23022,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B862" t="s">
         <v>70</v>
@@ -23048,7 +23048,7 @@
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B863" t="s">
         <v>70</v>
@@ -23057,7 +23057,7 @@
         <v>72</v>
       </c>
       <c r="D863" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E863">
         <v>2</v>
@@ -23074,7 +23074,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B864" t="s">
         <v>73</v>
@@ -23092,7 +23092,7 @@
         <v>1</v>
       </c>
       <c r="G864" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H864" t="s">
         <v>19</v>
@@ -23100,7 +23100,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B865" t="s">
         <v>75</v>
